--- a/reports/ASX_Strong_Buy_Screener_2026-10-13.xlsx
+++ b/reports/ASX_Strong_Buy_Screener_2026-10-13.xlsx
@@ -573,7 +573,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Report generated: 2026-10-13 02:11 </t>
+          <t xml:space="preserve">Report generated: 2026-10-13 23:48 </t>
         </is>
       </c>
     </row>
@@ -926,13 +926,13 @@
         <v>4.88</v>
       </c>
       <c r="F2" s="7" t="n">
-        <v>0.0354</v>
+        <v>0.0357</v>
       </c>
       <c r="G2" s="7" t="n">
-        <v>0.0708</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="H2" s="7" t="n">
-        <v>0.1417</v>
+        <v>0.1428</v>
       </c>
       <c r="I2" s="5" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         <v>26.36</v>
       </c>
       <c r="K2" s="5" t="n">
-        <v>5.45</v>
+        <v>5.55</v>
       </c>
       <c r="L2" s="5" t="n">
         <v>2.43</v>
@@ -968,7 +968,7 @@
       </c>
       <c r="Q2" s="5" t="inlineStr">
         <is>
-          <t>2026-10-13 02:11</t>
+          <t>2026-10-13 23:48</t>
         </is>
       </c>
     </row>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="Q3" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:11</t>
+          <t>2026-10-13 23:48</t>
         </is>
       </c>
     </row>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="Q4" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:11</t>
+          <t>2026-10-13 23:48</t>
         </is>
       </c>
     </row>
@@ -1134,7 +1134,7 @@
         </is>
       </c>
       <c r="C5" s="10" t="n">
-        <v>8.800000000000001</v>
+        <v>8.904999999999999</v>
       </c>
       <c r="D5" s="10" t="n">
         <v>10.63</v>
@@ -1143,13 +1143,13 @@
         <v>7.94</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>0.0319</v>
+        <v>0.0286</v>
       </c>
       <c r="G5" s="11" t="n">
-        <v>0.0639</v>
+        <v>0.0572</v>
       </c>
       <c r="H5" s="11" t="n">
-        <v>0.1278</v>
+        <v>0.1145</v>
       </c>
       <c r="I5" s="9" t="inlineStr">
         <is>
@@ -1157,13 +1157,13 @@
         </is>
       </c>
       <c r="J5" s="9" t="n">
-        <v>7.86</v>
+        <v>7.61</v>
       </c>
       <c r="K5" s="9" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="L5" s="9" t="n">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="M5" s="9" t="n">
         <v>0.77</v>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Q5" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:11</t>
+          <t>2026-10-13 23:48</t>
         </is>
       </c>
     </row>
@@ -1201,7 +1201,7 @@
         </is>
       </c>
       <c r="C6" s="10" t="n">
-        <v>6.65</v>
+        <v>6.68</v>
       </c>
       <c r="D6" s="10" t="n">
         <v>7.75</v>
@@ -1210,13 +1210,13 @@
         <v>6.52</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>0.0204</v>
+        <v>0.0194</v>
       </c>
       <c r="G6" s="11" t="n">
-        <v>0.0408</v>
+        <v>0.0389</v>
       </c>
       <c r="H6" s="11" t="n">
-        <v>0.08160000000000001</v>
+        <v>0.07779999999999999</v>
       </c>
       <c r="I6" s="9" t="inlineStr">
         <is>
@@ -1224,13 +1224,13 @@
         </is>
       </c>
       <c r="J6" s="9" t="n">
-        <v>39.12</v>
+        <v>39.29</v>
       </c>
       <c r="K6" s="9" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="L6" s="9" t="n">
-        <v>11.39</v>
+        <v>11.44</v>
       </c>
       <c r="M6" s="9" t="n">
         <v>0.26</v>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="Q6" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:11</t>
+          <t>2026-10-13 23:48</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1268,7 @@
         </is>
       </c>
       <c r="C7" s="10" t="n">
-        <v>43.81</v>
+        <v>43.63</v>
       </c>
       <c r="D7" s="10" t="n">
         <v>45.49</v>
@@ -1277,13 +1277,13 @@
         <v>27.575</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>-0.0018</v>
+        <v>0.0045</v>
       </c>
       <c r="G7" s="11" t="n">
-        <v>-0.0035</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="H7" s="11" t="n">
-        <v>-0.0071</v>
+        <v>0.018</v>
       </c>
       <c r="I7" s="9" t="inlineStr">
         <is>
@@ -1291,10 +1291,10 @@
         </is>
       </c>
       <c r="J7" s="9" t="n">
-        <v>6.78</v>
+        <v>6.64</v>
       </c>
       <c r="K7" s="9" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="L7" s="9" t="n">
         <v>0.29</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="Q7" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:11</t>
+          <t>2026-10-13 23:48</t>
         </is>
       </c>
     </row>
@@ -1335,22 +1335,22 @@
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>61.325</v>
+        <v>61.41</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>68.05</v>
+        <v>67.43000000000001</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>44.18</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>0.0211</v>
+        <v>0.0208</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>0.0423</v>
+        <v>0.0415</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>0.08459999999999999</v>
+        <v>0.08309999999999999</v>
       </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
@@ -1358,13 +1358,13 @@
         </is>
       </c>
       <c r="J8" s="5" t="n">
-        <v>25.88</v>
+        <v>25.38</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>5.99</v>
+        <v>6</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>5.77</v>
+        <v>5.78</v>
       </c>
       <c r="M8" s="5" t="n">
         <v>0.31</v>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="Q8" s="5" t="inlineStr">
         <is>
-          <t>2026-10-13 02:11</t>
+          <t>2026-10-13 23:48</t>
         </is>
       </c>
     </row>
@@ -1402,7 +1402,7 @@
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>20.49</v>
+        <v>20.22</v>
       </c>
       <c r="D9" s="6" t="n">
         <v>26.17</v>
@@ -1411,13 +1411,13 @@
         <v>19.28</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>0.0442</v>
+        <v>0.0482</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>0.0885</v>
+        <v>0.0964</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>0.177</v>
+        <v>0.1927</v>
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
@@ -1425,13 +1425,13 @@
         </is>
       </c>
       <c r="J9" s="5" t="n">
-        <v>32.52</v>
+        <v>32.61</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>6.12</v>
+        <v>6.04</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>3.13</v>
+        <v>3.09</v>
       </c>
       <c r="M9" s="5" t="n">
         <v>0.92</v>
@@ -1453,7 +1453,7 @@
       </c>
       <c r="Q9" s="5" t="inlineStr">
         <is>
-          <t>2026-10-13 02:11</t>
+          <t>2026-10-13 23:48</t>
         </is>
       </c>
     </row>
@@ -1469,22 +1469,22 @@
         </is>
       </c>
       <c r="C10" s="10" t="n">
-        <v>0.435</v>
+        <v>0.43</v>
       </c>
       <c r="D10" s="10" t="n">
         <v>0.95</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>0.41</v>
+        <v>0.395</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>0.9856</v>
+        <v>1</v>
       </c>
       <c r="G10" s="11" t="n">
-        <v>1.9713</v>
+        <v>2</v>
       </c>
       <c r="H10" s="11" t="n">
-        <v>3.9425</v>
+        <v>4</v>
       </c>
       <c r="I10" s="9" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         </is>
       </c>
       <c r="J10" s="9" t="n">
-        <v>-13.06</v>
+        <v>-12.91</v>
       </c>
       <c r="K10" s="9" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="Q10" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:11</t>
+          <t>2026-10-13 23:48</t>
         </is>
       </c>
     </row>
@@ -1542,7 +1542,7 @@
         </is>
       </c>
       <c r="C11" s="10" t="n">
-        <v>3.915</v>
+        <v>3.86</v>
       </c>
       <c r="D11" s="10" t="n">
         <v>5.235</v>
@@ -1551,13 +1551,13 @@
         <v>3.66</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>0.0364</v>
+        <v>0.0405</v>
       </c>
       <c r="G11" s="11" t="n">
-        <v>0.07290000000000001</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="H11" s="11" t="n">
-        <v>0.1458</v>
+        <v>0.1621</v>
       </c>
       <c r="I11" s="9" t="inlineStr">
         <is>
@@ -1565,13 +1565,13 @@
         </is>
       </c>
       <c r="J11" s="9" t="n">
-        <v>48.94</v>
+        <v>48.25</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="L11" s="9" t="n">
-        <v>36.29</v>
+        <v>35.78</v>
       </c>
       <c r="M11" s="9" t="n">
         <v>0.31</v>
@@ -1593,7 +1593,7 @@
       </c>
       <c r="Q11" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:11</t>
+          <t>2026-10-13 23:48</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
         </is>
       </c>
       <c r="C12" s="10" t="n">
-        <v>59.85</v>
+        <v>59.79</v>
       </c>
       <c r="D12" s="10" t="n">
         <v>71.09999999999999</v>
@@ -1618,13 +1618,13 @@
         <v>51.2</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>0.0501</v>
+        <v>0.0493</v>
       </c>
       <c r="G12" s="11" t="n">
-        <v>0.1002</v>
+        <v>0.0985</v>
       </c>
       <c r="H12" s="11" t="n">
-        <v>0.2005</v>
+        <v>0.197</v>
       </c>
       <c r="I12" s="9" t="inlineStr">
         <is>
@@ -1632,10 +1632,10 @@
         </is>
       </c>
       <c r="J12" s="9" t="n">
-        <v>17.05</v>
+        <v>17.03</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="L12" s="9" t="n">
         <v>1.18</v>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Q12" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:11</t>
+          <t>2026-10-13 23:48</t>
         </is>
       </c>
     </row>
@@ -1676,7 +1676,7 @@
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>2.475</v>
+        <v>2.41</v>
       </c>
       <c r="D13" s="6" t="n">
         <v>2.665</v>
@@ -1685,13 +1685,13 @@
         <v>1.14</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>0.0031</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>0.0062</v>
+        <v>0.0198</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>0.0123</v>
+        <v>0.0397</v>
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
@@ -1699,13 +1699,13 @@
         </is>
       </c>
       <c r="J13" s="5" t="n">
-        <v>30.94</v>
+        <v>30.13</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="M13" s="5" t="n">
         <v>7.9</v>
@@ -1727,7 +1727,7 @@
       </c>
       <c r="Q13" s="5" t="inlineStr">
         <is>
-          <t>2026-10-13 02:11</t>
+          <t>2026-10-13 23:48</t>
         </is>
       </c>
     </row>
@@ -1743,7 +1743,7 @@
         </is>
       </c>
       <c r="C14" s="10" t="n">
-        <v>45.22</v>
+        <v>45.24</v>
       </c>
       <c r="D14" s="10" t="n">
         <v>45.9</v>
@@ -1752,13 +1752,13 @@
         <v>25.05</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>-0.0285</v>
+        <v>-0.0294</v>
       </c>
       <c r="G14" s="11" t="n">
-        <v>-0.057</v>
+        <v>-0.0589</v>
       </c>
       <c r="H14" s="11" t="n">
-        <v>-0.1141</v>
+        <v>-0.1178</v>
       </c>
       <c r="I14" s="9" t="inlineStr">
         <is>
@@ -1766,10 +1766,10 @@
         </is>
       </c>
       <c r="J14" s="9" t="n">
-        <v>21.13</v>
+        <v>21.14</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="L14" s="9" t="n">
         <v>2.97</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="Q14" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:11</t>
+          <t>2026-10-13 23:48</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
         </is>
       </c>
       <c r="C15" s="10" t="n">
-        <v>38.23</v>
+        <v>37.97</v>
       </c>
       <c r="D15" s="10" t="n">
         <v>41</v>
@@ -1819,13 +1819,13 @@
         <v>33.36</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>-0.0109</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="G15" s="11" t="n">
-        <v>-0.0219</v>
+        <v>-0.0186</v>
       </c>
       <c r="H15" s="11" t="n">
-        <v>-0.0437</v>
+        <v>-0.0372</v>
       </c>
       <c r="I15" s="9" t="inlineStr">
         <is>
@@ -1833,15 +1833,13 @@
         </is>
       </c>
       <c r="J15" s="9" t="n">
-        <v>19.41</v>
+        <v>18.98</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="L15" s="9" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
+        <v>1.61</v>
+      </c>
+      <c r="L15" s="9" t="n">
+        <v>5.31</v>
       </c>
       <c r="M15" s="9" t="inlineStr">
         <is>
@@ -1865,7 +1863,7 @@
       </c>
       <c r="Q15" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:11</t>
+          <t>2026-10-13 23:48</t>
         </is>
       </c>
     </row>
@@ -1881,7 +1879,7 @@
         </is>
       </c>
       <c r="C16" s="10" t="n">
-        <v>11.04</v>
+        <v>11.005</v>
       </c>
       <c r="D16" s="10" t="n">
         <v>11.1</v>
@@ -1890,13 +1888,13 @@
         <v>8.445</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>-0.0289</v>
+        <v>-0.0282</v>
       </c>
       <c r="G16" s="11" t="n">
-        <v>-0.0577</v>
+        <v>-0.0563</v>
       </c>
       <c r="H16" s="11" t="n">
-        <v>-0.1154</v>
+        <v>-0.1126</v>
       </c>
       <c r="I16" s="9" t="inlineStr">
         <is>
@@ -1904,13 +1902,13 @@
         </is>
       </c>
       <c r="J16" s="9" t="n">
-        <v>69</v>
+        <v>68.78</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>5.41</v>
+        <v>5.4</v>
       </c>
       <c r="L16" s="9" t="n">
-        <v>4.9</v>
+        <v>4.88</v>
       </c>
       <c r="M16" s="9" t="n">
         <v>5.26</v>
@@ -1932,7 +1930,7 @@
       </c>
       <c r="Q16" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:11</t>
+          <t>2026-10-13 23:48</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1946,7 @@
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>17.915</v>
+        <v>18.01</v>
       </c>
       <c r="D17" s="6" t="n">
         <v>35.01</v>
@@ -1957,13 +1955,13 @@
         <v>17.71</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>0.1094</v>
+        <v>0.1075</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>0.2187</v>
+        <v>0.215</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>0.4375</v>
+        <v>0.4299</v>
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
@@ -1971,10 +1969,10 @@
         </is>
       </c>
       <c r="J17" s="5" t="n">
-        <v>20.83</v>
+        <v>20.47</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="L17" s="5" t="n">
         <v>0.35</v>
@@ -1999,7 +1997,7 @@
       </c>
       <c r="Q17" s="5" t="inlineStr">
         <is>
-          <t>2026-10-13 02:11</t>
+          <t>2026-10-13 23:48</t>
         </is>
       </c>
     </row>
@@ -2074,7 +2072,7 @@
       </c>
       <c r="Q18" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:11</t>
+          <t>2026-10-13 23:48</t>
         </is>
       </c>
     </row>
@@ -2090,22 +2088,22 @@
         </is>
       </c>
       <c r="C19" s="10" t="n">
-        <v>17.26</v>
+        <v>17.12</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>39.47</v>
+        <v>39.29</v>
       </c>
       <c r="E19" s="10" t="n">
         <v>16.505</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>0.0922</v>
+        <v>0.095</v>
       </c>
       <c r="G19" s="11" t="n">
-        <v>0.1844</v>
+        <v>0.19</v>
       </c>
       <c r="H19" s="11" t="n">
-        <v>0.3688</v>
+        <v>0.3799</v>
       </c>
       <c r="I19" s="9" t="inlineStr">
         <is>
@@ -2113,13 +2111,13 @@
         </is>
       </c>
       <c r="J19" s="9" t="n">
-        <v>15.55</v>
+        <v>15.02</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="L19" s="9" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="M19" s="9" t="n">
         <v>6.68</v>
@@ -2141,7 +2139,7 @@
       </c>
       <c r="Q19" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:11</t>
+          <t>2026-10-13 23:48</t>
         </is>
       </c>
     </row>
@@ -2157,7 +2155,7 @@
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>2.415</v>
+        <v>2.425</v>
       </c>
       <c r="D20" s="6" t="n">
         <v>3.95</v>
@@ -2166,13 +2164,13 @@
         <v>1.985</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>0.0612</v>
+        <v>0.0592</v>
       </c>
       <c r="G20" s="7" t="n">
-        <v>0.1224</v>
+        <v>0.1184</v>
       </c>
       <c r="H20" s="7" t="n">
-        <v>0.2449</v>
+        <v>0.2369</v>
       </c>
       <c r="I20" s="5" t="inlineStr">
         <is>
@@ -2180,13 +2178,13 @@
         </is>
       </c>
       <c r="J20" s="5" t="n">
-        <v>7.32</v>
+        <v>7.35</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>8.42</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="M20" s="5" t="n">
         <v>0.35</v>
@@ -2208,7 +2206,7 @@
       </c>
       <c r="Q20" s="5" t="inlineStr">
         <is>
-          <t>2026-10-13 02:11</t>
+          <t>2026-10-13 23:48</t>
         </is>
       </c>
     </row>
@@ -2224,7 +2222,7 @@
         </is>
       </c>
       <c r="C21" s="10" t="n">
-        <v>61.41</v>
+        <v>61.03</v>
       </c>
       <c r="D21" s="10" t="n">
         <v>62.9</v>
@@ -2233,13 +2231,13 @@
         <v>44.3</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>-0.0046</v>
+        <v>-0.003</v>
       </c>
       <c r="G21" s="11" t="n">
-        <v>-0.0091</v>
+        <v>-0.006</v>
       </c>
       <c r="H21" s="11" t="n">
-        <v>-0.0182</v>
+        <v>-0.0121</v>
       </c>
       <c r="I21" s="9" t="inlineStr">
         <is>
@@ -2247,13 +2245,13 @@
         </is>
       </c>
       <c r="J21" s="9" t="n">
-        <v>24.66</v>
+        <v>24.31</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>3.01</v>
+        <v>2.99</v>
       </c>
       <c r="L21" s="9" t="n">
-        <v>9.6</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="M21" s="9" t="n">
         <v>0.12</v>
@@ -2275,7 +2273,7 @@
       </c>
       <c r="Q21" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:11</t>
+          <t>2026-10-13 23:48</t>
         </is>
       </c>
     </row>
@@ -2291,7 +2289,7 @@
         </is>
       </c>
       <c r="C22" s="6" t="n">
-        <v>27.84</v>
+        <v>27.93</v>
       </c>
       <c r="D22" s="6" t="n">
         <v>40.28</v>
@@ -2300,13 +2298,13 @@
         <v>22.08</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>0.06619999999999999</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="G22" s="7" t="n">
-        <v>0.1324</v>
+        <v>0.1304</v>
       </c>
       <c r="H22" s="7" t="n">
-        <v>0.2649</v>
+        <v>0.2608</v>
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
@@ -2314,13 +2312,13 @@
         </is>
       </c>
       <c r="J22" s="5" t="n">
-        <v>35.69</v>
+        <v>35.81</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="M22" s="5" t="n">
         <v>0.55</v>
@@ -2342,7 +2340,7 @@
       </c>
       <c r="Q22" s="5" t="inlineStr">
         <is>
-          <t>2026-10-13 02:11</t>
+          <t>2026-10-13 23:49</t>
         </is>
       </c>
     </row>
@@ -2417,7 +2415,7 @@
       </c>
       <c r="Q23" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:11</t>
+          <t>2026-10-13 23:49</t>
         </is>
       </c>
     </row>
@@ -2433,22 +2431,22 @@
         </is>
       </c>
       <c r="C24" s="10" t="n">
-        <v>3.765</v>
+        <v>3.755</v>
       </c>
       <c r="D24" s="10" t="n">
         <v>4.42</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>3.23</v>
+        <v>3.245</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>-0.0036</v>
+        <v>-0.0029</v>
       </c>
       <c r="G24" s="11" t="n">
-        <v>-0.0071</v>
+        <v>-0.0058</v>
       </c>
       <c r="H24" s="11" t="n">
-        <v>-0.0142</v>
+        <v>-0.0116</v>
       </c>
       <c r="I24" s="9" t="inlineStr">
         <is>
@@ -2456,10 +2454,10 @@
         </is>
       </c>
       <c r="J24" s="9" t="n">
-        <v>17.93</v>
+        <v>17.88</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="L24" s="9" t="n">
         <v>1.52</v>
@@ -2484,7 +2482,7 @@
       </c>
       <c r="Q24" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:11</t>
+          <t>2026-10-13 23:49</t>
         </is>
       </c>
     </row>
@@ -2500,7 +2498,7 @@
         </is>
       </c>
       <c r="C25" s="10" t="n">
-        <v>0.762</v>
+        <v>0.755</v>
       </c>
       <c r="D25" s="10" t="n">
         <v>3.19</v>
@@ -2509,13 +2507,13 @@
         <v>0.355</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>-0.0016</v>
+        <v>0.0008</v>
       </c>
       <c r="G25" s="11" t="n">
-        <v>-0.0031</v>
+        <v>0.0015</v>
       </c>
       <c r="H25" s="11" t="n">
-        <v>-0.0062</v>
+        <v>0.003</v>
       </c>
       <c r="I25" s="9" t="inlineStr">
         <is>
@@ -2523,13 +2521,13 @@
         </is>
       </c>
       <c r="J25" s="9" t="n">
-        <v>17.05</v>
+        <v>16.89</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>0.91</v>
+        <v>0.9</v>
       </c>
       <c r="L25" s="9" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="M25" s="9" t="n">
         <v>0.76</v>
@@ -2551,7 +2549,7 @@
       </c>
       <c r="Q25" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:11</t>
+          <t>2026-10-13 23:49</t>
         </is>
       </c>
     </row>
@@ -2567,7 +2565,7 @@
         </is>
       </c>
       <c r="C26" s="10" t="n">
-        <v>10.48</v>
+        <v>10.38</v>
       </c>
       <c r="D26" s="10" t="n">
         <v>13.11</v>
@@ -2576,13 +2574,13 @@
         <v>9.81</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>-0.0016</v>
+        <v>0.0008</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>-0.0032</v>
+        <v>0.0016</v>
       </c>
       <c r="H26" s="11" t="n">
-        <v>-0.0065</v>
+        <v>0.0031</v>
       </c>
       <c r="I26" s="9" t="inlineStr">
         <is>
@@ -2590,13 +2588,13 @@
         </is>
       </c>
       <c r="J26" s="9" t="n">
-        <v>16.63</v>
+        <v>16.48</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>0.9</v>
+        <v>0.89</v>
       </c>
       <c r="L26" s="9" t="n">
-        <v>3.1</v>
+        <v>3.07</v>
       </c>
       <c r="M26" s="9" t="inlineStr">
         <is>
@@ -2620,7 +2618,7 @@
       </c>
       <c r="Q26" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:11</t>
+          <t>2026-10-13 23:49</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2634,7 @@
         </is>
       </c>
       <c r="C27" s="6" t="n">
-        <v>6.42</v>
+        <v>6.41</v>
       </c>
       <c r="D27" s="6" t="n">
         <v>6.89</v>
@@ -2645,13 +2643,13 @@
         <v>5</v>
       </c>
       <c r="F27" s="7" t="n">
-        <v>0.0256</v>
+        <v>0.026</v>
       </c>
       <c r="G27" s="7" t="n">
-        <v>0.0511</v>
+        <v>0.052</v>
       </c>
       <c r="H27" s="7" t="n">
-        <v>0.1022</v>
+        <v>0.104</v>
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
@@ -2659,7 +2657,7 @@
         </is>
       </c>
       <c r="J27" s="5" t="n">
-        <v>35.67</v>
+        <v>35.61</v>
       </c>
       <c r="K27" s="5" t="n">
         <v>1.97</v>
@@ -2687,7 +2685,7 @@
       </c>
       <c r="Q27" s="5" t="inlineStr">
         <is>
-          <t>2026-10-13 02:11</t>
+          <t>2026-10-13 23:49</t>
         </is>
       </c>
     </row>
@@ -2703,7 +2701,7 @@
         </is>
       </c>
       <c r="C28" s="10" t="n">
-        <v>61.48</v>
+        <v>61.17</v>
       </c>
       <c r="D28" s="10" t="n">
         <v>68.77</v>
@@ -2712,13 +2710,13 @@
         <v>40.175</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>-0.009299999999999999</v>
+        <v>-0.0057</v>
       </c>
       <c r="G28" s="11" t="n">
-        <v>-0.0185</v>
+        <v>-0.0114</v>
       </c>
       <c r="H28" s="11" t="n">
-        <v>-0.0371</v>
+        <v>-0.0228</v>
       </c>
       <c r="I28" s="9" t="inlineStr">
         <is>
@@ -2726,13 +2724,13 @@
         </is>
       </c>
       <c r="J28" s="9" t="n">
-        <v>21.57</v>
+        <v>21.46</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>4.28</v>
+        <v>4.26</v>
       </c>
       <c r="L28" s="9" t="n">
-        <v>5.32</v>
+        <v>5.29</v>
       </c>
       <c r="M28" s="9" t="n">
         <v>0.5</v>
@@ -2754,7 +2752,7 @@
       </c>
       <c r="Q28" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:11</t>
+          <t>2026-10-13 23:49</t>
         </is>
       </c>
     </row>
@@ -2829,7 +2827,7 @@
       </c>
       <c r="Q29" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:11</t>
+          <t>2026-10-13 23:49</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2902,7 @@
       </c>
       <c r="Q30" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:11</t>
+          <t>2026-10-13 23:49</t>
         </is>
       </c>
     </row>
@@ -2979,7 +2977,7 @@
       </c>
       <c r="Q31" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:11</t>
+          <t>2026-10-13 23:49</t>
         </is>
       </c>
     </row>
@@ -2995,7 +2993,7 @@
         </is>
       </c>
       <c r="C32" s="10" t="n">
-        <v>6.67</v>
+        <v>6.58</v>
       </c>
       <c r="D32" s="10" t="n">
         <v>7.48</v>
@@ -3004,13 +3002,13 @@
         <v>5.91</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>-0.0168</v>
+        <v>-0.0136</v>
       </c>
       <c r="G32" s="11" t="n">
-        <v>-0.0336</v>
+        <v>-0.0273</v>
       </c>
       <c r="H32" s="11" t="n">
-        <v>-0.0673</v>
+        <v>-0.0545</v>
       </c>
       <c r="I32" s="9" t="inlineStr">
         <is>
@@ -3018,13 +3016,13 @@
         </is>
       </c>
       <c r="J32" s="9" t="n">
-        <v>44.47</v>
+        <v>43.87</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>0.74</v>
+        <v>0.73</v>
       </c>
       <c r="L32" s="9" t="n">
-        <v>2.63</v>
+        <v>2.59</v>
       </c>
       <c r="M32" s="9" t="inlineStr">
         <is>
@@ -3048,7 +3046,7 @@
       </c>
       <c r="Q32" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:11</t>
+          <t>2026-10-13 23:49</t>
         </is>
       </c>
     </row>
@@ -3064,7 +3062,7 @@
         </is>
       </c>
       <c r="C33" s="10" t="n">
-        <v>0.862</v>
+        <v>0.877</v>
       </c>
       <c r="D33" s="10" t="n">
         <v>1.335</v>
@@ -3073,13 +3071,13 @@
         <v>0.8120000000000001</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>0.0426</v>
+        <v>0.0394</v>
       </c>
       <c r="G33" s="11" t="n">
-        <v>0.0851</v>
+        <v>0.0788</v>
       </c>
       <c r="H33" s="11" t="n">
-        <v>0.1702</v>
+        <v>0.1576</v>
       </c>
       <c r="I33" s="9" t="inlineStr">
         <is>
@@ -3087,15 +3085,13 @@
         </is>
       </c>
       <c r="J33" s="9" t="n">
-        <v>7.18</v>
+        <v>7.31</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="L33" s="9" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
+        <v>0.61</v>
+      </c>
+      <c r="L33" s="9" t="n">
+        <v>1.04</v>
       </c>
       <c r="M33" s="9" t="n">
         <v>0.19</v>
@@ -3117,7 +3113,7 @@
       </c>
       <c r="Q33" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:11</t>
+          <t>2026-10-13 23:49</t>
         </is>
       </c>
     </row>
@@ -3133,7 +3129,7 @@
         </is>
       </c>
       <c r="C34" s="6" t="n">
-        <v>31.32</v>
+        <v>30.86</v>
       </c>
       <c r="D34" s="6" t="n">
         <v>35.48</v>
@@ -3142,13 +3138,13 @@
         <v>25.41</v>
       </c>
       <c r="F34" s="7" t="n">
-        <v>0.0363</v>
+        <v>0.0406</v>
       </c>
       <c r="G34" s="7" t="n">
-        <v>0.0726</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="H34" s="7" t="n">
-        <v>0.1452</v>
+        <v>0.1623</v>
       </c>
       <c r="I34" s="5" t="inlineStr">
         <is>
@@ -3156,13 +3152,13 @@
         </is>
       </c>
       <c r="J34" s="5" t="n">
-        <v>33.32</v>
+        <v>32.83</v>
       </c>
       <c r="K34" s="5" t="n">
-        <v>4.29</v>
+        <v>4.22</v>
       </c>
       <c r="L34" s="5" t="n">
-        <v>2.52</v>
+        <v>2.49</v>
       </c>
       <c r="M34" s="5" t="n">
         <v>0.14</v>
@@ -3184,7 +3180,7 @@
       </c>
       <c r="Q34" s="5" t="inlineStr">
         <is>
-          <t>2026-10-13 02:11</t>
+          <t>2026-10-13 23:49</t>
         </is>
       </c>
     </row>
@@ -3200,7 +3196,7 @@
         </is>
       </c>
       <c r="C35" s="10" t="n">
-        <v>31.19</v>
+        <v>30.705</v>
       </c>
       <c r="D35" s="10" t="n">
         <v>35.26</v>
@@ -3209,13 +3205,13 @@
         <v>20.23</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>0.0317</v>
+        <v>0.0361</v>
       </c>
       <c r="G35" s="11" t="n">
-        <v>0.0634</v>
+        <v>0.0723</v>
       </c>
       <c r="H35" s="11" t="n">
-        <v>0.1267</v>
+        <v>0.1445</v>
       </c>
       <c r="I35" s="9" t="inlineStr">
         <is>
@@ -3223,15 +3219,13 @@
         </is>
       </c>
       <c r="J35" s="9" t="n">
-        <v>17.23</v>
+        <v>17.06</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="L35" s="9" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
+        <v>1.3</v>
+      </c>
+      <c r="L35" s="9" t="n">
+        <v>0.8100000000000001</v>
       </c>
       <c r="M35" s="9" t="n">
         <v>0.16</v>
@@ -3253,7 +3247,7 @@
       </c>
       <c r="Q35" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:11</t>
+          <t>2026-10-13 23:49</t>
         </is>
       </c>
     </row>
@@ -3269,7 +3263,7 @@
         </is>
       </c>
       <c r="C36" s="10" t="n">
-        <v>3.56</v>
+        <v>3.57</v>
       </c>
       <c r="D36" s="10" t="n">
         <v>4.12</v>
@@ -3278,13 +3272,13 @@
         <v>3.395</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>0.0185</v>
+        <v>0.0178</v>
       </c>
       <c r="G36" s="11" t="n">
-        <v>0.0371</v>
+        <v>0.0356</v>
       </c>
       <c r="H36" s="11" t="n">
-        <v>0.0741</v>
+        <v>0.0711</v>
       </c>
       <c r="I36" s="9" t="inlineStr">
         <is>
@@ -3292,13 +3286,13 @@
         </is>
       </c>
       <c r="J36" s="9" t="n">
-        <v>6.36</v>
+        <v>6.38</v>
       </c>
       <c r="K36" s="9" t="n">
         <v>0.84</v>
       </c>
       <c r="L36" s="9" t="n">
-        <v>13.36</v>
+        <v>13.4</v>
       </c>
       <c r="M36" s="9" t="n">
         <v>0.23</v>
@@ -3320,7 +3314,7 @@
       </c>
       <c r="Q36" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:11</t>
+          <t>2026-10-13 23:49</t>
         </is>
       </c>
     </row>
@@ -3336,7 +3330,7 @@
         </is>
       </c>
       <c r="C37" s="10" t="n">
-        <v>19.65</v>
+        <v>19.51</v>
       </c>
       <c r="D37" s="10" t="n">
         <v>25.56</v>
@@ -3345,13 +3339,13 @@
         <v>16.18</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>0.0287</v>
+        <v>0.0297</v>
       </c>
       <c r="G37" s="11" t="n">
-        <v>0.0575</v>
+        <v>0.0594</v>
       </c>
       <c r="H37" s="11" t="n">
-        <v>0.1149</v>
+        <v>0.1188</v>
       </c>
       <c r="I37" s="9" t="inlineStr">
         <is>
@@ -3359,13 +3353,13 @@
         </is>
       </c>
       <c r="J37" s="9" t="n">
-        <v>19.08</v>
+        <v>18.76</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>5.63</v>
+        <v>5.61</v>
       </c>
       <c r="L37" s="9" t="n">
-        <v>3.6</v>
+        <v>3.57</v>
       </c>
       <c r="M37" s="9" t="n">
         <v>0.9399999999999999</v>
@@ -3387,7 +3381,7 @@
       </c>
       <c r="Q37" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:11</t>
+          <t>2026-10-13 23:49</t>
         </is>
       </c>
     </row>
@@ -3403,7 +3397,7 @@
         </is>
       </c>
       <c r="C38" s="6" t="n">
-        <v>22.69</v>
+        <v>22.475</v>
       </c>
       <c r="D38" s="6" t="n">
         <v>37.45</v>
@@ -3412,13 +3406,13 @@
         <v>21.2</v>
       </c>
       <c r="F38" s="7" t="n">
-        <v>0.1171</v>
+        <v>0.1206</v>
       </c>
       <c r="G38" s="7" t="n">
-        <v>0.2342</v>
+        <v>0.2413</v>
       </c>
       <c r="H38" s="7" t="n">
-        <v>0.4685</v>
+        <v>0.4825</v>
       </c>
       <c r="I38" s="5" t="inlineStr">
         <is>
@@ -3426,13 +3420,13 @@
         </is>
       </c>
       <c r="J38" s="5" t="n">
-        <v>27.34</v>
+        <v>27.08</v>
       </c>
       <c r="K38" s="5" t="n">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>6.86</v>
+        <v>6.8</v>
       </c>
       <c r="M38" s="5" t="n">
         <v>0.57</v>
@@ -3454,7 +3448,7 @@
       </c>
       <c r="Q38" s="5" t="inlineStr">
         <is>
-          <t>2026-10-13 02:11</t>
+          <t>2026-10-13 23:49</t>
         </is>
       </c>
     </row>
@@ -3470,7 +3464,7 @@
         </is>
       </c>
       <c r="C39" s="10" t="n">
-        <v>152.48</v>
+        <v>152.02</v>
       </c>
       <c r="D39" s="10" t="n">
         <v>185.59</v>
@@ -3479,13 +3473,13 @@
         <v>146.98</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>-0.044</v>
+        <v>-0.0434</v>
       </c>
       <c r="G39" s="11" t="n">
-        <v>-0.08799999999999999</v>
+        <v>-0.0868</v>
       </c>
       <c r="H39" s="11" t="n">
-        <v>-0.176</v>
+        <v>-0.1735</v>
       </c>
       <c r="I39" s="9" t="inlineStr">
         <is>
@@ -3493,13 +3487,13 @@
         </is>
       </c>
       <c r="J39" s="9" t="n">
-        <v>23.39</v>
+        <v>23.32</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>3.24</v>
+        <v>3.23</v>
       </c>
       <c r="L39" s="9" t="n">
-        <v>8.68</v>
+        <v>8.66</v>
       </c>
       <c r="M39" s="9" t="inlineStr">
         <is>
@@ -3523,7 +3517,7 @@
       </c>
       <c r="Q39" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:11</t>
+          <t>2026-10-13 23:49</t>
         </is>
       </c>
     </row>
@@ -3539,7 +3533,7 @@
         </is>
       </c>
       <c r="C40" s="10" t="n">
-        <v>14.415</v>
+        <v>14.28</v>
       </c>
       <c r="D40" s="10" t="n">
         <v>15.32</v>
@@ -3548,13 +3542,13 @@
         <v>9.5</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>0.0464</v>
+        <v>0.0492</v>
       </c>
       <c r="G40" s="11" t="n">
-        <v>0.0929</v>
+        <v>0.0985</v>
       </c>
       <c r="H40" s="11" t="n">
-        <v>0.1858</v>
+        <v>0.197</v>
       </c>
       <c r="I40" s="9" t="inlineStr">
         <is>
@@ -3562,13 +3556,13 @@
         </is>
       </c>
       <c r="J40" s="9" t="n">
-        <v>9.300000000000001</v>
+        <v>9.15</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="L40" s="9" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="M40" s="9" t="n">
         <v>0.54</v>
@@ -3590,7 +3584,7 @@
       </c>
       <c r="Q40" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:11</t>
+          <t>2026-10-13 23:49</t>
         </is>
       </c>
     </row>
@@ -3665,7 +3659,7 @@
       </c>
       <c r="Q41" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:11</t>
+          <t>2026-10-13 23:49</t>
         </is>
       </c>
     </row>
@@ -3681,7 +3675,7 @@
         </is>
       </c>
       <c r="C42" s="10" t="n">
-        <v>9.82</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="D42" s="10" t="n">
         <v>10.85</v>
@@ -3690,13 +3684,13 @@
         <v>7.25</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>0.0139</v>
+        <v>0.0169</v>
       </c>
       <c r="G42" s="11" t="n">
-        <v>0.0277</v>
+        <v>0.0337</v>
       </c>
       <c r="H42" s="11" t="n">
-        <v>0.0555</v>
+        <v>0.0675</v>
       </c>
       <c r="I42" s="9" t="inlineStr">
         <is>
@@ -3704,13 +3698,13 @@
         </is>
       </c>
       <c r="J42" s="9" t="n">
-        <v>17.23</v>
+        <v>16.74</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="L42" s="9" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="M42" s="9" t="n">
         <v>2.08</v>
@@ -3732,7 +3726,7 @@
       </c>
       <c r="Q42" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:11</t>
+          <t>2026-10-13 23:49</t>
         </is>
       </c>
     </row>
@@ -3748,7 +3742,7 @@
         </is>
       </c>
       <c r="C43" s="10" t="n">
-        <v>18.145</v>
+        <v>18.35</v>
       </c>
       <c r="D43" s="10" t="n">
         <v>25.95</v>
@@ -3757,13 +3751,13 @@
         <v>17.49</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>0.0722</v>
+        <v>0.06859999999999999</v>
       </c>
       <c r="G43" s="11" t="n">
-        <v>0.1444</v>
+        <v>0.1372</v>
       </c>
       <c r="H43" s="11" t="n">
-        <v>0.2889</v>
+        <v>0.2745</v>
       </c>
       <c r="I43" s="9" t="inlineStr">
         <is>
@@ -3771,13 +3765,13 @@
         </is>
       </c>
       <c r="J43" s="9" t="n">
-        <v>20.39</v>
+        <v>21.09</v>
       </c>
       <c r="K43" s="9" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="L43" s="9" t="n">
-        <v>10.58</v>
+        <v>10.7</v>
       </c>
       <c r="M43" s="9" t="n">
         <v>0.26</v>
@@ -3799,7 +3793,7 @@
       </c>
       <c r="Q43" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:11</t>
+          <t>2026-10-13 23:49</t>
         </is>
       </c>
     </row>
@@ -3815,22 +3809,22 @@
         </is>
       </c>
       <c r="C44" s="6" t="n">
-        <v>2.75</v>
+        <v>2.705</v>
       </c>
       <c r="D44" s="6" t="n">
         <v>6.685</v>
       </c>
       <c r="E44" s="6" t="n">
-        <v>2.715</v>
+        <v>2.695</v>
       </c>
       <c r="F44" s="7" t="n">
-        <v>0.1484</v>
+        <v>0.155</v>
       </c>
       <c r="G44" s="7" t="n">
-        <v>0.2969</v>
+        <v>0.31</v>
       </c>
       <c r="H44" s="7" t="n">
-        <v>0.5937</v>
+        <v>0.6201</v>
       </c>
       <c r="I44" s="5" t="inlineStr">
         <is>
@@ -3838,13 +3832,13 @@
         </is>
       </c>
       <c r="J44" s="5" t="n">
-        <v>12.5</v>
+        <v>12.3</v>
       </c>
       <c r="K44" s="5" t="n">
-        <v>0.95</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="L44" s="5" t="n">
-        <v>0.89</v>
+        <v>0.87</v>
       </c>
       <c r="M44" s="5" t="n">
         <v>0.88</v>
@@ -3866,7 +3860,7 @@
       </c>
       <c r="Q44" s="5" t="inlineStr">
         <is>
-          <t>2026-10-13 02:11</t>
+          <t>2026-10-13 23:49</t>
         </is>
       </c>
     </row>
@@ -3905,7 +3899,7 @@
         </is>
       </c>
       <c r="J45" s="5" t="n">
-        <v>10.75</v>
+        <v>11.18</v>
       </c>
       <c r="K45" s="5" t="n">
         <v>0.7</v>
@@ -3933,7 +3927,7 @@
       </c>
       <c r="Q45" s="5" t="inlineStr">
         <is>
-          <t>2026-10-13 02:11</t>
+          <t>2026-10-13 23:49</t>
         </is>
       </c>
     </row>
@@ -3949,7 +3943,7 @@
         </is>
       </c>
       <c r="C46" s="6" t="n">
-        <v>8.449999999999999</v>
+        <v>8.435</v>
       </c>
       <c r="D46" s="6" t="n">
         <v>12.73</v>
@@ -3958,13 +3952,13 @@
         <v>7.59</v>
       </c>
       <c r="F46" s="7" t="n">
-        <v>0.0518</v>
+        <v>0.0523</v>
       </c>
       <c r="G46" s="7" t="n">
-        <v>0.1036</v>
+        <v>0.1047</v>
       </c>
       <c r="H46" s="7" t="n">
-        <v>0.2072</v>
+        <v>0.2093</v>
       </c>
       <c r="I46" s="5" t="inlineStr">
         <is>
@@ -3972,10 +3966,10 @@
         </is>
       </c>
       <c r="J46" s="5" t="n">
-        <v>21.12</v>
+        <v>21.09</v>
       </c>
       <c r="K46" s="5" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="L46" s="5" t="n">
         <v>0.63</v>
@@ -4000,7 +3994,7 @@
       </c>
       <c r="Q46" s="5" t="inlineStr">
         <is>
-          <t>2026-10-13 02:11</t>
+          <t>2026-10-13 23:49</t>
         </is>
       </c>
     </row>
@@ -4067,7 +4061,7 @@
       </c>
       <c r="Q47" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:11</t>
+          <t>2026-10-13 23:49</t>
         </is>
       </c>
     </row>
@@ -4134,7 +4128,7 @@
       </c>
       <c r="Q48" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:11</t>
+          <t>2026-10-13 23:49</t>
         </is>
       </c>
     </row>
@@ -4150,22 +4144,22 @@
         </is>
       </c>
       <c r="C49" s="10" t="n">
-        <v>6.55</v>
+        <v>6.54</v>
       </c>
       <c r="D49" s="10" t="n">
         <v>8.49</v>
       </c>
       <c r="E49" s="10" t="n">
-        <v>6.55</v>
+        <v>6.5</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>0.0606</v>
+        <v>0.0614</v>
       </c>
       <c r="G49" s="11" t="n">
-        <v>0.1213</v>
+        <v>0.1229</v>
       </c>
       <c r="H49" s="11" t="n">
-        <v>0.2426</v>
+        <v>0.2457</v>
       </c>
       <c r="I49" s="9" t="inlineStr">
         <is>
@@ -4173,7 +4167,7 @@
         </is>
       </c>
       <c r="J49" s="9" t="n">
-        <v>93.56999999999999</v>
+        <v>93.43000000000001</v>
       </c>
       <c r="K49" s="9" t="n">
         <v>3.41</v>
@@ -4201,7 +4195,7 @@
       </c>
       <c r="Q49" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:12</t>
+          <t>2026-10-13 23:49</t>
         </is>
       </c>
     </row>
@@ -4217,7 +4211,7 @@
         </is>
       </c>
       <c r="C50" s="10" t="n">
-        <v>129.39</v>
+        <v>127.57</v>
       </c>
       <c r="D50" s="10" t="n">
         <v>296.5</v>
@@ -4226,13 +4220,13 @@
         <v>88.73999999999999</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>0.0149</v>
+        <v>0.0186</v>
       </c>
       <c r="G50" s="11" t="n">
-        <v>0.0297</v>
+        <v>0.0373</v>
       </c>
       <c r="H50" s="11" t="n">
-        <v>0.0595</v>
+        <v>0.0746</v>
       </c>
       <c r="I50" s="9" t="inlineStr">
         <is>
@@ -4240,13 +4234,13 @@
         </is>
       </c>
       <c r="J50" s="9" t="n">
-        <v>57.51</v>
+        <v>56.95</v>
       </c>
       <c r="K50" s="9" t="n">
-        <v>4.86</v>
+        <v>4.79</v>
       </c>
       <c r="L50" s="9" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="M50" s="9" t="n">
         <v>0.12</v>
@@ -4268,7 +4262,7 @@
       </c>
       <c r="Q50" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:12</t>
+          <t>2026-10-13 23:49</t>
         </is>
       </c>
     </row>
@@ -4284,7 +4278,7 @@
         </is>
       </c>
       <c r="C51" s="10" t="n">
-        <v>23.68</v>
+        <v>23.74</v>
       </c>
       <c r="D51" s="10" t="n">
         <v>24.59</v>
@@ -4293,13 +4287,13 @@
         <v>20.1</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>0.005</v>
+        <v>0.0044</v>
       </c>
       <c r="G51" s="11" t="n">
-        <v>0.01</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="H51" s="11" t="n">
-        <v>0.0201</v>
+        <v>0.0175</v>
       </c>
       <c r="I51" s="9" t="inlineStr">
         <is>
@@ -4307,10 +4301,10 @@
         </is>
       </c>
       <c r="J51" s="9" t="n">
-        <v>29.23</v>
+        <v>29.31</v>
       </c>
       <c r="K51" s="9" t="n">
-        <v>8.029999999999999</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="L51" s="9" t="n">
         <v>0.7</v>
@@ -4335,7 +4329,7 @@
       </c>
       <c r="Q51" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:12</t>
+          <t>2026-10-13 23:49</t>
         </is>
       </c>
     </row>
@@ -4351,7 +4345,7 @@
         </is>
       </c>
       <c r="C52" s="10" t="n">
-        <v>40.335</v>
+        <v>40.3</v>
       </c>
       <c r="D52" s="10" t="n">
         <v>43.79</v>
@@ -4360,13 +4354,13 @@
         <v>26.73</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>-0.0004</v>
+        <v>-0.0011</v>
       </c>
       <c r="G52" s="11" t="n">
-        <v>-0.0008</v>
+        <v>-0.0023</v>
       </c>
       <c r="H52" s="11" t="n">
-        <v>-0.0017</v>
+        <v>-0.0046</v>
       </c>
       <c r="I52" s="9" t="inlineStr">
         <is>
@@ -4374,15 +4368,13 @@
         </is>
       </c>
       <c r="J52" s="9" t="n">
-        <v>25.53</v>
+        <v>25.51</v>
       </c>
       <c r="K52" s="9" t="n">
-        <v>7.11</v>
-      </c>
-      <c r="L52" s="9" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
+        <v>7.12</v>
+      </c>
+      <c r="L52" s="9" t="n">
+        <v>7.13</v>
       </c>
       <c r="M52" s="9" t="n">
         <v>0.59</v>
@@ -4404,7 +4396,7 @@
       </c>
       <c r="Q52" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:12</t>
+          <t>2026-10-13 23:49</t>
         </is>
       </c>
     </row>
@@ -4471,7 +4463,7 @@
       </c>
       <c r="Q53" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:12</t>
+          <t>2026-10-13 23:49</t>
         </is>
       </c>
     </row>
@@ -4487,7 +4479,7 @@
         </is>
       </c>
       <c r="C54" s="10" t="n">
-        <v>184.335</v>
+        <v>183.775</v>
       </c>
       <c r="D54" s="10" t="n">
         <v>222.47</v>
@@ -4496,13 +4488,13 @@
         <v>90</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>0.0014</v>
+        <v>0.0013</v>
       </c>
       <c r="G54" s="11" t="n">
-        <v>0.0029</v>
+        <v>0.0025</v>
       </c>
       <c r="H54" s="11" t="n">
-        <v>0.0058</v>
+        <v>0.0051</v>
       </c>
       <c r="I54" s="9" t="inlineStr">
         <is>
@@ -4510,13 +4502,13 @@
         </is>
       </c>
       <c r="J54" s="9" t="n">
-        <v>19.42</v>
+        <v>19.18</v>
       </c>
       <c r="K54" s="9" t="n">
-        <v>4.17</v>
+        <v>4.13</v>
       </c>
       <c r="L54" s="9" t="n">
-        <v>5.6</v>
+        <v>5.58</v>
       </c>
       <c r="M54" s="9" t="n">
         <v>0.67</v>
@@ -4538,7 +4530,7 @@
       </c>
       <c r="Q54" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:12</t>
+          <t>2026-10-13 23:49</t>
         </is>
       </c>
     </row>
@@ -4554,7 +4546,7 @@
         </is>
       </c>
       <c r="C55" s="10" t="n">
-        <v>2.365</v>
+        <v>2.57</v>
       </c>
       <c r="D55" s="10" t="n">
         <v>16.07</v>
@@ -4563,27 +4555,27 @@
         <v>1.97</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>0.321</v>
+        <v>0.2755</v>
       </c>
       <c r="G55" s="11" t="n">
-        <v>0.642</v>
+        <v>0.5508999999999999</v>
       </c>
       <c r="H55" s="11" t="n">
-        <v>1.284</v>
+        <v>1.1018</v>
       </c>
       <c r="I55" s="9" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J55" s="9" t="n">
-        <v>18.19</v>
+        <v>19.77</v>
       </c>
       <c r="K55" s="9" t="n">
-        <v>0.58</v>
+        <v>0.63</v>
       </c>
       <c r="L55" s="9" t="n">
-        <v>0.52</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="M55" s="9" t="n">
         <v>5.76</v>
@@ -4605,7 +4597,7 @@
       </c>
       <c r="Q55" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:12</t>
+          <t>2026-10-13 23:49</t>
         </is>
       </c>
     </row>
@@ -4621,22 +4613,22 @@
         </is>
       </c>
       <c r="C56" s="10" t="n">
-        <v>7.93</v>
+        <v>7.64</v>
       </c>
       <c r="D56" s="10" t="n">
         <v>13.48</v>
       </c>
       <c r="E56" s="10" t="n">
-        <v>7.8</v>
+        <v>7.51</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>0.2972</v>
+        <v>0.318</v>
       </c>
       <c r="G56" s="11" t="n">
-        <v>0.5945</v>
+        <v>0.636</v>
       </c>
       <c r="H56" s="11" t="n">
-        <v>1.1889</v>
+        <v>1.272</v>
       </c>
       <c r="I56" s="9" t="inlineStr">
         <is>
@@ -4644,13 +4636,13 @@
         </is>
       </c>
       <c r="J56" s="9" t="n">
-        <v>11.84</v>
+        <v>11.94</v>
       </c>
       <c r="K56" s="9" t="n">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="L56" s="9" t="n">
-        <v>4.26</v>
+        <v>4.1</v>
       </c>
       <c r="M56" s="9" t="n">
         <v>0.71</v>
@@ -4672,7 +4664,7 @@
       </c>
       <c r="Q56" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:12</t>
+          <t>2026-10-13 23:49</t>
         </is>
       </c>
     </row>
@@ -4688,22 +4680,22 @@
         </is>
       </c>
       <c r="C57" s="10" t="n">
-        <v>2.655</v>
+        <v>2.65</v>
       </c>
       <c r="D57" s="10" t="n">
-        <v>2.93</v>
+        <v>2.895</v>
       </c>
       <c r="E57" s="10" t="n">
         <v>2.14</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>0.0351</v>
+        <v>0.0357</v>
       </c>
       <c r="G57" s="11" t="n">
-        <v>0.0702</v>
+        <v>0.0713</v>
       </c>
       <c r="H57" s="11" t="n">
-        <v>0.1405</v>
+        <v>0.1426</v>
       </c>
       <c r="I57" s="9" t="inlineStr">
         <is>
@@ -4711,7 +4703,7 @@
         </is>
       </c>
       <c r="J57" s="9" t="n">
-        <v>66.38</v>
+        <v>66.25</v>
       </c>
       <c r="K57" s="9" t="n">
         <v>1.97</v>
@@ -4739,7 +4731,7 @@
       </c>
       <c r="Q57" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:12</t>
+          <t>2026-10-13 23:49</t>
         </is>
       </c>
     </row>
@@ -4814,7 +4806,7 @@
       </c>
       <c r="Q58" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:12</t>
+          <t>2026-10-13 23:49</t>
         </is>
       </c>
     </row>
@@ -4830,22 +4822,22 @@
         </is>
       </c>
       <c r="C59" s="10" t="n">
-        <v>21.9</v>
+        <v>21.22</v>
       </c>
       <c r="D59" s="10" t="n">
         <v>24.58</v>
       </c>
       <c r="E59" s="10" t="n">
-        <v>14.37</v>
+        <v>14.49</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>-0.014</v>
+        <v>-0.0064</v>
       </c>
       <c r="G59" s="11" t="n">
-        <v>-0.0279</v>
+        <v>-0.0128</v>
       </c>
       <c r="H59" s="11" t="n">
-        <v>-0.0558</v>
+        <v>-0.0256</v>
       </c>
       <c r="I59" s="9" t="inlineStr">
         <is>
@@ -4853,13 +4845,13 @@
         </is>
       </c>
       <c r="J59" s="9" t="n">
-        <v>15.36</v>
+        <v>14.88</v>
       </c>
       <c r="K59" s="9" t="n">
-        <v>4.54</v>
+        <v>4.4</v>
       </c>
       <c r="L59" s="9" t="n">
-        <v>1.01</v>
+        <v>0.98</v>
       </c>
       <c r="M59" s="9" t="n">
         <v>2.45</v>
@@ -4881,7 +4873,7 @@
       </c>
       <c r="Q59" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:12</t>
+          <t>2026-10-13 23:49</t>
         </is>
       </c>
     </row>
@@ -4897,7 +4889,7 @@
         </is>
       </c>
       <c r="C60" s="10" t="n">
-        <v>6.935</v>
+        <v>6.87</v>
       </c>
       <c r="D60" s="10" t="n">
         <v>8.654999999999999</v>
@@ -4906,13 +4898,13 @@
         <v>6.25</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>0.0303</v>
+        <v>0.0329</v>
       </c>
       <c r="G60" s="11" t="n">
-        <v>0.0606</v>
+        <v>0.0659</v>
       </c>
       <c r="H60" s="11" t="n">
-        <v>0.1211</v>
+        <v>0.1317</v>
       </c>
       <c r="I60" s="9" t="inlineStr">
         <is>
@@ -4920,13 +4912,13 @@
         </is>
       </c>
       <c r="J60" s="9" t="n">
-        <v>21.02</v>
+        <v>20.82</v>
       </c>
       <c r="K60" s="9" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="L60" s="9" t="n">
-        <v>0.47</v>
+        <v>0.46</v>
       </c>
       <c r="M60" s="9" t="n">
         <v>0.66</v>
@@ -4948,7 +4940,7 @@
       </c>
       <c r="Q60" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:12</t>
+          <t>2026-10-13 23:49</t>
         </is>
       </c>
     </row>
@@ -4964,7 +4956,7 @@
         </is>
       </c>
       <c r="C61" s="10" t="n">
-        <v>3.99</v>
+        <v>3.935</v>
       </c>
       <c r="D61" s="10" t="n">
         <v>4.78</v>
@@ -4973,13 +4965,13 @@
         <v>3.67</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>0.0442</v>
+        <v>0.0483</v>
       </c>
       <c r="G61" s="11" t="n">
-        <v>0.08840000000000001</v>
+        <v>0.09669999999999999</v>
       </c>
       <c r="H61" s="11" t="n">
-        <v>0.1769</v>
+        <v>0.1933</v>
       </c>
       <c r="I61" s="9" t="inlineStr">
         <is>
@@ -4987,13 +4979,13 @@
         </is>
       </c>
       <c r="J61" s="9" t="n">
-        <v>12.87</v>
+        <v>12.69</v>
       </c>
       <c r="K61" s="9" t="n">
-        <v>14.83</v>
+        <v>14.63</v>
       </c>
       <c r="L61" s="9" t="n">
-        <v>8.75</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="M61" s="9" t="n">
         <v>1</v>
@@ -5015,7 +5007,7 @@
       </c>
       <c r="Q61" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:12</t>
+          <t>2026-10-13 23:49</t>
         </is>
       </c>
     </row>
@@ -5031,7 +5023,7 @@
         </is>
       </c>
       <c r="C62" s="10" t="n">
-        <v>5.635</v>
+        <v>5.675</v>
       </c>
       <c r="D62" s="10" t="n">
         <v>7.73</v>
@@ -5040,13 +5032,13 @@
         <v>5.3</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>0.0385</v>
+        <v>0.0364</v>
       </c>
       <c r="G62" s="11" t="n">
-        <v>0.0769</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="H62" s="11" t="n">
-        <v>0.1539</v>
+        <v>0.1457</v>
       </c>
       <c r="I62" s="9" t="inlineStr">
         <is>
@@ -5054,13 +5046,13 @@
         </is>
       </c>
       <c r="J62" s="9" t="n">
-        <v>10.25</v>
+        <v>10.32</v>
       </c>
       <c r="K62" s="9" t="n">
         <v>0.61</v>
       </c>
       <c r="L62" s="9" t="n">
-        <v>4.54</v>
+        <v>4.58</v>
       </c>
       <c r="M62" s="9" t="n">
         <v>0.47</v>
@@ -5082,7 +5074,7 @@
       </c>
       <c r="Q62" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:12</t>
+          <t>2026-10-13 23:49</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5090,7 @@
         </is>
       </c>
       <c r="C63" s="10" t="n">
-        <v>6.565</v>
+        <v>6.48</v>
       </c>
       <c r="D63" s="10" t="n">
         <v>7.77</v>
@@ -5107,13 +5099,13 @@
         <v>4.96</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>0.0032</v>
+        <v>0.0065</v>
       </c>
       <c r="G63" s="11" t="n">
-        <v>0.0064</v>
+        <v>0.013</v>
       </c>
       <c r="H63" s="11" t="n">
-        <v>0.0128</v>
+        <v>0.026</v>
       </c>
       <c r="I63" s="9" t="inlineStr">
         <is>
@@ -5121,13 +5113,13 @@
         </is>
       </c>
       <c r="J63" s="9" t="n">
-        <v>26.26</v>
+        <v>25.92</v>
       </c>
       <c r="K63" s="9" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="L63" s="9" t="n">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="M63" s="9" t="n">
         <v>0.79</v>
@@ -5149,7 +5141,7 @@
       </c>
       <c r="Q63" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:12</t>
+          <t>2026-10-13 23:49</t>
         </is>
       </c>
     </row>
@@ -5165,7 +5157,7 @@
         </is>
       </c>
       <c r="C64" s="10" t="n">
-        <v>0.22</v>
+        <v>0.205</v>
       </c>
       <c r="D64" s="10" t="n">
         <v>1.02</v>
@@ -5174,13 +5166,13 @@
         <v>0.205</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>0.4697</v>
+        <v>0.5224</v>
       </c>
       <c r="G64" s="11" t="n">
-        <v>0.9394</v>
+        <v>1.0447</v>
       </c>
       <c r="H64" s="11" t="n">
-        <v>1.8788</v>
+        <v>2.0894</v>
       </c>
       <c r="I64" s="9" t="inlineStr">
         <is>
@@ -5188,13 +5180,13 @@
         </is>
       </c>
       <c r="J64" s="9" t="n">
-        <v>9.279999999999999</v>
+        <v>8.65</v>
       </c>
       <c r="K64" s="9" t="n">
-        <v>0.66</v>
+        <v>0.61</v>
       </c>
       <c r="L64" s="9" t="n">
-        <v>0.42</v>
+        <v>0.39</v>
       </c>
       <c r="M64" s="9" t="n">
         <v>0.6899999999999999</v>
@@ -5216,7 +5208,7 @@
       </c>
       <c r="Q64" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:12</t>
+          <t>2026-10-13 23:49</t>
         </is>
       </c>
     </row>
@@ -5232,7 +5224,7 @@
         </is>
       </c>
       <c r="C65" s="10" t="n">
-        <v>12.8</v>
+        <v>12.97</v>
       </c>
       <c r="D65" s="10" t="n">
         <v>17.75</v>
@@ -5241,13 +5233,13 @@
         <v>9.789999999999999</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>0.0169</v>
+        <v>0.0138</v>
       </c>
       <c r="G65" s="11" t="n">
-        <v>0.0338</v>
+        <v>0.0275</v>
       </c>
       <c r="H65" s="11" t="n">
-        <v>0.0677</v>
+        <v>0.055</v>
       </c>
       <c r="I65" s="9" t="inlineStr">
         <is>
@@ -5255,13 +5247,13 @@
         </is>
       </c>
       <c r="J65" s="9" t="n">
-        <v>17.53</v>
+        <v>18.27</v>
       </c>
       <c r="K65" s="9" t="n">
-        <v>4.46</v>
+        <v>4.52</v>
       </c>
       <c r="L65" s="9" t="n">
-        <v>4.71</v>
+        <v>4.77</v>
       </c>
       <c r="M65" s="9" t="n">
         <v>0.25</v>
@@ -5283,7 +5275,7 @@
       </c>
       <c r="Q65" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:12</t>
+          <t>2026-10-13 23:49</t>
         </is>
       </c>
     </row>
@@ -5299,7 +5291,7 @@
         </is>
       </c>
       <c r="C66" s="10" t="n">
-        <v>2.69</v>
+        <v>2.685</v>
       </c>
       <c r="D66" s="10" t="n">
         <v>3.44</v>
@@ -5308,13 +5300,13 @@
         <v>2.22</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>0.0404</v>
+        <v>0.041</v>
       </c>
       <c r="G66" s="11" t="n">
-        <v>0.0809</v>
+        <v>0.0819</v>
       </c>
       <c r="H66" s="11" t="n">
-        <v>0.1617</v>
+        <v>0.1639</v>
       </c>
       <c r="I66" s="9" t="inlineStr">
         <is>
@@ -5322,7 +5314,7 @@
         </is>
       </c>
       <c r="J66" s="9" t="n">
-        <v>16.81</v>
+        <v>16.78</v>
       </c>
       <c r="K66" s="9" t="n">
         <v>0.91</v>
@@ -5350,74 +5342,74 @@
       </c>
       <c r="Q66" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:12</t>
+          <t>2026-10-13 23:49</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="9" t="inlineStr">
+      <c r="A67" s="5" t="inlineStr">
         <is>
           <t>FLT</t>
         </is>
       </c>
-      <c r="B67" s="9" t="inlineStr">
+      <c r="B67" s="5" t="inlineStr">
         <is>
           <t>Flight Centre Travel Group Limited</t>
         </is>
       </c>
-      <c r="C67" s="10" t="n">
-        <v>10.245</v>
-      </c>
-      <c r="D67" s="10" t="n">
+      <c r="C67" s="6" t="n">
+        <v>10.17</v>
+      </c>
+      <c r="D67" s="6" t="n">
         <v>16.56</v>
       </c>
-      <c r="E67" s="10" t="n">
+      <c r="E67" s="6" t="n">
         <v>9.609999999999999</v>
       </c>
-      <c r="F67" s="11" t="n">
-        <v>0.0979</v>
-      </c>
-      <c r="G67" s="11" t="n">
-        <v>0.1957</v>
-      </c>
-      <c r="H67" s="11" t="n">
-        <v>0.3915</v>
-      </c>
-      <c r="I67" s="9" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="J67" s="9" t="n">
-        <v>14.64</v>
-      </c>
-      <c r="K67" s="9" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="L67" s="9" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="M67" s="9" t="n">
+      <c r="F67" s="7" t="n">
+        <v>0.1004</v>
+      </c>
+      <c r="G67" s="7" t="n">
+        <v>0.2009</v>
+      </c>
+      <c r="H67" s="7" t="n">
+        <v>0.4017</v>
+      </c>
+      <c r="I67" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J67" s="5" t="n">
+        <v>14.53</v>
+      </c>
+      <c r="K67" s="5" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="L67" s="5" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="M67" s="5" t="n">
         <v>1.12</v>
       </c>
-      <c r="N67" s="12" t="inlineStr">
+      <c r="N67" s="8" t="inlineStr">
         <is>
           <t>2026: $2,854.9M | 2025: $2,783.9M | 2024: $2,710.7M | 2023: $2,280.8M</t>
         </is>
       </c>
-      <c r="O67" s="12" t="inlineStr">
+      <c r="O67" s="8" t="inlineStr">
         <is>
           <t>2026: $149.2M | 2025: $109.5M | 2024: $139.6M | 2023: $47.5M</t>
         </is>
       </c>
-      <c r="P67" s="12" t="inlineStr">
+      <c r="P67" s="8" t="inlineStr">
         <is>
           <t>Flight Centre Travel Group Limited engages in leisure travel retailing activities in Australia, New Zealand, the Americas, Europe, the Middle East, Africa, Asia, and internationally. The company is involved in the operation of leisure travel under the Aunt Betty, BYOjet, Cruiseabout, Envoyage, Flight Centre, Iglu.com, ignite, Laurier Du Vallon, Luxury Travel Collection, Scott Dunn, Travel, Trav...</t>
         </is>
       </c>
-      <c r="Q67" s="9" t="inlineStr">
-        <is>
-          <t>2026-10-13 02:12</t>
+      <c r="Q67" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-13 23:49</t>
         </is>
       </c>
     </row>
@@ -5433,7 +5425,7 @@
         </is>
       </c>
       <c r="C68" s="10" t="n">
-        <v>15.44</v>
+        <v>15.375</v>
       </c>
       <c r="D68" s="10" t="n">
         <v>23.38</v>
@@ -5442,13 +5434,13 @@
         <v>15.335</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>0.0195</v>
+        <v>0.0192</v>
       </c>
       <c r="G68" s="11" t="n">
-        <v>0.0391</v>
+        <v>0.0384</v>
       </c>
       <c r="H68" s="11" t="n">
-        <v>0.07820000000000001</v>
+        <v>0.07679999999999999</v>
       </c>
       <c r="I68" s="9" t="inlineStr">
         <is>
@@ -5456,13 +5448,13 @@
         </is>
       </c>
       <c r="J68" s="9" t="n">
-        <v>11.27</v>
+        <v>11.56</v>
       </c>
       <c r="K68" s="9" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="L68" s="9" t="n">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="M68" s="9" t="n">
         <v>0.29</v>
@@ -5484,7 +5476,7 @@
       </c>
       <c r="Q68" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:12</t>
+          <t>2026-10-13 23:49</t>
         </is>
       </c>
     </row>
@@ -5500,22 +5492,22 @@
         </is>
       </c>
       <c r="C69" s="10" t="n">
-        <v>39.22</v>
+        <v>38.99</v>
       </c>
       <c r="D69" s="10" t="n">
-        <v>39.52</v>
+        <v>39.3</v>
       </c>
       <c r="E69" s="10" t="n">
         <v>26.51</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>-0.0152</v>
+        <v>-0.0136</v>
       </c>
       <c r="G69" s="11" t="n">
-        <v>-0.0304</v>
+        <v>-0.0271</v>
       </c>
       <c r="H69" s="11" t="n">
-        <v>-0.0607</v>
+        <v>-0.0542</v>
       </c>
       <c r="I69" s="9" t="inlineStr">
         <is>
@@ -5523,13 +5515,13 @@
         </is>
       </c>
       <c r="J69" s="9" t="n">
-        <v>56.03</v>
+        <v>54.92</v>
       </c>
       <c r="K69" s="9" t="n">
-        <v>13.55</v>
+        <v>13.47</v>
       </c>
       <c r="L69" s="9" t="n">
-        <v>9.99</v>
+        <v>9.94</v>
       </c>
       <c r="M69" s="9" t="n">
         <v>6.91</v>
@@ -5551,7 +5543,7 @@
       </c>
       <c r="Q69" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:12</t>
+          <t>2026-10-13 23:49</t>
         </is>
       </c>
     </row>
@@ -5567,7 +5559,7 @@
         </is>
       </c>
       <c r="C70" s="6" t="n">
-        <v>26.31</v>
+        <v>26.64</v>
       </c>
       <c r="D70" s="6" t="n">
         <v>34.78</v>
@@ -5576,13 +5568,13 @@
         <v>24.56</v>
       </c>
       <c r="F70" s="7" t="n">
-        <v>0.0776</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="G70" s="7" t="n">
-        <v>0.1552</v>
+        <v>0.144</v>
       </c>
       <c r="H70" s="7" t="n">
-        <v>0.3104</v>
+        <v>0.288</v>
       </c>
       <c r="I70" s="5" t="inlineStr">
         <is>
@@ -5590,13 +5582,13 @@
         </is>
       </c>
       <c r="J70" s="5" t="n">
-        <v>19.78</v>
+        <v>19.73</v>
       </c>
       <c r="K70" s="5" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="L70" s="5" t="n">
-        <v>13.32</v>
+        <v>13.48</v>
       </c>
       <c r="M70" s="5" t="n">
         <v>0.24</v>
@@ -5618,7 +5610,7 @@
       </c>
       <c r="Q70" s="5" t="inlineStr">
         <is>
-          <t>2026-10-13 02:12</t>
+          <t>2026-10-13 23:49</t>
         </is>
       </c>
     </row>
@@ -5634,22 +5626,22 @@
         </is>
       </c>
       <c r="C71" s="10" t="n">
-        <v>6.75</v>
+        <v>6.65</v>
       </c>
       <c r="D71" s="10" t="n">
-        <v>9.025</v>
+        <v>9</v>
       </c>
       <c r="E71" s="10" t="n">
         <v>4.69</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>0.0132</v>
+        <v>0.0171</v>
       </c>
       <c r="G71" s="11" t="n">
-        <v>0.0264</v>
+        <v>0.0343</v>
       </c>
       <c r="H71" s="11" t="n">
-        <v>0.0528</v>
+        <v>0.06859999999999999</v>
       </c>
       <c r="I71" s="9" t="inlineStr">
         <is>
@@ -5657,10 +5649,10 @@
         </is>
       </c>
       <c r="J71" s="9" t="n">
-        <v>21.67</v>
+        <v>21.35</v>
       </c>
       <c r="K71" s="9" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="L71" s="9" t="n">
         <v>0.21</v>
@@ -5685,7 +5677,7 @@
       </c>
       <c r="Q71" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:12</t>
+          <t>2026-10-13 23:49</t>
         </is>
       </c>
     </row>
@@ -5760,7 +5752,7 @@
       </c>
       <c r="Q72" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:12</t>
+          <t>2026-10-13 23:49</t>
         </is>
       </c>
     </row>
@@ -5776,7 +5768,7 @@
         </is>
       </c>
       <c r="C73" s="6" t="n">
-        <v>1.905</v>
+        <v>1.92</v>
       </c>
       <c r="D73" s="6" t="n">
         <v>2.68</v>
@@ -5785,13 +5777,13 @@
         <v>1.835</v>
       </c>
       <c r="F73" s="7" t="n">
-        <v>0.0965</v>
+        <v>0.09379999999999999</v>
       </c>
       <c r="G73" s="7" t="n">
-        <v>0.1929</v>
+        <v>0.1875</v>
       </c>
       <c r="H73" s="7" t="n">
-        <v>0.3858</v>
+        <v>0.375</v>
       </c>
       <c r="I73" s="5" t="inlineStr">
         <is>
@@ -5799,13 +5791,13 @@
         </is>
       </c>
       <c r="J73" s="5" t="n">
-        <v>15.88</v>
+        <v>16</v>
       </c>
       <c r="K73" s="5" t="n">
         <v>0.63</v>
       </c>
       <c r="L73" s="5" t="n">
-        <v>4.31</v>
+        <v>4.34</v>
       </c>
       <c r="M73" s="5" t="n">
         <v>0.84</v>
@@ -5827,7 +5819,7 @@
       </c>
       <c r="Q73" s="5" t="inlineStr">
         <is>
-          <t>2026-10-13 02:12</t>
+          <t>2026-10-13 23:49</t>
         </is>
       </c>
     </row>
@@ -5843,7 +5835,7 @@
         </is>
       </c>
       <c r="C74" s="10" t="n">
-        <v>4.535</v>
+        <v>4.54</v>
       </c>
       <c r="D74" s="10" t="n">
         <v>5.75</v>
@@ -5852,13 +5844,13 @@
         <v>4.35</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>0.0494</v>
+        <v>0.0491</v>
       </c>
       <c r="G74" s="11" t="n">
-        <v>0.0989</v>
+        <v>0.0982</v>
       </c>
       <c r="H74" s="11" t="n">
-        <v>0.1977</v>
+        <v>0.1964</v>
       </c>
       <c r="I74" s="9" t="inlineStr">
         <is>
@@ -5872,7 +5864,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="L74" s="9" t="n">
-        <v>8.75</v>
+        <v>8.76</v>
       </c>
       <c r="M74" s="9" t="n">
         <v>0.53</v>
@@ -5894,7 +5886,7 @@
       </c>
       <c r="Q74" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:12</t>
+          <t>2026-10-13 23:49</t>
         </is>
       </c>
     </row>
@@ -5969,7 +5961,7 @@
       </c>
       <c r="Q75" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:12</t>
+          <t>2026-10-13 23:49</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6000,7 @@
         </is>
       </c>
       <c r="J76" s="9" t="n">
-        <v>137.87</v>
+        <v>120.19</v>
       </c>
       <c r="K76" s="9" t="n">
         <v>1.59</v>
@@ -6036,7 +6028,7 @@
       </c>
       <c r="Q76" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:12</t>
+          <t>2026-10-13 23:49</t>
         </is>
       </c>
     </row>
@@ -6052,7 +6044,7 @@
         </is>
       </c>
       <c r="C77" s="6" t="n">
-        <v>65.66</v>
+        <v>64.59</v>
       </c>
       <c r="D77" s="6" t="n">
         <v>122.03</v>
@@ -6061,13 +6053,13 @@
         <v>61.79</v>
       </c>
       <c r="F77" s="7" t="n">
-        <v>0.1032</v>
+        <v>0.1091</v>
       </c>
       <c r="G77" s="7" t="n">
-        <v>0.2064</v>
+        <v>0.2181</v>
       </c>
       <c r="H77" s="7" t="n">
-        <v>0.4129</v>
+        <v>0.4363</v>
       </c>
       <c r="I77" s="5" t="inlineStr">
         <is>
@@ -6075,13 +6067,13 @@
         </is>
       </c>
       <c r="J77" s="5" t="n">
-        <v>44.97</v>
+        <v>44.85</v>
       </c>
       <c r="K77" s="5" t="n">
-        <v>9.68</v>
+        <v>9.52</v>
       </c>
       <c r="L77" s="5" t="n">
-        <v>10.81</v>
+        <v>10.63</v>
       </c>
       <c r="M77" s="5" t="n">
         <v>0.13</v>
@@ -6103,7 +6095,7 @@
       </c>
       <c r="Q77" s="5" t="inlineStr">
         <is>
-          <t>2026-10-13 02:12</t>
+          <t>2026-10-13 23:49</t>
         </is>
       </c>
     </row>
@@ -6119,7 +6111,7 @@
         </is>
       </c>
       <c r="C78" s="10" t="n">
-        <v>4.15</v>
+        <v>4.12</v>
       </c>
       <c r="D78" s="10" t="n">
         <v>7.7</v>
@@ -6128,13 +6120,13 @@
         <v>3.93</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>0.025</v>
+        <v>0.027</v>
       </c>
       <c r="G78" s="11" t="n">
-        <v>0.05</v>
+        <v>0.054</v>
       </c>
       <c r="H78" s="11" t="n">
-        <v>0.0999</v>
+        <v>0.1079</v>
       </c>
       <c r="I78" s="9" t="inlineStr">
         <is>
@@ -6142,13 +6134,13 @@
         </is>
       </c>
       <c r="J78" s="9" t="n">
-        <v>9.880000000000001</v>
+        <v>9.58</v>
       </c>
       <c r="K78" s="9" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="L78" s="9" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="M78" s="9" t="n">
         <v>0.52</v>
@@ -6170,7 +6162,7 @@
       </c>
       <c r="Q78" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:12</t>
+          <t>2026-10-13 23:49</t>
         </is>
       </c>
     </row>
@@ -6186,7 +6178,7 @@
         </is>
       </c>
       <c r="C79" s="10" t="n">
-        <v>8.289999999999999</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="D79" s="10" t="n">
         <v>8.720000000000001</v>
@@ -6195,13 +6187,13 @@
         <v>6.39</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>0.0003</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="G79" s="11" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0012</v>
       </c>
       <c r="H79" s="11" t="n">
-        <v>0.0012</v>
+        <v>0.0024</v>
       </c>
       <c r="I79" s="9" t="inlineStr">
         <is>
@@ -6209,7 +6201,7 @@
         </is>
       </c>
       <c r="J79" s="9" t="n">
-        <v>16.63</v>
+        <v>16.56</v>
       </c>
       <c r="K79" s="9" t="n">
         <v>2.67</v>
@@ -6237,7 +6229,7 @@
       </c>
       <c r="Q79" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:12</t>
+          <t>2026-10-13 23:49</t>
         </is>
       </c>
     </row>
@@ -6253,7 +6245,7 @@
         </is>
       </c>
       <c r="C80" s="10" t="n">
-        <v>2.205</v>
+        <v>2.19</v>
       </c>
       <c r="D80" s="10" t="n">
         <v>6.735</v>
@@ -6262,13 +6254,13 @@
         <v>1.49</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>0.0358</v>
+        <v>0.0378</v>
       </c>
       <c r="G80" s="11" t="n">
-        <v>0.0716</v>
+        <v>0.0756</v>
       </c>
       <c r="H80" s="11" t="n">
-        <v>0.1433</v>
+        <v>0.1511</v>
       </c>
       <c r="I80" s="9" t="inlineStr">
         <is>
@@ -6276,10 +6268,10 @@
         </is>
       </c>
       <c r="J80" s="9" t="n">
-        <v>55.12</v>
+        <v>54.75</v>
       </c>
       <c r="K80" s="9" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="L80" s="9" t="n">
         <v>0.77</v>
@@ -6304,7 +6296,7 @@
       </c>
       <c r="Q80" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:12</t>
+          <t>2026-10-13 23:49</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6371,7 @@
       </c>
       <c r="Q81" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:12</t>
+          <t>2026-10-13 23:49</t>
         </is>
       </c>
     </row>
@@ -6395,7 +6387,7 @@
         </is>
       </c>
       <c r="C82" s="10" t="n">
-        <v>5.655</v>
+        <v>5.645</v>
       </c>
       <c r="D82" s="10" t="n">
         <v>10.05</v>
@@ -6404,13 +6396,13 @@
         <v>4.87</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>0.0885</v>
+        <v>0.0851</v>
       </c>
       <c r="G82" s="11" t="n">
-        <v>0.177</v>
+        <v>0.1703</v>
       </c>
       <c r="H82" s="11" t="n">
-        <v>0.3541</v>
+        <v>0.3405</v>
       </c>
       <c r="I82" s="9" t="inlineStr">
         <is>
@@ -6418,13 +6410,13 @@
         </is>
       </c>
       <c r="J82" s="9" t="n">
-        <v>29.76</v>
+        <v>31.36</v>
       </c>
       <c r="K82" s="9" t="n">
         <v>1.91</v>
       </c>
       <c r="L82" s="9" t="n">
-        <v>9.25</v>
+        <v>9.23</v>
       </c>
       <c r="M82" s="9" t="n">
         <v>0.75</v>
@@ -6446,7 +6438,7 @@
       </c>
       <c r="Q82" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:12</t>
+          <t>2026-10-13 23:49</t>
         </is>
       </c>
     </row>
@@ -6462,7 +6454,7 @@
         </is>
       </c>
       <c r="C83" s="6" t="n">
-        <v>5.365</v>
+        <v>5.43</v>
       </c>
       <c r="D83" s="6" t="n">
         <v>9.48</v>
@@ -6471,13 +6463,13 @@
         <v>4.92</v>
       </c>
       <c r="F83" s="7" t="n">
-        <v>0.1209</v>
+        <v>0.1165</v>
       </c>
       <c r="G83" s="7" t="n">
-        <v>0.2418</v>
+        <v>0.233</v>
       </c>
       <c r="H83" s="7" t="n">
-        <v>0.4837</v>
+        <v>0.4659</v>
       </c>
       <c r="I83" s="5" t="inlineStr">
         <is>
@@ -6485,13 +6477,13 @@
         </is>
       </c>
       <c r="J83" s="5" t="n">
-        <v>-19.84</v>
+        <v>-17.72</v>
       </c>
       <c r="K83" s="5" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="L83" s="5" t="n">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="M83" s="5" t="n">
         <v>0.63</v>
@@ -6513,7 +6505,7 @@
       </c>
       <c r="Q83" s="5" t="inlineStr">
         <is>
-          <t>2026-10-13 02:12</t>
+          <t>2026-10-13 23:49</t>
         </is>
       </c>
     </row>
@@ -6529,7 +6521,7 @@
         </is>
       </c>
       <c r="C84" s="6" t="n">
-        <v>4.74</v>
+        <v>4.72</v>
       </c>
       <c r="D84" s="6" t="n">
         <v>5.875</v>
@@ -6538,13 +6530,13 @@
         <v>3.49</v>
       </c>
       <c r="F84" s="7" t="n">
-        <v>0.0179</v>
+        <v>0.0191</v>
       </c>
       <c r="G84" s="7" t="n">
-        <v>0.0359</v>
+        <v>0.0381</v>
       </c>
       <c r="H84" s="7" t="n">
-        <v>0.0717</v>
+        <v>0.07630000000000001</v>
       </c>
       <c r="I84" s="5" t="inlineStr">
         <is>
@@ -6552,13 +6544,13 @@
         </is>
       </c>
       <c r="J84" s="5" t="n">
-        <v>10.53</v>
+        <v>10.49</v>
       </c>
       <c r="K84" s="5" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="L84" s="5" t="n">
-        <v>3.35</v>
+        <v>3.34</v>
       </c>
       <c r="M84" s="5" t="n">
         <v>0.58</v>
@@ -6580,7 +6572,7 @@
       </c>
       <c r="Q84" s="5" t="inlineStr">
         <is>
-          <t>2026-10-13 02:12</t>
+          <t>2026-10-13 23:49</t>
         </is>
       </c>
     </row>
@@ -6596,7 +6588,7 @@
         </is>
       </c>
       <c r="C85" s="10" t="n">
-        <v>2.09</v>
+        <v>2.06</v>
       </c>
       <c r="D85" s="10" t="n">
         <v>2.69</v>
@@ -6605,13 +6597,13 @@
         <v>1.69</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>0.0206</v>
+        <v>0.0245</v>
       </c>
       <c r="G85" s="11" t="n">
-        <v>0.0412</v>
+        <v>0.0491</v>
       </c>
       <c r="H85" s="11" t="n">
-        <v>0.0824</v>
+        <v>0.0982</v>
       </c>
       <c r="I85" s="9" t="inlineStr">
         <is>
@@ -6619,10 +6611,10 @@
         </is>
       </c>
       <c r="J85" s="9" t="n">
-        <v>23.22</v>
+        <v>22.89</v>
       </c>
       <c r="K85" s="9" t="n">
-        <v>3.09</v>
+        <v>3.04</v>
       </c>
       <c r="L85" s="9" t="n">
         <v>0.24</v>
@@ -6647,7 +6639,7 @@
       </c>
       <c r="Q85" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:12</t>
+          <t>2026-10-13 23:49</t>
         </is>
       </c>
     </row>
@@ -6663,7 +6655,7 @@
         </is>
       </c>
       <c r="C86" s="10" t="n">
-        <v>3.485</v>
+        <v>3.52</v>
       </c>
       <c r="D86" s="10" t="n">
         <v>4.42</v>
@@ -6672,27 +6664,27 @@
         <v>3.155</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>0.0585</v>
+        <v>0.0554</v>
       </c>
       <c r="G86" s="11" t="n">
-        <v>0.117</v>
+        <v>0.1109</v>
       </c>
       <c r="H86" s="11" t="n">
-        <v>0.234</v>
+        <v>0.2217</v>
       </c>
       <c r="I86" s="9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="J86" s="9" t="n">
-        <v>11.24</v>
+        <v>11.35</v>
       </c>
       <c r="K86" s="9" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="L86" s="9" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="M86" s="9" t="n">
         <v>0.67</v>
@@ -6714,7 +6706,7 @@
       </c>
       <c r="Q86" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:12</t>
+          <t>2026-10-13 23:49</t>
         </is>
       </c>
     </row>
@@ -6789,7 +6781,7 @@
       </c>
       <c r="Q87" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:12</t>
+          <t>2026-10-13 23:49</t>
         </is>
       </c>
     </row>
@@ -6805,7 +6797,7 @@
         </is>
       </c>
       <c r="C88" s="6" t="n">
-        <v>5.525</v>
+        <v>5.48</v>
       </c>
       <c r="D88" s="6" t="n">
         <v>10.38</v>
@@ -6814,13 +6806,13 @@
         <v>5.04</v>
       </c>
       <c r="F88" s="7" t="n">
-        <v>0.1485</v>
+        <v>0.1517</v>
       </c>
       <c r="G88" s="7" t="n">
-        <v>0.2969</v>
+        <v>0.3035</v>
       </c>
       <c r="H88" s="7" t="n">
-        <v>0.5939</v>
+        <v>0.607</v>
       </c>
       <c r="I88" s="5" t="inlineStr">
         <is>
@@ -6828,13 +6820,13 @@
         </is>
       </c>
       <c r="J88" s="5" t="n">
-        <v>11.28</v>
+        <v>11.42</v>
       </c>
       <c r="K88" s="5" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="L88" s="5" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="M88" s="5" t="n">
         <v>0.41</v>
@@ -6856,7 +6848,7 @@
       </c>
       <c r="Q88" s="5" t="inlineStr">
         <is>
-          <t>2026-10-13 02:12</t>
+          <t>2026-10-13 23:49</t>
         </is>
       </c>
     </row>
@@ -6931,7 +6923,7 @@
       </c>
       <c r="Q89" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:12</t>
+          <t>2026-10-13 23:49</t>
         </is>
       </c>
     </row>
@@ -6947,22 +6939,22 @@
         </is>
       </c>
       <c r="C90" s="10" t="n">
-        <v>71.5</v>
+        <v>70.84</v>
       </c>
       <c r="D90" s="10" t="n">
-        <v>116.48</v>
+        <v>116.24</v>
       </c>
       <c r="E90" s="10" t="n">
         <v>64.18000000000001</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>0.018</v>
+        <v>0.0205</v>
       </c>
       <c r="G90" s="11" t="n">
-        <v>0.0361</v>
+        <v>0.0411</v>
       </c>
       <c r="H90" s="11" t="n">
-        <v>0.0722</v>
+        <v>0.0822</v>
       </c>
       <c r="I90" s="9" t="inlineStr">
         <is>
@@ -6970,13 +6962,13 @@
         </is>
       </c>
       <c r="J90" s="9" t="n">
-        <v>16</v>
+        <v>15.85</v>
       </c>
       <c r="K90" s="9" t="n">
-        <v>4.77</v>
+        <v>4.73</v>
       </c>
       <c r="L90" s="9" t="n">
-        <v>0.71</v>
+        <v>0.7</v>
       </c>
       <c r="M90" s="9" t="n">
         <v>0.43</v>
@@ -6998,7 +6990,7 @@
       </c>
       <c r="Q90" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:12</t>
+          <t>2026-10-13 23:49</t>
         </is>
       </c>
     </row>
@@ -7073,7 +7065,7 @@
       </c>
       <c r="Q91" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:12</t>
+          <t>2026-10-13 23:49</t>
         </is>
       </c>
     </row>
@@ -7089,7 +7081,7 @@
         </is>
       </c>
       <c r="C92" s="6" t="n">
-        <v>35.515</v>
+        <v>35.37</v>
       </c>
       <c r="D92" s="6" t="n">
         <v>44.12</v>
@@ -7098,13 +7090,13 @@
         <v>24.41</v>
       </c>
       <c r="F92" s="7" t="n">
-        <v>0.06469999999999999</v>
+        <v>0.0639</v>
       </c>
       <c r="G92" s="7" t="n">
-        <v>0.1294</v>
+        <v>0.1279</v>
       </c>
       <c r="H92" s="7" t="n">
-        <v>0.2587</v>
+        <v>0.2558</v>
       </c>
       <c r="I92" s="5" t="inlineStr">
         <is>
@@ -7112,13 +7104,13 @@
         </is>
       </c>
       <c r="J92" s="5" t="n">
-        <v>95.98999999999999</v>
+        <v>95.59</v>
       </c>
       <c r="K92" s="5" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="L92" s="5" t="n">
-        <v>3.81</v>
+        <v>3.8</v>
       </c>
       <c r="M92" s="5" t="n">
         <v>0.6899999999999999</v>
@@ -7140,7 +7132,7 @@
       </c>
       <c r="Q92" s="5" t="inlineStr">
         <is>
-          <t>2026-10-13 02:12</t>
+          <t>2026-10-13 23:49</t>
         </is>
       </c>
     </row>
@@ -7156,7 +7148,7 @@
         </is>
       </c>
       <c r="C93" s="6" t="n">
-        <v>3.905</v>
+        <v>3.87</v>
       </c>
       <c r="D93" s="6" t="n">
         <v>5.25</v>
@@ -7165,13 +7157,13 @@
         <v>3.68</v>
       </c>
       <c r="F93" s="7" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.0901</v>
       </c>
       <c r="G93" s="7" t="n">
-        <v>0.174</v>
+        <v>0.1801</v>
       </c>
       <c r="H93" s="7" t="n">
-        <v>0.3481</v>
+        <v>0.3603</v>
       </c>
       <c r="I93" s="5" t="inlineStr">
         <is>
@@ -7179,10 +7171,10 @@
         </is>
       </c>
       <c r="J93" s="5" t="n">
-        <v>16.98</v>
+        <v>16.83</v>
       </c>
       <c r="K93" s="5" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="L93" s="5" t="n">
         <v>0.44</v>
@@ -7207,7 +7199,7 @@
       </c>
       <c r="Q93" s="5" t="inlineStr">
         <is>
-          <t>2026-10-13 02:12</t>
+          <t>2026-10-13 23:49</t>
         </is>
       </c>
     </row>
@@ -7223,7 +7215,7 @@
         </is>
       </c>
       <c r="C94" s="10" t="n">
-        <v>2.425</v>
+        <v>2.385</v>
       </c>
       <c r="D94" s="10" t="n">
         <v>5.85</v>
@@ -7232,13 +7224,13 @@
         <v>2.36</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>0.1204</v>
+        <v>0.1266</v>
       </c>
       <c r="G94" s="11" t="n">
-        <v>0.2408</v>
+        <v>0.2532</v>
       </c>
       <c r="H94" s="11" t="n">
-        <v>0.4816</v>
+        <v>0.5064</v>
       </c>
       <c r="I94" s="9" t="inlineStr">
         <is>
@@ -7246,13 +7238,13 @@
         </is>
       </c>
       <c r="J94" s="9" t="n">
-        <v>9.789999999999999</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="K94" s="9" t="n">
         <v>0.42</v>
       </c>
       <c r="L94" s="9" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="M94" s="9" t="n">
         <v>0.97</v>
@@ -7274,7 +7266,7 @@
       </c>
       <c r="Q94" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:12</t>
+          <t>2026-10-13 23:49</t>
         </is>
       </c>
     </row>
@@ -7349,7 +7341,7 @@
       </c>
       <c r="Q95" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:12</t>
+          <t>2026-10-13 23:49</t>
         </is>
       </c>
     </row>
@@ -7365,22 +7357,22 @@
         </is>
       </c>
       <c r="C96" s="10" t="n">
-        <v>11.74</v>
+        <v>11.81</v>
       </c>
       <c r="D96" s="10" t="n">
         <v>22.37</v>
       </c>
       <c r="E96" s="10" t="n">
-        <v>11.68</v>
+        <v>11.62</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>0.1188</v>
+        <v>0.1184</v>
       </c>
       <c r="G96" s="11" t="n">
-        <v>0.2376</v>
+        <v>0.2367</v>
       </c>
       <c r="H96" s="11" t="n">
-        <v>0.4752</v>
+        <v>0.4735</v>
       </c>
       <c r="I96" s="9" t="inlineStr">
         <is>
@@ -7388,13 +7380,13 @@
         </is>
       </c>
       <c r="J96" s="9" t="n">
-        <v>53.36</v>
+        <v>56.24</v>
       </c>
       <c r="K96" s="9" t="n">
-        <v>3.39</v>
+        <v>3.41</v>
       </c>
       <c r="L96" s="9" t="n">
-        <v>12.08</v>
+        <v>12.15</v>
       </c>
       <c r="M96" s="9" t="n">
         <v>9.69</v>
@@ -7416,7 +7408,7 @@
       </c>
       <c r="Q96" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:12</t>
+          <t>2026-10-13 23:49</t>
         </is>
       </c>
     </row>
@@ -7432,7 +7424,7 @@
         </is>
       </c>
       <c r="C97" s="10" t="n">
-        <v>8.565</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="D97" s="10" t="n">
         <v>11.55</v>
@@ -7441,13 +7433,13 @@
         <v>7.96</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>0.012</v>
+        <v>0.0131</v>
       </c>
       <c r="G97" s="11" t="n">
-        <v>0.024</v>
+        <v>0.0261</v>
       </c>
       <c r="H97" s="11" t="n">
-        <v>0.048</v>
+        <v>0.0523</v>
       </c>
       <c r="I97" s="9" t="inlineStr">
         <is>
@@ -7455,13 +7447,13 @@
         </is>
       </c>
       <c r="J97" s="9" t="n">
-        <v>17.13</v>
+        <v>17.06</v>
       </c>
       <c r="K97" s="9" t="n">
         <v>1.5</v>
       </c>
       <c r="L97" s="9" t="n">
-        <v>12.73</v>
+        <v>12.68</v>
       </c>
       <c r="M97" s="9" t="n">
         <v>0.19</v>
@@ -7483,7 +7475,7 @@
       </c>
       <c r="Q97" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:12</t>
+          <t>2026-10-13 23:49</t>
         </is>
       </c>
     </row>
@@ -7499,7 +7491,7 @@
         </is>
       </c>
       <c r="C98" s="6" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="D98" s="6" t="n">
         <v>2.46</v>
@@ -7508,13 +7500,13 @@
         <v>1.607</v>
       </c>
       <c r="F98" s="7" t="n">
-        <v>0.0403</v>
+        <v>0.0372</v>
       </c>
       <c r="G98" s="7" t="n">
-        <v>0.08069999999999999</v>
+        <v>0.07439999999999999</v>
       </c>
       <c r="H98" s="7" t="n">
-        <v>0.1613</v>
+        <v>0.1487</v>
       </c>
       <c r="I98" s="5" t="inlineStr">
         <is>
@@ -7522,13 +7514,13 @@
         </is>
       </c>
       <c r="J98" s="5" t="n">
-        <v>10.71</v>
+        <v>10.82</v>
       </c>
       <c r="K98" s="5" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="L98" s="5" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="M98" s="5" t="n">
         <v>0.42</v>
@@ -7550,7 +7542,7 @@
       </c>
       <c r="Q98" s="5" t="inlineStr">
         <is>
-          <t>2026-10-13 02:12</t>
+          <t>2026-10-13 23:49</t>
         </is>
       </c>
     </row>
@@ -7566,7 +7558,7 @@
         </is>
       </c>
       <c r="C99" s="10" t="n">
-        <v>46.78</v>
+        <v>46.975</v>
       </c>
       <c r="D99" s="10" t="n">
         <v>74.94</v>
@@ -7575,13 +7567,13 @@
         <v>40.5</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>0.0959</v>
+        <v>0.0854</v>
       </c>
       <c r="G99" s="11" t="n">
-        <v>0.1918</v>
+        <v>0.1707</v>
       </c>
       <c r="H99" s="11" t="n">
-        <v>0.3837</v>
+        <v>0.3414</v>
       </c>
       <c r="I99" s="9" t="inlineStr">
         <is>
@@ -7589,10 +7581,10 @@
         </is>
       </c>
       <c r="J99" s="9" t="n">
-        <v>8.76</v>
+        <v>9.43</v>
       </c>
       <c r="K99" s="9" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="L99" s="9" t="n">
         <v>1.44</v>
@@ -7617,7 +7609,7 @@
       </c>
       <c r="Q99" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:12</t>
+          <t>2026-10-13 23:49</t>
         </is>
       </c>
     </row>
@@ -7633,7 +7625,7 @@
         </is>
       </c>
       <c r="C100" s="10" t="n">
-        <v>4.65</v>
+        <v>4.63</v>
       </c>
       <c r="D100" s="10" t="n">
         <v>5.31</v>
@@ -7642,13 +7634,13 @@
         <v>4.06</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>0.0182</v>
+        <v>0.0194</v>
       </c>
       <c r="G100" s="11" t="n">
-        <v>0.0364</v>
+        <v>0.0388</v>
       </c>
       <c r="H100" s="11" t="n">
-        <v>0.07290000000000001</v>
+        <v>0.0775</v>
       </c>
       <c r="I100" s="9" t="inlineStr">
         <is>
@@ -7656,13 +7648,13 @@
         </is>
       </c>
       <c r="J100" s="9" t="n">
-        <v>20.22</v>
+        <v>20.13</v>
       </c>
       <c r="K100" s="9" t="n">
-        <v>5.27</v>
+        <v>5.24</v>
       </c>
       <c r="L100" s="9" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="M100" s="9" t="n">
         <v>0.11</v>
@@ -7684,7 +7676,7 @@
       </c>
       <c r="Q100" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:12</t>
+          <t>2026-10-13 23:49</t>
         </is>
       </c>
     </row>
@@ -7700,7 +7692,7 @@
         </is>
       </c>
       <c r="C101" s="10" t="n">
-        <v>252.16</v>
+        <v>247.96</v>
       </c>
       <c r="D101" s="10" t="n">
         <v>267.905</v>
@@ -7709,33 +7701,27 @@
         <v>187.31</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v/>
+        <v>-0.008</v>
       </c>
       <c r="G101" s="11" t="n">
-        <v/>
+        <v>-0.016</v>
       </c>
       <c r="H101" s="11" t="n">
-        <v/>
+        <v>-0.032</v>
       </c>
       <c r="I101" s="9" t="inlineStr">
         <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="J101" s="9" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="K101" s="9" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="L101" s="9" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J101" s="9" t="n">
+        <v>25.54</v>
+      </c>
+      <c r="K101" s="9" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="L101" s="9" t="n">
+        <v>5.31</v>
       </c>
       <c r="M101" s="9" t="inlineStr">
         <is>
@@ -7754,12 +7740,12 @@
       </c>
       <c r="P101" s="12" t="inlineStr">
         <is>
-          <t>No business summary available.</t>
+          <t>Macquarie Group Limited provides diversified financial services in Australia, New Zealand the Americas, Europe, the Middle East, Africa, and Asia. It operates through four segments: Macquarie Asset Management (MAM); Banking and Financial Services (BFS); Commodities and Global Markets (CGM); and Macquarie Capital. The MAM segment provides investment solutions to clients across various capabiliti...</t>
         </is>
       </c>
       <c r="Q101" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:12</t>
+          <t>2026-10-13 23:49</t>
         </is>
       </c>
     </row>
@@ -7803,10 +7789,8 @@
       <c r="K102" s="9" t="n">
         <v>1.98</v>
       </c>
-      <c r="L102" s="9" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
+      <c r="L102" s="9" t="n">
+        <v>0.2</v>
       </c>
       <c r="M102" s="9" t="n">
         <v>1.1</v>
@@ -7828,7 +7812,7 @@
       </c>
       <c r="Q102" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:12</t>
+          <t>2026-10-13 23:50</t>
         </is>
       </c>
     </row>
@@ -7844,7 +7828,7 @@
         </is>
       </c>
       <c r="C103" s="10" t="n">
-        <v>39.01</v>
+        <v>38.72</v>
       </c>
       <c r="D103" s="10" t="n">
         <v>49.45</v>
@@ -7853,13 +7837,13 @@
         <v>35.48</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>-0.0035</v>
+        <v>-0.0017</v>
       </c>
       <c r="G103" s="11" t="n">
-        <v>-0.007</v>
+        <v>-0.0033</v>
       </c>
       <c r="H103" s="11" t="n">
-        <v>-0.0141</v>
+        <v>-0.0067</v>
       </c>
       <c r="I103" s="9" t="inlineStr">
         <is>
@@ -7867,15 +7851,13 @@
         </is>
       </c>
       <c r="J103" s="9" t="n">
-        <v>19.5</v>
+        <v>18.98</v>
       </c>
       <c r="K103" s="9" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="L103" s="9" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
+        <v>1.96</v>
+      </c>
+      <c r="L103" s="9" t="n">
+        <v>5.68</v>
       </c>
       <c r="M103" s="9" t="inlineStr">
         <is>
@@ -7899,7 +7881,7 @@
       </c>
       <c r="Q103" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:12</t>
+          <t>2026-10-13 23:50</t>
         </is>
       </c>
     </row>
@@ -7915,7 +7897,7 @@
         </is>
       </c>
       <c r="C104" s="6" t="n">
-        <v>2.845</v>
+        <v>2.77</v>
       </c>
       <c r="D104" s="6" t="n">
         <v>4.76</v>
@@ -7924,13 +7906,13 @@
         <v>2.64</v>
       </c>
       <c r="F104" s="7" t="n">
-        <v>0.0911</v>
+        <v>0.1003</v>
       </c>
       <c r="G104" s="7" t="n">
-        <v>0.1821</v>
+        <v>0.2006</v>
       </c>
       <c r="H104" s="7" t="n">
-        <v>0.3643</v>
+        <v>0.4012</v>
       </c>
       <c r="I104" s="5" t="inlineStr">
         <is>
@@ -7938,13 +7920,13 @@
         </is>
       </c>
       <c r="J104" s="5" t="n">
-        <v>47.42</v>
+        <v>46.17</v>
       </c>
       <c r="K104" s="5" t="n">
-        <v>3.91</v>
+        <v>3.8</v>
       </c>
       <c r="L104" s="5" t="n">
-        <v>4.17</v>
+        <v>4.06</v>
       </c>
       <c r="M104" s="5" t="n">
         <v>0.11</v>
@@ -7966,7 +7948,7 @@
       </c>
       <c r="Q104" s="5" t="inlineStr">
         <is>
-          <t>2026-10-13 02:12</t>
+          <t>2026-10-13 23:50</t>
         </is>
       </c>
     </row>
@@ -7982,22 +7964,22 @@
         </is>
       </c>
       <c r="C105" s="10" t="n">
-        <v>0.647</v>
+        <v>0.64</v>
       </c>
       <c r="D105" s="10" t="n">
         <v>1.25</v>
       </c>
       <c r="E105" s="10" t="n">
-        <v>0.645</v>
+        <v>0.64</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>0.2304</v>
+        <v>0.2357</v>
       </c>
       <c r="G105" s="11" t="n">
-        <v>0.4608</v>
+        <v>0.4714</v>
       </c>
       <c r="H105" s="11" t="n">
-        <v>0.9217</v>
+        <v>0.9427</v>
       </c>
       <c r="I105" s="9" t="inlineStr">
         <is>
@@ -8005,13 +7987,13 @@
         </is>
       </c>
       <c r="J105" s="9" t="n">
-        <v>6.67</v>
+        <v>6.6</v>
       </c>
       <c r="K105" s="9" t="n">
-        <v>0.87</v>
+        <v>0.86</v>
       </c>
       <c r="L105" s="9" t="n">
-        <v>0.47</v>
+        <v>0.46</v>
       </c>
       <c r="M105" s="9" t="n">
         <v>1.41</v>
@@ -8033,7 +8015,7 @@
       </c>
       <c r="Q105" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:12</t>
+          <t>2026-10-13 23:50</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8031,7 @@
         </is>
       </c>
       <c r="C106" s="10" t="n">
-        <v>6.55</v>
+        <v>6.52</v>
       </c>
       <c r="D106" s="10" t="n">
         <v>7.73</v>
@@ -8058,13 +8040,13 @@
         <v>5.79</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>0.0322</v>
+        <v>0.0335</v>
       </c>
       <c r="G106" s="11" t="n">
-        <v>0.0645</v>
+        <v>0.06710000000000001</v>
       </c>
       <c r="H106" s="11" t="n">
-        <v>0.1289</v>
+        <v>0.1341</v>
       </c>
       <c r="I106" s="9" t="inlineStr">
         <is>
@@ -8072,10 +8054,10 @@
         </is>
       </c>
       <c r="J106" s="9" t="n">
-        <v>17.24</v>
+        <v>17.16</v>
       </c>
       <c r="K106" s="9" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="L106" s="9" t="n">
         <v>0.84</v>
@@ -8100,7 +8082,7 @@
       </c>
       <c r="Q106" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:12</t>
+          <t>2026-10-13 23:50</t>
         </is>
       </c>
     </row>
@@ -8175,7 +8157,7 @@
       </c>
       <c r="Q107" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:12</t>
+          <t>2026-10-13 23:50</t>
         </is>
       </c>
     </row>
@@ -8191,7 +8173,7 @@
         </is>
       </c>
       <c r="C108" s="10" t="n">
-        <v>24.675</v>
+        <v>25.12</v>
       </c>
       <c r="D108" s="10" t="n">
         <v>31.96</v>
@@ -8200,13 +8182,13 @@
         <v>17.07</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>0.0128</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="G108" s="11" t="n">
-        <v>0.0256</v>
+        <v>0.0163</v>
       </c>
       <c r="H108" s="11" t="n">
-        <v>0.0512</v>
+        <v>0.0326</v>
       </c>
       <c r="I108" s="9" t="inlineStr">
         <is>
@@ -8214,13 +8196,13 @@
         </is>
       </c>
       <c r="J108" s="9" t="n">
-        <v>21.27</v>
+        <v>21.66</v>
       </c>
       <c r="K108" s="9" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="L108" s="9" t="n">
-        <v>4.61</v>
+        <v>4.7</v>
       </c>
       <c r="M108" s="9" t="n">
         <v>0.11</v>
@@ -8242,7 +8224,7 @@
       </c>
       <c r="Q108" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:12</t>
+          <t>2026-10-13 23:50</t>
         </is>
       </c>
     </row>
@@ -8258,7 +8240,7 @@
         </is>
       </c>
       <c r="C109" s="6" t="n">
-        <v>3.135</v>
+        <v>3.085</v>
       </c>
       <c r="D109" s="6" t="n">
         <v>3.37</v>
@@ -8267,13 +8249,13 @@
         <v>1.79</v>
       </c>
       <c r="F109" s="7" t="n">
-        <v>0.0335</v>
+        <v>0.0381</v>
       </c>
       <c r="G109" s="7" t="n">
-        <v>0.06710000000000001</v>
+        <v>0.07630000000000001</v>
       </c>
       <c r="H109" s="7" t="n">
-        <v>0.1341</v>
+        <v>0.1525</v>
       </c>
       <c r="I109" s="5" t="inlineStr">
         <is>
@@ -8281,15 +8263,13 @@
         </is>
       </c>
       <c r="J109" s="5" t="n">
-        <v>17.97</v>
+        <v>17.68</v>
       </c>
       <c r="K109" s="5" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="L109" s="5" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
+        <v>0.65</v>
+      </c>
+      <c r="L109" s="5" t="n">
+        <v>0.35</v>
       </c>
       <c r="M109" s="5" t="n">
         <v>0.77</v>
@@ -8311,7 +8291,7 @@
       </c>
       <c r="Q109" s="5" t="inlineStr">
         <is>
-          <t>2026-10-13 02:12</t>
+          <t>2026-10-13 23:50</t>
         </is>
       </c>
     </row>
@@ -8327,7 +8307,7 @@
         </is>
       </c>
       <c r="C110" s="6" t="n">
-        <v>16.99</v>
+        <v>16.8</v>
       </c>
       <c r="D110" s="6" t="n">
         <v>33.62</v>
@@ -8336,13 +8316,13 @@
         <v>16.35</v>
       </c>
       <c r="F110" s="7" t="n">
-        <v>0.1221</v>
+        <v>0.1263</v>
       </c>
       <c r="G110" s="7" t="n">
-        <v>0.2443</v>
+        <v>0.2527</v>
       </c>
       <c r="H110" s="7" t="n">
-        <v>0.4886</v>
+        <v>0.5054</v>
       </c>
       <c r="I110" s="5" t="inlineStr">
         <is>
@@ -8350,13 +8330,13 @@
         </is>
       </c>
       <c r="J110" s="5" t="n">
-        <v>67.95999999999999</v>
+        <v>70</v>
       </c>
       <c r="K110" s="5" t="n">
-        <v>25.74</v>
+        <v>25.45</v>
       </c>
       <c r="L110" s="5" t="n">
-        <v>10.7</v>
+        <v>10.59</v>
       </c>
       <c r="M110" s="5" t="n">
         <v>0.43</v>
@@ -8378,7 +8358,7 @@
       </c>
       <c r="Q110" s="5" t="inlineStr">
         <is>
-          <t>2026-10-13 02:12</t>
+          <t>2026-10-13 23:50</t>
         </is>
       </c>
     </row>
@@ -8394,7 +8374,7 @@
         </is>
       </c>
       <c r="C111" s="10" t="n">
-        <v>46.71</v>
+        <v>46.63</v>
       </c>
       <c r="D111" s="10" t="n">
         <v>49.67</v>
@@ -8403,13 +8383,13 @@
         <v>36.01</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>0.0477</v>
+        <v>0.0471</v>
       </c>
       <c r="G111" s="11" t="n">
-        <v>0.0955</v>
+        <v>0.09429999999999999</v>
       </c>
       <c r="H111" s="11" t="n">
-        <v>0.1909</v>
+        <v>0.1886</v>
       </c>
       <c r="I111" s="9" t="inlineStr">
         <is>
@@ -8417,13 +8397,13 @@
         </is>
       </c>
       <c r="J111" s="9" t="n">
-        <v>30.73</v>
+        <v>30.08</v>
       </c>
       <c r="K111" s="9" t="n">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="L111" s="9" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="M111" s="9" t="n">
         <v>0.32</v>
@@ -8445,7 +8425,7 @@
       </c>
       <c r="Q111" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:12</t>
+          <t>2026-10-13 23:50</t>
         </is>
       </c>
     </row>
@@ -8461,22 +8441,22 @@
         </is>
       </c>
       <c r="C112" s="6" t="n">
-        <v>9.539999999999999</v>
+        <v>9.59</v>
       </c>
       <c r="D112" s="6" t="n">
         <v>16.78</v>
       </c>
       <c r="E112" s="6" t="n">
-        <v>9.52</v>
+        <v>9.44</v>
       </c>
       <c r="F112" s="7" t="n">
-        <v>0.2787</v>
+        <v>0.26</v>
       </c>
       <c r="G112" s="7" t="n">
-        <v>0.5574</v>
+        <v>0.52</v>
       </c>
       <c r="H112" s="7" t="n">
-        <v>1.1148</v>
+        <v>1.04</v>
       </c>
       <c r="I112" s="5" t="inlineStr">
         <is>
@@ -8484,13 +8464,13 @@
         </is>
       </c>
       <c r="J112" s="5" t="n">
-        <v>79.5</v>
+        <v>79.92</v>
       </c>
       <c r="K112" s="5" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="L112" s="5" t="n">
-        <v>14.61</v>
+        <v>14.69</v>
       </c>
       <c r="M112" s="5" t="n">
         <v>0.55</v>
@@ -8512,7 +8492,7 @@
       </c>
       <c r="Q112" s="5" t="inlineStr">
         <is>
-          <t>2026-10-13 02:12</t>
+          <t>2026-10-13 23:50</t>
         </is>
       </c>
     </row>
@@ -8528,7 +8508,7 @@
         </is>
       </c>
       <c r="C113" s="10" t="n">
-        <v>1.38</v>
+        <v>1.335</v>
       </c>
       <c r="D113" s="10" t="n">
         <v>2.43</v>
@@ -8537,13 +8517,13 @@
         <v>1.212</v>
       </c>
       <c r="F113" s="11" t="n">
-        <v>0.0522</v>
+        <v>0.0624</v>
       </c>
       <c r="G113" s="11" t="n">
-        <v>0.1044</v>
+        <v>0.1247</v>
       </c>
       <c r="H113" s="11" t="n">
-        <v>0.2087</v>
+        <v>0.2495</v>
       </c>
       <c r="I113" s="9" t="inlineStr">
         <is>
@@ -8551,13 +8531,13 @@
         </is>
       </c>
       <c r="J113" s="9" t="n">
-        <v>11.89</v>
+        <v>11.5</v>
       </c>
       <c r="K113" s="9" t="n">
-        <v>0.87</v>
+        <v>0.84</v>
       </c>
       <c r="L113" s="9" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="M113" s="9" t="n">
         <v>0.6</v>
@@ -8579,7 +8559,7 @@
       </c>
       <c r="Q113" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:13</t>
+          <t>2026-10-13 23:50</t>
         </is>
       </c>
     </row>
@@ -8595,7 +8575,7 @@
         </is>
       </c>
       <c r="C114" s="10" t="n">
-        <v>11.55</v>
+        <v>11.6</v>
       </c>
       <c r="D114" s="10" t="n">
         <v>12.84</v>
@@ -8604,13 +8584,13 @@
         <v>10.02</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>0.0114</v>
+        <v>0.0104</v>
       </c>
       <c r="G114" s="11" t="n">
-        <v>0.0227</v>
+        <v>0.0209</v>
       </c>
       <c r="H114" s="11" t="n">
-        <v>0.0455</v>
+        <v>0.0418</v>
       </c>
       <c r="I114" s="9" t="inlineStr">
         <is>
@@ -8618,13 +8598,13 @@
         </is>
       </c>
       <c r="J114" s="9" t="n">
-        <v>12.69</v>
+        <v>12.34</v>
       </c>
       <c r="K114" s="9" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="L114" s="9" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="M114" s="9" t="n">
         <v>0.49</v>
@@ -8646,7 +8626,7 @@
       </c>
       <c r="Q114" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:13</t>
+          <t>2026-10-13 23:50</t>
         </is>
       </c>
     </row>
@@ -8662,7 +8642,7 @@
         </is>
       </c>
       <c r="C115" s="6" t="n">
-        <v>22.91</v>
+        <v>22.83</v>
       </c>
       <c r="D115" s="6" t="n">
         <v>26.47</v>
@@ -8671,13 +8651,13 @@
         <v>18.58</v>
       </c>
       <c r="F115" s="7" t="n">
-        <v>0.0328</v>
+        <v>0.0338</v>
       </c>
       <c r="G115" s="7" t="n">
-        <v>0.06560000000000001</v>
+        <v>0.06759999999999999</v>
       </c>
       <c r="H115" s="7" t="n">
-        <v>0.1312</v>
+        <v>0.1351</v>
       </c>
       <c r="I115" s="5" t="inlineStr">
         <is>
@@ -8685,15 +8665,13 @@
         </is>
       </c>
       <c r="J115" s="5" t="n">
-        <v>44.92</v>
+        <v>44.76</v>
       </c>
       <c r="K115" s="5" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="L115" s="5" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
+        <v>2.84</v>
+      </c>
+      <c r="L115" s="5" t="n">
+        <v>1.3</v>
       </c>
       <c r="M115" s="5" t="n">
         <v>0.85</v>
@@ -8715,7 +8693,7 @@
       </c>
       <c r="Q115" s="5" t="inlineStr">
         <is>
-          <t>2026-10-13 02:13</t>
+          <t>2026-10-13 23:50</t>
         </is>
       </c>
     </row>
@@ -8790,7 +8768,7 @@
       </c>
       <c r="Q116" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:13</t>
+          <t>2026-10-13 23:50</t>
         </is>
       </c>
     </row>
@@ -8806,7 +8784,7 @@
         </is>
       </c>
       <c r="C117" s="10" t="n">
-        <v>3.175</v>
+        <v>3.13</v>
       </c>
       <c r="D117" s="10" t="n">
         <v>6.81</v>
@@ -8815,13 +8793,13 @@
         <v>2.54</v>
       </c>
       <c r="F117" s="11" t="n">
-        <v>0.1424</v>
+        <v>0.1374</v>
       </c>
       <c r="G117" s="11" t="n">
-        <v>0.2848</v>
+        <v>0.2748</v>
       </c>
       <c r="H117" s="11" t="n">
-        <v>0.5696</v>
+        <v>0.5495</v>
       </c>
       <c r="I117" s="9" t="inlineStr">
         <is>
@@ -8829,13 +8807,13 @@
         </is>
       </c>
       <c r="J117" s="9" t="n">
-        <v>19.84</v>
+        <v>20.87</v>
       </c>
       <c r="K117" s="9" t="n">
-        <v>2.51</v>
+        <v>2.47</v>
       </c>
       <c r="L117" s="9" t="n">
-        <v>5.3</v>
+        <v>5.22</v>
       </c>
       <c r="M117" s="9" t="n">
         <v>0.3</v>
@@ -8857,7 +8835,7 @@
       </c>
       <c r="Q117" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:13</t>
+          <t>2026-10-13 23:50</t>
         </is>
       </c>
     </row>
@@ -8873,22 +8851,22 @@
         </is>
       </c>
       <c r="C118" s="10" t="n">
-        <v>165.49</v>
+        <v>162.8</v>
       </c>
       <c r="D118" s="10" t="n">
-        <v>300</v>
+        <v>299.19</v>
       </c>
       <c r="E118" s="10" t="n">
         <v>107.75</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>0.0559</v>
+        <v>0.0609</v>
       </c>
       <c r="G118" s="11" t="n">
-        <v>0.1117</v>
+        <v>0.1218</v>
       </c>
       <c r="H118" s="11" t="n">
-        <v>0.2235</v>
+        <v>0.2437</v>
       </c>
       <c r="I118" s="9" t="inlineStr">
         <is>
@@ -8896,13 +8874,13 @@
         </is>
       </c>
       <c r="J118" s="9" t="n">
-        <v>65.15000000000001</v>
+        <v>65.12</v>
       </c>
       <c r="K118" s="9" t="n">
-        <v>38.34</v>
+        <v>37.72</v>
       </c>
       <c r="L118" s="9" t="n">
-        <v>66.06999999999999</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="M118" s="9" t="n">
         <v>0.49</v>
@@ -8924,7 +8902,7 @@
       </c>
       <c r="Q118" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:13</t>
+          <t>2026-10-13 23:50</t>
         </is>
       </c>
     </row>
@@ -8940,7 +8918,7 @@
         </is>
       </c>
       <c r="C119" s="6" t="n">
-        <v>12.46</v>
+        <v>12.45</v>
       </c>
       <c r="D119" s="6" t="n">
         <v>18.74</v>
@@ -8949,13 +8927,13 @@
         <v>10.58</v>
       </c>
       <c r="F119" s="7" t="n">
-        <v>0.0591</v>
+        <v>0.0594</v>
       </c>
       <c r="G119" s="7" t="n">
-        <v>0.1182</v>
+        <v>0.1187</v>
       </c>
       <c r="H119" s="7" t="n">
-        <v>0.2364</v>
+        <v>0.2374</v>
       </c>
       <c r="I119" s="5" t="inlineStr">
         <is>
@@ -8963,10 +8941,10 @@
         </is>
       </c>
       <c r="J119" s="5" t="n">
-        <v>15.57</v>
+        <v>15.37</v>
       </c>
       <c r="K119" s="5" t="n">
-        <v>1.95</v>
+        <v>2.06</v>
       </c>
       <c r="L119" s="5" t="n">
         <v>2.46</v>
@@ -8991,7 +8969,7 @@
       </c>
       <c r="Q119" s="5" t="inlineStr">
         <is>
-          <t>2026-10-13 02:13</t>
+          <t>2026-10-13 23:50</t>
         </is>
       </c>
     </row>
@@ -9007,7 +8985,7 @@
         </is>
       </c>
       <c r="C120" s="10" t="n">
-        <v>17.44</v>
+        <v>17.09</v>
       </c>
       <c r="D120" s="10" t="n">
         <v>21.41</v>
@@ -9016,13 +8994,13 @@
         <v>15.1</v>
       </c>
       <c r="F120" s="11" t="n">
-        <v>0.0295</v>
+        <v>0.0353</v>
       </c>
       <c r="G120" s="11" t="n">
-        <v>0.0591</v>
+        <v>0.07049999999999999</v>
       </c>
       <c r="H120" s="11" t="n">
-        <v>0.1181</v>
+        <v>0.141</v>
       </c>
       <c r="I120" s="9" t="inlineStr">
         <is>
@@ -9030,13 +9008,13 @@
         </is>
       </c>
       <c r="J120" s="9" t="n">
-        <v>34.2</v>
+        <v>33.51</v>
       </c>
       <c r="K120" s="9" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="L120" s="9" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="M120" s="9" t="n">
         <v>0.48</v>
@@ -9058,7 +9036,7 @@
       </c>
       <c r="Q120" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:13</t>
+          <t>2026-10-13 23:50</t>
         </is>
       </c>
     </row>
@@ -9074,7 +9052,7 @@
         </is>
       </c>
       <c r="C121" s="6" t="n">
-        <v>8.289999999999999</v>
+        <v>8.15</v>
       </c>
       <c r="D121" s="6" t="n">
         <v>11.09</v>
@@ -9083,13 +9061,13 @@
         <v>8.035</v>
       </c>
       <c r="F121" s="7" t="n">
-        <v>0.0958</v>
+        <v>0.1012</v>
       </c>
       <c r="G121" s="7" t="n">
-        <v>0.1916</v>
+        <v>0.2023</v>
       </c>
       <c r="H121" s="7" t="n">
-        <v>0.3833</v>
+        <v>0.4047</v>
       </c>
       <c r="I121" s="5" t="inlineStr">
         <is>
@@ -9097,13 +9075,13 @@
         </is>
       </c>
       <c r="J121" s="5" t="n">
-        <v>9.869999999999999</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="K121" s="5" t="n">
-        <v>9.34</v>
+        <v>8.19</v>
       </c>
       <c r="L121" s="5" t="n">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="M121" s="5" t="n">
         <v>6.88</v>
@@ -9125,7 +9103,7 @@
       </c>
       <c r="Q121" s="5" t="inlineStr">
         <is>
-          <t>2026-10-13 02:13</t>
+          <t>2026-10-13 23:50</t>
         </is>
       </c>
     </row>
@@ -9141,7 +9119,7 @@
         </is>
       </c>
       <c r="C122" s="10" t="n">
-        <v>25.465</v>
+        <v>25.22</v>
       </c>
       <c r="D122" s="10" t="n">
         <v>25.83</v>
@@ -9150,13 +9128,13 @@
         <v>18.57</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>-0.0052</v>
+        <v>-0.0028</v>
       </c>
       <c r="G122" s="11" t="n">
-        <v>-0.0103</v>
+        <v>-0.0056</v>
       </c>
       <c r="H122" s="11" t="n">
-        <v>-0.0206</v>
+        <v>-0.0111</v>
       </c>
       <c r="I122" s="9" t="inlineStr">
         <is>
@@ -9164,13 +9142,13 @@
         </is>
       </c>
       <c r="J122" s="9" t="n">
-        <v>12.07</v>
+        <v>11.73</v>
       </c>
       <c r="K122" s="9" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="L122" s="9" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="M122" s="9" t="n">
         <v>0.38</v>
@@ -9192,7 +9170,7 @@
       </c>
       <c r="Q122" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:13</t>
+          <t>2026-10-13 23:50</t>
         </is>
       </c>
     </row>
@@ -9237,7 +9215,7 @@
         <v>2.9</v>
       </c>
       <c r="L123" s="9" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="M123" s="9" t="n">
         <v>0.98</v>
@@ -9259,7 +9237,7 @@
       </c>
       <c r="Q123" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:13</t>
+          <t>2026-10-13 23:50</t>
         </is>
       </c>
     </row>
@@ -9275,7 +9253,7 @@
         </is>
       </c>
       <c r="C124" s="10" t="n">
-        <v>157.35</v>
+        <v>154.19</v>
       </c>
       <c r="D124" s="10" t="n">
         <v>226</v>
@@ -9284,13 +9262,13 @@
         <v>131.07</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>0.054</v>
+        <v>0.0602</v>
       </c>
       <c r="G124" s="11" t="n">
-        <v>0.108</v>
+        <v>0.1205</v>
       </c>
       <c r="H124" s="11" t="n">
-        <v>0.216</v>
+        <v>0.2409</v>
       </c>
       <c r="I124" s="9" t="inlineStr">
         <is>
@@ -9298,13 +9276,13 @@
         </is>
       </c>
       <c r="J124" s="9" t="n">
-        <v>30.79</v>
+        <v>30.17</v>
       </c>
       <c r="K124" s="9" t="n">
-        <v>10.84</v>
+        <v>10.62</v>
       </c>
       <c r="L124" s="9" t="n">
-        <v>10.42</v>
+        <v>10.21</v>
       </c>
       <c r="M124" s="9" t="n">
         <v>3.96</v>
@@ -9326,7 +9304,7 @@
       </c>
       <c r="Q124" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:13</t>
+          <t>2026-10-13 23:50</t>
         </is>
       </c>
     </row>
@@ -9342,7 +9320,7 @@
         </is>
       </c>
       <c r="C125" s="10" t="n">
-        <v>54.725</v>
+        <v>54.37</v>
       </c>
       <c r="D125" s="10" t="n">
         <v>55.98</v>
@@ -9351,13 +9329,13 @@
         <v>30.39</v>
       </c>
       <c r="F125" s="11" t="n">
-        <v>-0.0128</v>
+        <v>-0.0108</v>
       </c>
       <c r="G125" s="11" t="n">
-        <v>-0.0256</v>
+        <v>-0.0216</v>
       </c>
       <c r="H125" s="11" t="n">
-        <v>-0.0511</v>
+        <v>-0.0433</v>
       </c>
       <c r="I125" s="9" t="inlineStr">
         <is>
@@ -9365,13 +9343,13 @@
         </is>
       </c>
       <c r="J125" s="9" t="n">
-        <v>40.24</v>
+        <v>39.69</v>
       </c>
       <c r="K125" s="9" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="L125" s="9" t="n">
-        <v>0.68</v>
+        <v>0.67</v>
       </c>
       <c r="M125" s="9" t="n">
         <v>1.97</v>
@@ -9393,7 +9371,7 @@
       </c>
       <c r="Q125" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:13</t>
+          <t>2026-10-13 23:50</t>
         </is>
       </c>
     </row>
@@ -9409,22 +9387,22 @@
         </is>
       </c>
       <c r="C126" s="10" t="n">
-        <v>160.42</v>
+        <v>161.49</v>
       </c>
       <c r="D126" s="10" t="n">
         <v>195.84</v>
       </c>
       <c r="E126" s="10" t="n">
-        <v>123.62</v>
+        <v>125.5</v>
       </c>
       <c r="F126" s="11" t="n">
-        <v>0.0171</v>
+        <v>0.0134</v>
       </c>
       <c r="G126" s="11" t="n">
-        <v>0.0342</v>
+        <v>0.0267</v>
       </c>
       <c r="H126" s="11" t="n">
-        <v>0.0684</v>
+        <v>0.0535</v>
       </c>
       <c r="I126" s="9" t="inlineStr">
         <is>
@@ -9432,13 +9410,13 @@
         </is>
       </c>
       <c r="J126" s="9" t="n">
-        <v>14.72</v>
+        <v>15.18</v>
       </c>
       <c r="K126" s="9" t="n">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="L126" s="9" t="n">
-        <v>4.22</v>
+        <v>4.25</v>
       </c>
       <c r="M126" s="9" t="n">
         <v>0.32</v>
@@ -9460,7 +9438,7 @@
       </c>
       <c r="Q126" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:13</t>
+          <t>2026-10-13 23:50</t>
         </is>
       </c>
     </row>
@@ -9476,22 +9454,22 @@
         </is>
       </c>
       <c r="C127" s="6" t="n">
-        <v>33.67</v>
+        <v>33.61</v>
       </c>
       <c r="D127" s="6" t="n">
-        <v>42</v>
+        <v>41.86</v>
       </c>
       <c r="E127" s="6" t="n">
         <v>25.5</v>
       </c>
       <c r="F127" s="7" t="n">
-        <v>0.0524</v>
+        <v>0.051</v>
       </c>
       <c r="G127" s="7" t="n">
-        <v>0.1047</v>
+        <v>0.102</v>
       </c>
       <c r="H127" s="7" t="n">
-        <v>0.2094</v>
+        <v>0.204</v>
       </c>
       <c r="I127" s="5" t="inlineStr">
         <is>
@@ -9499,13 +9477,13 @@
         </is>
       </c>
       <c r="J127" s="5" t="n">
-        <v>21.86</v>
+        <v>21.41</v>
       </c>
       <c r="K127" s="5" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="L127" s="5" t="n">
-        <v>8.380000000000001</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="M127" s="5" t="n">
         <v>0.13</v>
@@ -9527,7 +9505,7 @@
       </c>
       <c r="Q127" s="5" t="inlineStr">
         <is>
-          <t>2026-10-13 02:13</t>
+          <t>2026-10-13 23:50</t>
         </is>
       </c>
     </row>
@@ -9543,7 +9521,7 @@
         </is>
       </c>
       <c r="C128" s="10" t="n">
-        <v>6.955</v>
+        <v>7.03</v>
       </c>
       <c r="D128" s="10" t="n">
         <v>10</v>
@@ -9552,13 +9530,13 @@
         <v>5.335</v>
       </c>
       <c r="F128" s="11" t="n">
-        <v>0.0385</v>
+        <v>0.0354</v>
       </c>
       <c r="G128" s="11" t="n">
-        <v>0.077</v>
+        <v>0.0709</v>
       </c>
       <c r="H128" s="11" t="n">
-        <v>0.1541</v>
+        <v>0.1417</v>
       </c>
       <c r="I128" s="9" t="inlineStr">
         <is>
@@ -9566,13 +9544,13 @@
         </is>
       </c>
       <c r="J128" s="9" t="n">
-        <v>7.4</v>
+        <v>7.48</v>
       </c>
       <c r="K128" s="9" t="n">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="L128" s="9" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="M128" s="9" t="n">
         <v>4.66</v>
@@ -9594,7 +9572,7 @@
       </c>
       <c r="Q128" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:13</t>
+          <t>2026-10-13 23:50</t>
         </is>
       </c>
     </row>
@@ -9610,7 +9588,7 @@
         </is>
       </c>
       <c r="C129" s="10" t="n">
-        <v>4.695</v>
+        <v>4.7</v>
       </c>
       <c r="D129" s="10" t="n">
         <v>4.79</v>
@@ -9619,13 +9597,13 @@
         <v>2.86</v>
       </c>
       <c r="F129" s="11" t="n">
-        <v>0.0038</v>
+        <v>0.0035</v>
       </c>
       <c r="G129" s="11" t="n">
-        <v>0.0075</v>
+        <v>0.007</v>
       </c>
       <c r="H129" s="11" t="n">
-        <v>0.015</v>
+        <v>0.0139</v>
       </c>
       <c r="I129" s="9" t="inlineStr">
         <is>
@@ -9633,10 +9611,10 @@
         </is>
       </c>
       <c r="J129" s="9" t="n">
-        <v>469.5</v>
+        <v>470</v>
       </c>
       <c r="K129" s="9" t="n">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="L129" s="9" t="n">
         <v>2.69</v>
@@ -9661,7 +9639,7 @@
       </c>
       <c r="Q129" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:13</t>
+          <t>2026-10-13 23:50</t>
         </is>
       </c>
     </row>
@@ -9677,7 +9655,7 @@
         </is>
       </c>
       <c r="C130" s="10" t="n">
-        <v>4.85</v>
+        <v>4.86</v>
       </c>
       <c r="D130" s="10" t="n">
         <v>5.33</v>
@@ -9686,13 +9664,13 @@
         <v>2.96</v>
       </c>
       <c r="F130" s="11" t="n">
-        <v>0.0156</v>
+        <v>0.0136</v>
       </c>
       <c r="G130" s="11" t="n">
-        <v>0.0311</v>
+        <v>0.0272</v>
       </c>
       <c r="H130" s="11" t="n">
-        <v>0.0623</v>
+        <v>0.0543</v>
       </c>
       <c r="I130" s="9" t="inlineStr">
         <is>
@@ -9700,10 +9678,10 @@
         </is>
       </c>
       <c r="J130" s="9" t="n">
-        <v>13.86</v>
+        <v>14.73</v>
       </c>
       <c r="K130" s="9" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="L130" s="9" t="n">
         <v>3.66</v>
@@ -9728,7 +9706,7 @@
       </c>
       <c r="Q130" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:13</t>
+          <t>2026-10-13 23:50</t>
         </is>
       </c>
     </row>
@@ -9744,7 +9722,7 @@
         </is>
       </c>
       <c r="C131" s="10" t="n">
-        <v>3.4</v>
+        <v>3.405</v>
       </c>
       <c r="D131" s="10" t="n">
         <v>4.27</v>
@@ -9753,13 +9731,13 @@
         <v>3.275</v>
       </c>
       <c r="F131" s="11" t="n">
-        <v>0.0462</v>
+        <v>0.0457</v>
       </c>
       <c r="G131" s="11" t="n">
-        <v>0.0924</v>
+        <v>0.0915</v>
       </c>
       <c r="H131" s="11" t="n">
-        <v>0.1847</v>
+        <v>0.183</v>
       </c>
       <c r="I131" s="9" t="inlineStr">
         <is>
@@ -9767,13 +9745,13 @@
         </is>
       </c>
       <c r="J131" s="9" t="n">
-        <v>8.949999999999999</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="K131" s="9" t="n">
         <v>0.92</v>
       </c>
       <c r="L131" s="9" t="n">
-        <v>6.9</v>
+        <v>6.91</v>
       </c>
       <c r="M131" s="9" t="n">
         <v>0.72</v>
@@ -9795,7 +9773,7 @@
       </c>
       <c r="Q131" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:13</t>
+          <t>2026-10-13 23:50</t>
         </is>
       </c>
     </row>
@@ -9811,7 +9789,7 @@
         </is>
       </c>
       <c r="C132" s="10" t="n">
-        <v>4.7</v>
+        <v>4.77</v>
       </c>
       <c r="D132" s="10" t="n">
         <v>8.699999999999999</v>
@@ -9839,10 +9817,10 @@
         </is>
       </c>
       <c r="K132" s="9" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="L132" s="9" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="M132" s="9" t="n">
         <v>2.07</v>
@@ -9864,7 +9842,7 @@
       </c>
       <c r="Q132" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:13</t>
+          <t>2026-10-13 23:50</t>
         </is>
       </c>
     </row>
@@ -9880,7 +9858,7 @@
         </is>
       </c>
       <c r="C133" s="10" t="n">
-        <v>5.785</v>
+        <v>5.78</v>
       </c>
       <c r="D133" s="10" t="n">
         <v>6.665</v>
@@ -9889,13 +9867,13 @@
         <v>3.87</v>
       </c>
       <c r="F133" s="11" t="n">
-        <v>0.0071</v>
+        <v>0.0074</v>
       </c>
       <c r="G133" s="11" t="n">
-        <v>0.0143</v>
+        <v>0.0147</v>
       </c>
       <c r="H133" s="11" t="n">
-        <v>0.0285</v>
+        <v>0.0294</v>
       </c>
       <c r="I133" s="9" t="inlineStr">
         <is>
@@ -9903,13 +9881,13 @@
         </is>
       </c>
       <c r="J133" s="9" t="n">
-        <v>24.1</v>
+        <v>24.08</v>
       </c>
       <c r="K133" s="9" t="n">
         <v>2.71</v>
       </c>
       <c r="L133" s="9" t="n">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
       <c r="M133" s="9" t="n">
         <v>0.77</v>
@@ -9931,7 +9909,7 @@
       </c>
       <c r="Q133" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:13</t>
+          <t>2026-10-13 23:50</t>
         </is>
       </c>
     </row>
@@ -9947,7 +9925,7 @@
         </is>
       </c>
       <c r="C134" s="6" t="n">
-        <v>12.84</v>
+        <v>12.79</v>
       </c>
       <c r="D134" s="6" t="n">
         <v>28.2</v>
@@ -9956,13 +9934,13 @@
         <v>10.86</v>
       </c>
       <c r="F134" s="7" t="n">
-        <v>0.1185</v>
+        <v>0.1199</v>
       </c>
       <c r="G134" s="7" t="n">
-        <v>0.237</v>
+        <v>0.2398</v>
       </c>
       <c r="H134" s="7" t="n">
-        <v>0.4739</v>
+        <v>0.4797</v>
       </c>
       <c r="I134" s="5" t="inlineStr">
         <is>
@@ -9970,13 +9948,13 @@
         </is>
       </c>
       <c r="J134" s="5" t="n">
-        <v>18.34</v>
+        <v>18.27</v>
       </c>
       <c r="K134" s="5" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="L134" s="5" t="n">
-        <v>3.58</v>
+        <v>3.57</v>
       </c>
       <c r="M134" s="5" t="n">
         <v>0.6</v>
@@ -9998,7 +9976,7 @@
       </c>
       <c r="Q134" s="5" t="inlineStr">
         <is>
-          <t>2026-10-13 02:13</t>
+          <t>2026-10-13 23:50</t>
         </is>
       </c>
     </row>
@@ -10014,22 +9992,22 @@
         </is>
       </c>
       <c r="C135" s="10" t="n">
-        <v>21.98</v>
+        <v>21.77</v>
       </c>
       <c r="D135" s="10" t="n">
         <v>31.81</v>
       </c>
       <c r="E135" s="10" t="n">
-        <v>13.2</v>
+        <v>13.25</v>
       </c>
       <c r="F135" s="11" t="n">
-        <v>0.0572</v>
+        <v>0.0601</v>
       </c>
       <c r="G135" s="11" t="n">
-        <v>0.1143</v>
+        <v>0.1202</v>
       </c>
       <c r="H135" s="11" t="n">
-        <v>0.2286</v>
+        <v>0.2405</v>
       </c>
       <c r="I135" s="9" t="inlineStr">
         <is>
@@ -10037,13 +10015,13 @@
         </is>
       </c>
       <c r="J135" s="9" t="n">
-        <v>17.58</v>
+        <v>17.42</v>
       </c>
       <c r="K135" s="9" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="L135" s="9" t="n">
-        <v>0.53</v>
+        <v>0.52</v>
       </c>
       <c r="M135" s="9" t="n">
         <v>0.31</v>
@@ -10065,7 +10043,7 @@
       </c>
       <c r="Q135" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:13</t>
+          <t>2026-10-13 23:50</t>
         </is>
       </c>
     </row>
@@ -10081,7 +10059,7 @@
         </is>
       </c>
       <c r="C136" s="6" t="n">
-        <v>4.115</v>
+        <v>4.14</v>
       </c>
       <c r="D136" s="6" t="n">
         <v>6.75</v>
@@ -10090,13 +10068,13 @@
         <v>3.71</v>
       </c>
       <c r="F136" s="7" t="n">
-        <v>0.061</v>
+        <v>0.0592</v>
       </c>
       <c r="G136" s="7" t="n">
-        <v>0.1221</v>
+        <v>0.1183</v>
       </c>
       <c r="H136" s="7" t="n">
-        <v>0.2442</v>
+        <v>0.2367</v>
       </c>
       <c r="I136" s="5" t="inlineStr">
         <is>
@@ -10104,13 +10082,13 @@
         </is>
       </c>
       <c r="J136" s="5" t="n">
-        <v>10.04</v>
+        <v>10.1</v>
       </c>
       <c r="K136" s="5" t="n">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="L136" s="5" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="M136" s="5" t="n">
         <v>0.47</v>
@@ -10132,7 +10110,7 @@
       </c>
       <c r="Q136" s="5" t="inlineStr">
         <is>
-          <t>2026-10-13 02:13</t>
+          <t>2026-10-13 23:50</t>
         </is>
       </c>
     </row>
@@ -10148,7 +10126,7 @@
         </is>
       </c>
       <c r="C137" s="10" t="n">
-        <v>0.12</v>
+        <v>0.125</v>
       </c>
       <c r="D137" s="10" t="n">
         <v>0.195</v>
@@ -10157,13 +10135,13 @@
         <v>0.083</v>
       </c>
       <c r="F137" s="11" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="G137" s="11" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="H137" s="11" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="I137" s="9" t="inlineStr">
         <is>
@@ -10171,13 +10149,13 @@
         </is>
       </c>
       <c r="J137" s="9" t="n">
-        <v>-10.94</v>
+        <v>-11.39</v>
       </c>
       <c r="K137" s="9" t="n">
-        <v>1.38</v>
+        <v>2.19</v>
       </c>
       <c r="L137" s="9" t="n">
-        <v>0.61</v>
+        <v>0.64</v>
       </c>
       <c r="M137" s="9" t="n">
         <v>1.51</v>
@@ -10199,7 +10177,7 @@
       </c>
       <c r="Q137" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:13</t>
+          <t>2026-10-13 23:50</t>
         </is>
       </c>
     </row>
@@ -10215,22 +10193,22 @@
         </is>
       </c>
       <c r="C138" s="10" t="n">
-        <v>18.545</v>
+        <v>18.24</v>
       </c>
       <c r="D138" s="10" t="n">
         <v>24.27</v>
       </c>
       <c r="E138" s="10" t="n">
-        <v>18.26</v>
+        <v>18.11</v>
       </c>
       <c r="F138" s="11" t="n">
-        <v>0.0482</v>
+        <v>0.0531</v>
       </c>
       <c r="G138" s="11" t="n">
-        <v>0.0963</v>
+        <v>0.1063</v>
       </c>
       <c r="H138" s="11" t="n">
-        <v>0.1926</v>
+        <v>0.2126</v>
       </c>
       <c r="I138" s="9" t="inlineStr">
         <is>
@@ -10238,13 +10216,13 @@
         </is>
       </c>
       <c r="J138" s="9" t="n">
-        <v>15.08</v>
+        <v>14.83</v>
       </c>
       <c r="K138" s="9" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="L138" s="9" t="n">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
       <c r="M138" s="9" t="n">
         <v>0.6899999999999999</v>
@@ -10266,7 +10244,7 @@
       </c>
       <c r="Q138" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:13</t>
+          <t>2026-10-13 23:50</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10319,7 @@
       </c>
       <c r="Q139" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:13</t>
+          <t>2026-10-13 23:50</t>
         </is>
       </c>
     </row>
@@ -10357,7 +10335,7 @@
         </is>
       </c>
       <c r="C140" s="10" t="n">
-        <v>45.68</v>
+        <v>45.92</v>
       </c>
       <c r="D140" s="10" t="n">
         <v>49.43</v>
@@ -10366,13 +10344,13 @@
         <v>34.78</v>
       </c>
       <c r="F140" s="11" t="n">
-        <v>-0.0301</v>
+        <v>-0.0313</v>
       </c>
       <c r="G140" s="11" t="n">
-        <v>-0.0603</v>
+        <v>-0.0626</v>
       </c>
       <c r="H140" s="11" t="n">
-        <v>-0.1205</v>
+        <v>-0.1251</v>
       </c>
       <c r="I140" s="9" t="inlineStr">
         <is>
@@ -10380,13 +10358,13 @@
         </is>
       </c>
       <c r="J140" s="9" t="n">
-        <v>7.77</v>
+        <v>7.74</v>
       </c>
       <c r="K140" s="9" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="L140" s="9" t="n">
-        <v>5.88</v>
+        <v>5.92</v>
       </c>
       <c r="M140" s="9" t="n">
         <v>6.55</v>
@@ -10408,7 +10386,7 @@
       </c>
       <c r="Q140" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:13</t>
+          <t>2026-10-13 23:50</t>
         </is>
       </c>
     </row>
@@ -10424,22 +10402,22 @@
         </is>
       </c>
       <c r="C141" s="6" t="n">
-        <v>8.935</v>
+        <v>9.074999999999999</v>
       </c>
       <c r="D141" s="6" t="n">
-        <v>9.055</v>
+        <v>9.074999999999999</v>
       </c>
       <c r="E141" s="6" t="n">
         <v>5.9</v>
       </c>
       <c r="F141" s="7" t="n">
-        <v>0.0132</v>
+        <v>0.0116</v>
       </c>
       <c r="G141" s="7" t="n">
-        <v>0.0265</v>
+        <v>0.0233</v>
       </c>
       <c r="H141" s="7" t="n">
-        <v>0.0529</v>
+        <v>0.0466</v>
       </c>
       <c r="I141" s="5" t="inlineStr">
         <is>
@@ -10447,15 +10425,13 @@
         </is>
       </c>
       <c r="J141" s="5" t="n">
-        <v>27.08</v>
+        <v>27.5</v>
       </c>
       <c r="K141" s="5" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="L141" s="5" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
+        <v>1.33</v>
+      </c>
+      <c r="L141" s="5" t="n">
+        <v>5.92</v>
       </c>
       <c r="M141" s="5" t="n">
         <v>0.47</v>
@@ -10477,7 +10453,7 @@
       </c>
       <c r="Q141" s="5" t="inlineStr">
         <is>
-          <t>2026-10-13 02:13</t>
+          <t>2026-10-13 23:50</t>
         </is>
       </c>
     </row>
@@ -10493,7 +10469,7 @@
         </is>
       </c>
       <c r="C142" s="10" t="n">
-        <v>13.615</v>
+        <v>13.51</v>
       </c>
       <c r="D142" s="10" t="n">
         <v>17.65</v>
@@ -10502,13 +10478,13 @@
         <v>10.08</v>
       </c>
       <c r="F142" s="11" t="n">
-        <v>0.0193</v>
+        <v>0.0214</v>
       </c>
       <c r="G142" s="11" t="n">
-        <v>0.0386</v>
+        <v>0.0428</v>
       </c>
       <c r="H142" s="11" t="n">
-        <v>0.07729999999999999</v>
+        <v>0.0857</v>
       </c>
       <c r="I142" s="9" t="inlineStr">
         <is>
@@ -10516,10 +10492,10 @@
         </is>
       </c>
       <c r="J142" s="9" t="n">
-        <v>14.96</v>
+        <v>14.85</v>
       </c>
       <c r="K142" s="9" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="L142" s="9" t="n">
         <v>0.73</v>
@@ -10544,7 +10520,7 @@
       </c>
       <c r="Q142" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:13</t>
+          <t>2026-10-13 23:50</t>
         </is>
       </c>
     </row>
@@ -10560,22 +10536,22 @@
         </is>
       </c>
       <c r="C143" s="10" t="n">
-        <v>19.33</v>
+        <v>19.05</v>
       </c>
       <c r="D143" s="10" t="n">
-        <v>20.85</v>
+        <v>20.48</v>
       </c>
       <c r="E143" s="10" t="n">
         <v>13.8</v>
       </c>
       <c r="F143" s="11" t="n">
-        <v>0.0045</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="G143" s="11" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.0165</v>
       </c>
       <c r="H143" s="11" t="n">
-        <v>0.018</v>
+        <v>0.0329</v>
       </c>
       <c r="I143" s="9" t="inlineStr">
         <is>
@@ -10583,13 +10559,13 @@
         </is>
       </c>
       <c r="J143" s="9" t="n">
-        <v>20.35</v>
+        <v>20.05</v>
       </c>
       <c r="K143" s="9" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="L143" s="9" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="M143" s="9" t="n">
         <v>0.26</v>
@@ -10611,7 +10587,7 @@
       </c>
       <c r="Q143" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:13</t>
+          <t>2026-10-13 23:50</t>
         </is>
       </c>
     </row>
@@ -10686,7 +10662,7 @@
       </c>
       <c r="Q144" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:13</t>
+          <t>2026-10-13 23:50</t>
         </is>
       </c>
     </row>
@@ -10702,7 +10678,7 @@
         </is>
       </c>
       <c r="C145" s="10" t="n">
-        <v>0.865</v>
+        <v>0.862</v>
       </c>
       <c r="D145" s="10" t="n">
         <v>1.19</v>
@@ -10711,13 +10687,13 @@
         <v>0.66</v>
       </c>
       <c r="F145" s="11" t="n">
-        <v>0.042</v>
+        <v>0.0431</v>
       </c>
       <c r="G145" s="11" t="n">
-        <v>0.08409999999999999</v>
+        <v>0.0861</v>
       </c>
       <c r="H145" s="11" t="n">
-        <v>0.1682</v>
+        <v>0.1722</v>
       </c>
       <c r="I145" s="9" t="inlineStr">
         <is>
@@ -10725,10 +10701,10 @@
         </is>
       </c>
       <c r="J145" s="9" t="n">
-        <v>43.25</v>
+        <v>43.1</v>
       </c>
       <c r="K145" s="9" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="L145" s="9" t="n">
         <v>0.75</v>
@@ -10753,7 +10729,7 @@
       </c>
       <c r="Q145" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:13</t>
+          <t>2026-10-13 23:50</t>
         </is>
       </c>
     </row>
@@ -10769,7 +10745,7 @@
         </is>
       </c>
       <c r="C146" s="10" t="n">
-        <v>13.45</v>
+        <v>13.39</v>
       </c>
       <c r="D146" s="10" t="n">
         <v>15.62</v>
@@ -10778,13 +10754,13 @@
         <v>12.82</v>
       </c>
       <c r="F146" s="11" t="n">
-        <v>0.0037</v>
+        <v>0.0048</v>
       </c>
       <c r="G146" s="11" t="n">
-        <v>0.0073</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="H146" s="11" t="n">
-        <v>0.0147</v>
+        <v>0.0192</v>
       </c>
       <c r="I146" s="9" t="inlineStr">
         <is>
@@ -10792,13 +10768,13 @@
         </is>
       </c>
       <c r="J146" s="9" t="n">
-        <v>112.08</v>
+        <v>111.58</v>
       </c>
       <c r="K146" s="9" t="n">
-        <v>5.43</v>
+        <v>5.41</v>
       </c>
       <c r="L146" s="9" t="n">
-        <v>10.78</v>
+        <v>10.73</v>
       </c>
       <c r="M146" s="9" t="n">
         <v>2.71</v>
@@ -10820,7 +10796,7 @@
       </c>
       <c r="Q146" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:13</t>
+          <t>2026-10-13 23:50</t>
         </is>
       </c>
     </row>
@@ -10836,7 +10812,7 @@
         </is>
       </c>
       <c r="C147" s="10" t="n">
-        <v>4.605</v>
+        <v>4.655</v>
       </c>
       <c r="D147" s="10" t="n">
         <v>5.58</v>
@@ -10845,13 +10821,13 @@
         <v>4.56</v>
       </c>
       <c r="F147" s="11" t="n">
-        <v>0.0221</v>
+        <v>0.0192</v>
       </c>
       <c r="G147" s="11" t="n">
-        <v>0.0442</v>
+        <v>0.0383</v>
       </c>
       <c r="H147" s="11" t="n">
-        <v>0.08840000000000001</v>
+        <v>0.0767</v>
       </c>
       <c r="I147" s="9" t="inlineStr">
         <is>
@@ -10859,15 +10835,13 @@
         </is>
       </c>
       <c r="J147" s="9" t="n">
-        <v>23.02</v>
+        <v>23.28</v>
       </c>
       <c r="K147" s="9" t="n">
-        <v>4.08</v>
-      </c>
-      <c r="L147" s="9" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
+        <v>4.12</v>
+      </c>
+      <c r="L147" s="9" t="n">
+        <v>2.25</v>
       </c>
       <c r="M147" s="9" t="n">
         <v>1.26</v>
@@ -10889,7 +10863,7 @@
       </c>
       <c r="Q147" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:13</t>
+          <t>2026-10-13 23:50</t>
         </is>
       </c>
     </row>
@@ -10905,7 +10879,7 @@
         </is>
       </c>
       <c r="C148" s="10" t="n">
-        <v>30.43</v>
+        <v>30.16</v>
       </c>
       <c r="D148" s="10" t="n">
         <v>39.99</v>
@@ -10914,13 +10888,13 @@
         <v>20.14</v>
       </c>
       <c r="F148" s="11" t="n">
-        <v>0.0042</v>
+        <v>0.0076</v>
       </c>
       <c r="G148" s="11" t="n">
-        <v>0.0083</v>
+        <v>0.0151</v>
       </c>
       <c r="H148" s="11" t="n">
-        <v>0.0167</v>
+        <v>0.0302</v>
       </c>
       <c r="I148" s="9" t="inlineStr">
         <is>
@@ -10928,13 +10902,13 @@
         </is>
       </c>
       <c r="J148" s="9" t="n">
-        <v>70.77</v>
+        <v>71.81</v>
       </c>
       <c r="K148" s="9" t="n">
-        <v>23.23</v>
+        <v>23.02</v>
       </c>
       <c r="L148" s="9" t="n">
-        <v>15.78</v>
+        <v>15.64</v>
       </c>
       <c r="M148" s="9" t="n">
         <v>0.12</v>
@@ -10956,7 +10930,7 @@
       </c>
       <c r="Q148" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:13</t>
+          <t>2026-10-13 23:50</t>
         </is>
       </c>
     </row>
@@ -10972,7 +10946,7 @@
         </is>
       </c>
       <c r="C149" s="10" t="n">
-        <v>3.715</v>
+        <v>3.705</v>
       </c>
       <c r="D149" s="10" t="n">
         <v>5.85</v>
@@ -10981,13 +10955,13 @@
         <v>3.47</v>
       </c>
       <c r="F149" s="11" t="n">
-        <v>0.0254</v>
+        <v>0.0261</v>
       </c>
       <c r="G149" s="11" t="n">
-        <v>0.0508</v>
+        <v>0.0523</v>
       </c>
       <c r="H149" s="11" t="n">
-        <v>0.1016</v>
+        <v>0.1046</v>
       </c>
       <c r="I149" s="9" t="inlineStr">
         <is>
@@ -10995,13 +10969,13 @@
         </is>
       </c>
       <c r="J149" s="9" t="n">
-        <v>123.83</v>
+        <v>123.5</v>
       </c>
       <c r="K149" s="9" t="n">
         <v>0.85</v>
       </c>
       <c r="L149" s="9" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="M149" s="9" t="n">
         <v>0.49</v>
@@ -11023,7 +10997,7 @@
       </c>
       <c r="Q149" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:13</t>
+          <t>2026-10-13 23:50</t>
         </is>
       </c>
     </row>
@@ -11039,7 +11013,7 @@
         </is>
       </c>
       <c r="C150" s="10" t="n">
-        <v>5.69</v>
+        <v>5.6</v>
       </c>
       <c r="D150" s="10" t="n">
         <v>6.58</v>
@@ -11048,13 +11022,13 @@
         <v>3.34</v>
       </c>
       <c r="F150" s="11" t="n">
-        <v>0.028</v>
+        <v>0.0325</v>
       </c>
       <c r="G150" s="11" t="n">
-        <v>0.0561</v>
+        <v>0.065</v>
       </c>
       <c r="H150" s="11" t="n">
-        <v>0.1121</v>
+        <v>0.13</v>
       </c>
       <c r="I150" s="9" t="inlineStr">
         <is>
@@ -11062,13 +11036,13 @@
         </is>
       </c>
       <c r="J150" s="9" t="n">
-        <v>13.7</v>
+        <v>13.48</v>
       </c>
       <c r="K150" s="9" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="L150" s="9" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="M150" s="9" t="n">
         <v>0.6</v>
@@ -11090,7 +11064,7 @@
       </c>
       <c r="Q150" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:13</t>
+          <t>2026-10-13 23:50</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11080,7 @@
         </is>
       </c>
       <c r="C151" s="10" t="n">
-        <v>2.305</v>
+        <v>2.3</v>
       </c>
       <c r="D151" s="10" t="n">
         <v>2.73</v>
@@ -11115,13 +11089,13 @@
         <v>2.21</v>
       </c>
       <c r="F151" s="11" t="n">
-        <v>0.0329</v>
+        <v>0.0335</v>
       </c>
       <c r="G151" s="11" t="n">
-        <v>0.0658</v>
+        <v>0.067</v>
       </c>
       <c r="H151" s="11" t="n">
-        <v>0.1316</v>
+        <v>0.134</v>
       </c>
       <c r="I151" s="9" t="inlineStr">
         <is>
@@ -11129,13 +11103,13 @@
         </is>
       </c>
       <c r="J151" s="9" t="n">
-        <v>7.68</v>
+        <v>7.67</v>
       </c>
       <c r="K151" s="9" t="n">
         <v>0.88</v>
       </c>
       <c r="L151" s="9" t="n">
-        <v>7.64</v>
+        <v>7.62</v>
       </c>
       <c r="M151" s="9" t="n">
         <v>0.41</v>
@@ -11157,74 +11131,74 @@
       </c>
       <c r="Q151" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:13</t>
+          <t>2026-10-13 23:50</t>
         </is>
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="5" t="inlineStr">
+      <c r="A152" s="9" t="inlineStr">
         <is>
           <t>VEA</t>
         </is>
       </c>
-      <c r="B152" s="5" t="inlineStr">
+      <c r="B152" s="9" t="inlineStr">
         <is>
           <t>Viva Energy Group Limited</t>
         </is>
       </c>
-      <c r="C152" s="6" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="D152" s="6" t="n">
+      <c r="C152" s="10" t="n">
+        <v>3.225</v>
+      </c>
+      <c r="D152" s="10" t="n">
         <v>3.28</v>
       </c>
-      <c r="E152" s="6" t="n">
+      <c r="E152" s="10" t="n">
         <v>1.695</v>
       </c>
-      <c r="F152" s="7" t="n">
-        <v>-0.0089</v>
-      </c>
-      <c r="G152" s="7" t="n">
-        <v>-0.0177</v>
-      </c>
-      <c r="H152" s="7" t="n">
-        <v>-0.0354</v>
-      </c>
-      <c r="I152" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J152" s="5" t="n">
-        <v>24.62</v>
-      </c>
-      <c r="K152" s="5" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="L152" s="5" t="n">
+      <c r="F152" s="11" t="n">
+        <v>-0.0051</v>
+      </c>
+      <c r="G152" s="11" t="n">
+        <v>-0.0102</v>
+      </c>
+      <c r="H152" s="11" t="n">
+        <v>-0.0205</v>
+      </c>
+      <c r="I152" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J152" s="9" t="n">
+        <v>24.81</v>
+      </c>
+      <c r="K152" s="9" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="L152" s="9" t="n">
         <v>0.18</v>
       </c>
-      <c r="M152" s="5" t="n">
+      <c r="M152" s="9" t="n">
         <v>3.01</v>
       </c>
-      <c r="N152" s="8" t="inlineStr">
+      <c r="N152" s="12" t="inlineStr">
         <is>
           <t>2025: $28,438.2M | 2024: $29,992.2M | 2023: $25,615.4M | 2022: $26,196.5M</t>
         </is>
       </c>
-      <c r="O152" s="8" t="inlineStr">
+      <c r="O152" s="12" t="inlineStr">
         <is>
           <t>2025: $-421.1M | 2024: $-76.3M | 2023: $3.8M | 2022: $514.3M</t>
         </is>
       </c>
-      <c r="P152" s="8" t="inlineStr">
+      <c r="P152" s="12" t="inlineStr">
         <is>
           <t>Viva Energy Group Limited operates as an energy company in Australia, Singapore, and Papua New Guinea. The company operates through three segments: Convenience &amp; Mobility, Commercial &amp; Industrial, and Energy &amp; Infrastructure. The Convenience &amp; Mobility segment operates as an integrated convenience and fuel network under the Shell, Coles Express, Reddy Express, Liberty, Westside, OTR, S24, and S...</t>
         </is>
       </c>
-      <c r="Q152" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-13 02:13</t>
+      <c r="Q152" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-13 23:50</t>
         </is>
       </c>
     </row>
@@ -11240,7 +11214,7 @@
         </is>
       </c>
       <c r="C153" s="10" t="n">
-        <v>34.96</v>
+        <v>34.79</v>
       </c>
       <c r="D153" s="10" t="n">
         <v>43.32</v>
@@ -11249,13 +11223,13 @@
         <v>33.46</v>
       </c>
       <c r="F153" s="11" t="n">
-        <v>-0.0107</v>
+        <v>-0.0095</v>
       </c>
       <c r="G153" s="11" t="n">
-        <v>-0.0214</v>
+        <v>-0.019</v>
       </c>
       <c r="H153" s="11" t="n">
-        <v>-0.0427</v>
+        <v>-0.0381</v>
       </c>
       <c r="I153" s="9" t="inlineStr">
         <is>
@@ -11263,13 +11237,13 @@
         </is>
       </c>
       <c r="J153" s="9" t="n">
-        <v>17.22</v>
+        <v>16.89</v>
       </c>
       <c r="K153" s="9" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="L153" s="9" t="n">
-        <v>5.36</v>
+        <v>5.34</v>
       </c>
       <c r="M153" s="9" t="inlineStr">
         <is>
@@ -11293,7 +11267,7 @@
       </c>
       <c r="Q153" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:13</t>
+          <t>2026-10-13 23:50</t>
         </is>
       </c>
     </row>
@@ -11309,7 +11283,7 @@
         </is>
       </c>
       <c r="C154" s="6" t="n">
-        <v>3.38</v>
+        <v>3.34</v>
       </c>
       <c r="D154" s="6" t="n">
         <v>5.04</v>
@@ -11318,13 +11292,13 @@
         <v>2.17</v>
       </c>
       <c r="F154" s="7" t="n">
-        <v>0.09329999999999999</v>
+        <v>0.0867</v>
       </c>
       <c r="G154" s="7" t="n">
-        <v>0.1866</v>
+        <v>0.1734</v>
       </c>
       <c r="H154" s="7" t="n">
-        <v>0.3732</v>
+        <v>0.3468</v>
       </c>
       <c r="I154" s="5" t="inlineStr">
         <is>
@@ -11332,13 +11306,13 @@
         </is>
       </c>
       <c r="J154" s="5" t="n">
-        <v>33.8</v>
+        <v>33.4</v>
       </c>
       <c r="K154" s="5" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="L154" s="5" t="n">
-        <v>3.08</v>
+        <v>3.05</v>
       </c>
       <c r="M154" s="5" t="n">
         <v>0.44</v>
@@ -11360,7 +11334,7 @@
       </c>
       <c r="Q154" s="5" t="inlineStr">
         <is>
-          <t>2026-10-13 02:13</t>
+          <t>2026-10-13 23:50</t>
         </is>
       </c>
     </row>
@@ -11376,7 +11350,7 @@
         </is>
       </c>
       <c r="C155" s="10" t="n">
-        <v>77.78</v>
+        <v>77.485</v>
       </c>
       <c r="D155" s="10" t="n">
         <v>94.7</v>
@@ -11385,13 +11359,13 @@
         <v>70.8</v>
       </c>
       <c r="F155" s="11" t="n">
-        <v>-0.0052</v>
+        <v>-0.0043</v>
       </c>
       <c r="G155" s="11" t="n">
-        <v>-0.0104</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="H155" s="11" t="n">
-        <v>-0.0207</v>
+        <v>-0.017</v>
       </c>
       <c r="I155" s="9" t="inlineStr">
         <is>
@@ -11399,13 +11373,13 @@
         </is>
       </c>
       <c r="J155" s="9" t="n">
-        <v>30.74</v>
+        <v>30.63</v>
       </c>
       <c r="K155" s="9" t="n">
-        <v>11.24</v>
+        <v>11.03</v>
       </c>
       <c r="L155" s="9" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="M155" s="9" t="n">
         <v>1.59</v>
@@ -11427,7 +11401,7 @@
       </c>
       <c r="Q155" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:13</t>
+          <t>2026-10-13 23:50</t>
         </is>
       </c>
     </row>
@@ -11443,22 +11417,22 @@
         </is>
       </c>
       <c r="C156" s="10" t="n">
-        <v>7.88</v>
+        <v>7.81</v>
       </c>
       <c r="D156" s="10" t="n">
         <v>9.9</v>
       </c>
       <c r="E156" s="10" t="n">
-        <v>6.33</v>
+        <v>6.42</v>
       </c>
       <c r="F156" s="11" t="n">
-        <v>0.0213</v>
+        <v>0.0237</v>
       </c>
       <c r="G156" s="11" t="n">
-        <v>0.0425</v>
+        <v>0.0474</v>
       </c>
       <c r="H156" s="11" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="I156" s="9" t="inlineStr">
         <is>
@@ -11466,13 +11440,13 @@
         </is>
       </c>
       <c r="J156" s="9" t="n">
-        <v>16.42</v>
+        <v>16.27</v>
       </c>
       <c r="K156" s="9" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="L156" s="9" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="M156" s="9" t="n">
         <v>0.39</v>
@@ -11494,7 +11468,7 @@
       </c>
       <c r="Q156" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:13</t>
+          <t>2026-10-13 23:50</t>
         </is>
       </c>
     </row>
@@ -11510,22 +11484,22 @@
         </is>
       </c>
       <c r="C157" s="10" t="n">
-        <v>9.32</v>
+        <v>9.324999999999999</v>
       </c>
       <c r="D157" s="10" t="n">
         <v>14.615</v>
       </c>
       <c r="E157" s="10" t="n">
-        <v>9.24</v>
+        <v>9.295</v>
       </c>
       <c r="F157" s="11" t="n">
-        <v>0.063</v>
+        <v>0.0629</v>
       </c>
       <c r="G157" s="11" t="n">
-        <v>0.1261</v>
+        <v>0.1257</v>
       </c>
       <c r="H157" s="11" t="n">
-        <v>0.2521</v>
+        <v>0.2515</v>
       </c>
       <c r="I157" s="9" t="inlineStr">
         <is>
@@ -11533,13 +11507,13 @@
         </is>
       </c>
       <c r="J157" s="9" t="n">
-        <v>19.83</v>
+        <v>19.84</v>
       </c>
       <c r="K157" s="9" t="n">
         <v>0.93</v>
       </c>
       <c r="L157" s="9" t="n">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="M157" s="9" t="n">
         <v>0.58</v>
@@ -11561,7 +11535,7 @@
       </c>
       <c r="Q157" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:13</t>
+          <t>2026-10-13 23:50</t>
         </is>
       </c>
     </row>
@@ -11577,7 +11551,7 @@
         </is>
       </c>
       <c r="C158" s="10" t="n">
-        <v>39.61</v>
+        <v>39.69</v>
       </c>
       <c r="D158" s="10" t="n">
         <v>41.19</v>
@@ -11586,13 +11560,13 @@
         <v>25.51</v>
       </c>
       <c r="F158" s="11" t="n">
-        <v>-0.0018</v>
+        <v>-0.0023</v>
       </c>
       <c r="G158" s="11" t="n">
-        <v>-0.0037</v>
+        <v>-0.0047</v>
       </c>
       <c r="H158" s="11" t="n">
-        <v>-0.0073</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="I158" s="9" t="inlineStr">
         <is>
@@ -11600,15 +11574,13 @@
         </is>
       </c>
       <c r="J158" s="9" t="n">
-        <v>43.05</v>
+        <v>42.22</v>
       </c>
       <c r="K158" s="9" t="n">
-        <v>10.07</v>
-      </c>
-      <c r="L158" s="9" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
+        <v>10.09</v>
+      </c>
+      <c r="L158" s="9" t="n">
+        <v>0.68</v>
       </c>
       <c r="M158" s="9" t="n">
         <v>3.36</v>
@@ -11630,7 +11602,7 @@
       </c>
       <c r="Q158" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:13</t>
+          <t>2026-10-13 23:50</t>
         </is>
       </c>
     </row>
@@ -11646,22 +11618,22 @@
         </is>
       </c>
       <c r="C159" s="10" t="n">
-        <v>32.725</v>
+        <v>33.01</v>
       </c>
       <c r="D159" s="10" t="n">
         <v>35.82</v>
       </c>
       <c r="E159" s="10" t="n">
-        <v>21.96</v>
+        <v>22.01</v>
       </c>
       <c r="F159" s="11" t="n">
-        <v>0.0143</v>
+        <v>0.0107</v>
       </c>
       <c r="G159" s="11" t="n">
-        <v>0.0285</v>
+        <v>0.0214</v>
       </c>
       <c r="H159" s="11" t="n">
-        <v>0.0571</v>
+        <v>0.0429</v>
       </c>
       <c r="I159" s="9" t="inlineStr">
         <is>
@@ -11669,13 +11641,13 @@
         </is>
       </c>
       <c r="J159" s="9" t="n">
-        <v>13.81</v>
+        <v>13.7</v>
       </c>
       <c r="K159" s="9" t="n">
         <v>1.21</v>
       </c>
       <c r="L159" s="9" t="n">
-        <v>4.5</v>
+        <v>4.53</v>
       </c>
       <c r="M159" s="9" t="n">
         <v>0.33</v>
@@ -11697,7 +11669,7 @@
       </c>
       <c r="Q159" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:13</t>
+          <t>2026-10-13 23:50</t>
         </is>
       </c>
     </row>
@@ -11713,7 +11685,7 @@
         </is>
       </c>
       <c r="C160" s="10" t="n">
-        <v>2.09</v>
+        <v>2.085</v>
       </c>
       <c r="D160" s="10" t="n">
         <v>2.74</v>
@@ -11722,13 +11694,13 @@
         <v>2.005</v>
       </c>
       <c r="F160" s="11" t="n">
-        <v>0.0688</v>
+        <v>0.06950000000000001</v>
       </c>
       <c r="G160" s="11" t="n">
-        <v>0.1375</v>
+        <v>0.1391</v>
       </c>
       <c r="H160" s="11" t="n">
-        <v>0.2751</v>
+        <v>0.2781</v>
       </c>
       <c r="I160" s="9" t="inlineStr">
         <is>
@@ -11736,13 +11708,13 @@
         </is>
       </c>
       <c r="J160" s="9" t="n">
-        <v>11</v>
+        <v>10.97</v>
       </c>
       <c r="K160" s="9" t="n">
-        <v>130.62</v>
+        <v>130.31</v>
       </c>
       <c r="L160" s="9" t="n">
-        <v>17.04</v>
+        <v>17</v>
       </c>
       <c r="M160" s="9" t="n">
         <v>0.49</v>
@@ -11764,7 +11736,7 @@
       </c>
       <c r="Q160" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:13</t>
+          <t>2026-10-13 23:50</t>
         </is>
       </c>
     </row>
@@ -11780,7 +11752,7 @@
         </is>
       </c>
       <c r="C161" s="6" t="n">
-        <v>32.89</v>
+        <v>32.66</v>
       </c>
       <c r="D161" s="6" t="n">
         <v>86.92</v>
@@ -11789,13 +11761,13 @@
         <v>28.76</v>
       </c>
       <c r="F161" s="7" t="n">
-        <v>0.207</v>
+        <v>0.2023</v>
       </c>
       <c r="G161" s="7" t="n">
-        <v>0.4141</v>
+        <v>0.4046</v>
       </c>
       <c r="H161" s="7" t="n">
-        <v>0.8280999999999999</v>
+        <v>0.8091</v>
       </c>
       <c r="I161" s="5" t="inlineStr">
         <is>
@@ -11803,13 +11775,13 @@
         </is>
       </c>
       <c r="J161" s="5" t="n">
-        <v>41.63</v>
+        <v>42.97</v>
       </c>
       <c r="K161" s="5" t="n">
-        <v>4.04</v>
+        <v>3.9</v>
       </c>
       <c r="L161" s="5" t="n">
-        <v>7.92</v>
+        <v>7.87</v>
       </c>
       <c r="M161" s="5" t="n">
         <v>1.15</v>
@@ -11831,7 +11803,7 @@
       </c>
       <c r="Q161" s="5" t="inlineStr">
         <is>
-          <t>2026-10-13 02:13</t>
+          <t>2026-10-13 23:50</t>
         </is>
       </c>
     </row>
@@ -11847,7 +11819,7 @@
         </is>
       </c>
       <c r="C162" s="6" t="n">
-        <v>60.05</v>
+        <v>58.75</v>
       </c>
       <c r="D162" s="6" t="n">
         <v>157.965</v>
@@ -11856,13 +11828,13 @@
         <v>55.09</v>
       </c>
       <c r="F162" s="7" t="n">
-        <v>0.2609</v>
+        <v>0.2727</v>
       </c>
       <c r="G162" s="7" t="n">
-        <v>0.5217000000000001</v>
+        <v>0.5454</v>
       </c>
       <c r="H162" s="7" t="n">
-        <v>1.0434</v>
+        <v>1.0908</v>
       </c>
       <c r="I162" s="5" t="inlineStr">
         <is>
@@ -11870,13 +11842,13 @@
         </is>
       </c>
       <c r="J162" s="5" t="n">
-        <v>31.87</v>
+        <v>31.19</v>
       </c>
       <c r="K162" s="5" t="n">
-        <v>2.27</v>
+        <v>2.31</v>
       </c>
       <c r="L162" s="5" t="n">
-        <v>3.85</v>
+        <v>3.77</v>
       </c>
       <c r="M162" s="5" t="n">
         <v>0.39</v>
@@ -11898,7 +11870,7 @@
       </c>
       <c r="Q162" s="5" t="inlineStr">
         <is>
-          <t>2026-10-13 02:13</t>
+          <t>2026-10-13 23:50</t>
         </is>
       </c>
     </row>
@@ -11914,7 +11886,7 @@
         </is>
       </c>
       <c r="C163" s="6" t="n">
-        <v>2.16</v>
+        <v>2.175</v>
       </c>
       <c r="D163" s="6" t="n">
         <v>4.93</v>
@@ -11923,13 +11895,13 @@
         <v>1.375</v>
       </c>
       <c r="F163" s="7" t="n">
-        <v>0.2422</v>
+        <v>0.2388</v>
       </c>
       <c r="G163" s="7" t="n">
-        <v>0.4844</v>
+        <v>0.4776</v>
       </c>
       <c r="H163" s="7" t="n">
-        <v>0.9688</v>
+        <v>0.9552</v>
       </c>
       <c r="I163" s="5" t="inlineStr">
         <is>
@@ -11937,13 +11909,13 @@
         </is>
       </c>
       <c r="J163" s="5" t="n">
-        <v>24</v>
+        <v>27.19</v>
       </c>
       <c r="K163" s="5" t="n">
-        <v>4.13</v>
+        <v>4.03</v>
       </c>
       <c r="L163" s="5" t="n">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="M163" s="5" t="n">
         <v>4.09</v>
@@ -11965,7 +11937,7 @@
       </c>
       <c r="Q163" s="5" t="inlineStr">
         <is>
-          <t>2026-10-13 02:13</t>
+          <t>2026-10-13 23:50</t>
         </is>
       </c>
     </row>
@@ -12104,7 +12076,7 @@
         </is>
       </c>
       <c r="C2" s="6" t="n">
-        <v>0.22</v>
+        <v>0.225</v>
       </c>
       <c r="D2" s="6" t="n">
         <v>0.43</v>
@@ -12113,13 +12085,13 @@
         <v>0.105</v>
       </c>
       <c r="F2" s="7" t="n">
-        <v>0.09470000000000001</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="G2" s="7" t="n">
-        <v>0.1894</v>
+        <v>0.1741</v>
       </c>
       <c r="H2" s="7" t="n">
-        <v>0.3788</v>
+        <v>0.3481</v>
       </c>
       <c r="I2" s="5" t="inlineStr">
         <is>
@@ -12127,13 +12099,13 @@
         </is>
       </c>
       <c r="J2" s="5" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="K2" s="5" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="L2" s="5" t="n">
-        <v>39.9</v>
+        <v>40.81</v>
       </c>
       <c r="M2" s="5" t="n">
         <v>9.02</v>
@@ -12155,7 +12127,7 @@
       </c>
       <c r="Q2" s="5" t="inlineStr">
         <is>
-          <t>2026-10-13 02:13</t>
+          <t>2026-10-13 23:50</t>
         </is>
       </c>
     </row>
@@ -12230,7 +12202,7 @@
       </c>
       <c r="Q3" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:13</t>
+          <t>2026-10-13 23:50</t>
         </is>
       </c>
     </row>
@@ -12246,22 +12218,22 @@
         </is>
       </c>
       <c r="C4" s="10" t="n">
-        <v>0.727</v>
+        <v>0.71</v>
       </c>
       <c r="D4" s="10" t="n">
         <v>2.65</v>
       </c>
       <c r="E4" s="10" t="n">
-        <v>0.72</v>
+        <v>0.707</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>0.1491</v>
+        <v>0.148</v>
       </c>
       <c r="G4" s="11" t="n">
-        <v>0.2981</v>
+        <v>0.2961</v>
       </c>
       <c r="H4" s="11" t="n">
-        <v>0.5962</v>
+        <v>0.5921999999999999</v>
       </c>
       <c r="I4" s="9" t="inlineStr">
         <is>
@@ -12269,13 +12241,13 @@
         </is>
       </c>
       <c r="J4" s="9" t="n">
-        <v>24.23</v>
+        <v>23.67</v>
       </c>
       <c r="K4" s="9" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="L4" s="9" t="n">
-        <v>3.63</v>
+        <v>3.55</v>
       </c>
       <c r="M4" s="9" t="n">
         <v>0.34</v>
@@ -12297,7 +12269,7 @@
       </c>
       <c r="Q4" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:13</t>
+          <t>2026-10-13 23:50</t>
         </is>
       </c>
     </row>
@@ -12313,7 +12285,7 @@
         </is>
       </c>
       <c r="C5" s="10" t="n">
-        <v>0.034</v>
+        <v>0.032</v>
       </c>
       <c r="D5" s="10" t="n">
         <v>0.16</v>
@@ -12341,10 +12313,10 @@
         </is>
       </c>
       <c r="K5" s="9" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="L5" s="9" t="n">
-        <v>74.23999999999999</v>
+        <v>69.87</v>
       </c>
       <c r="M5" s="9" t="n">
         <v>0.36</v>
@@ -12366,7 +12338,7 @@
       </c>
       <c r="Q5" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:13</t>
+          <t>2026-10-13 23:50</t>
         </is>
       </c>
     </row>
@@ -12382,7 +12354,7 @@
         </is>
       </c>
       <c r="C6" s="10" t="n">
-        <v>0.127</v>
+        <v>0.125</v>
       </c>
       <c r="D6" s="10" t="n">
         <v>0.24</v>
@@ -12391,13 +12363,13 @@
         <v>0.113</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>2.0897</v>
+        <v>2.1177</v>
       </c>
       <c r="G6" s="11" t="n">
-        <v>4.1794</v>
+        <v>4.2354</v>
       </c>
       <c r="H6" s="11" t="n">
-        <v>8.3588</v>
+        <v>8.470800000000001</v>
       </c>
       <c r="I6" s="9" t="inlineStr">
         <is>
@@ -12405,13 +12377,13 @@
         </is>
       </c>
       <c r="J6" s="9" t="n">
-        <v>-11.08</v>
+        <v>-10.91</v>
       </c>
       <c r="K6" s="9" t="n">
-        <v>9.85</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="L6" s="9" t="n">
-        <v>145.84</v>
+        <v>143.55</v>
       </c>
       <c r="M6" s="9" t="n">
         <v>2.95</v>
@@ -12433,7 +12405,7 @@
       </c>
       <c r="Q6" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:13</t>
+          <t>2026-10-13 23:50</t>
         </is>
       </c>
     </row>
@@ -12449,22 +12421,22 @@
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>0.037</v>
+        <v>0.036</v>
       </c>
       <c r="D7" s="6" t="n">
         <v>0.43</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>0.037</v>
+        <v>0.036</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>1.3041</v>
+        <v>1.3472</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>2.6081</v>
+        <v>2.6944</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>5.2162</v>
+        <v>5.3889</v>
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
@@ -12472,13 +12444,13 @@
         </is>
       </c>
       <c r="J7" s="5" t="n">
-        <v>-0.96</v>
+        <v>-0.93</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>9.880000000000001</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="M7" s="5" t="n">
         <v>0.7</v>
@@ -12500,7 +12472,7 @@
       </c>
       <c r="Q7" s="5" t="inlineStr">
         <is>
-          <t>2026-10-13 02:13</t>
+          <t>2026-10-13 23:50</t>
         </is>
       </c>
     </row>
@@ -12516,7 +12488,7 @@
         </is>
       </c>
       <c r="C8" s="10" t="n">
-        <v>6.225</v>
+        <v>6.29</v>
       </c>
       <c r="D8" s="10" t="n">
         <v>6.96</v>
@@ -12525,13 +12497,13 @@
         <v>4.42</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>0.0219</v>
+        <v>0.0191</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>0.0439</v>
+        <v>0.0383</v>
       </c>
       <c r="H8" s="11" t="n">
-        <v>0.0878</v>
+        <v>0.0765</v>
       </c>
       <c r="I8" s="9" t="inlineStr">
         <is>
@@ -12539,13 +12511,13 @@
         </is>
       </c>
       <c r="J8" s="9" t="n">
-        <v>13.24</v>
+        <v>13.67</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>2.51</v>
+        <v>2.53</v>
       </c>
       <c r="L8" s="9" t="n">
-        <v>5.56</v>
+        <v>5.62</v>
       </c>
       <c r="M8" s="9" t="n">
         <v>0.09</v>
@@ -12567,7 +12539,7 @@
       </c>
       <c r="Q8" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:13</t>
+          <t>2026-10-13 23:50</t>
         </is>
       </c>
     </row>
@@ -12583,7 +12555,7 @@
         </is>
       </c>
       <c r="C9" s="10" t="n">
-        <v>0.777</v>
+        <v>0.785</v>
       </c>
       <c r="D9" s="10" t="n">
         <v>0.93</v>
@@ -12592,13 +12564,13 @@
         <v>0.405</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>0.0718</v>
+        <v>0.06850000000000001</v>
       </c>
       <c r="G9" s="11" t="n">
-        <v>0.1435</v>
+        <v>0.1369</v>
       </c>
       <c r="H9" s="11" t="n">
-        <v>0.287</v>
+        <v>0.2739</v>
       </c>
       <c r="I9" s="9" t="inlineStr">
         <is>
@@ -12606,13 +12578,13 @@
         </is>
       </c>
       <c r="J9" s="9" t="n">
-        <v>21.05</v>
+        <v>21.27</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>2.16</v>
+        <v>1.02</v>
       </c>
       <c r="L9" s="9" t="n">
-        <v>262.8</v>
+        <v>265.5</v>
       </c>
       <c r="M9" s="9" t="n">
         <v>0.21</v>
@@ -12634,7 +12606,7 @@
       </c>
       <c r="Q9" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:13</t>
+          <t>2026-10-13 23:50</t>
         </is>
       </c>
     </row>
@@ -12650,7 +12622,7 @@
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>15.63</v>
+        <v>15.69</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>18.22</v>
@@ -12659,13 +12631,13 @@
         <v>8.26</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>0.142</v>
+        <v>0.1386</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>0.284</v>
+        <v>0.2772</v>
       </c>
       <c r="H10" s="7" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.5544</v>
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
@@ -12673,13 +12645,13 @@
         </is>
       </c>
       <c r="J10" s="5" t="n">
-        <v>104.2</v>
+        <v>112.07</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>7.86</v>
+        <v>7.61</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>5.96</v>
+        <v>5.97</v>
       </c>
       <c r="M10" s="5" t="n">
         <v>1.19</v>
@@ -12701,7 +12673,7 @@
       </c>
       <c r="Q10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-13 02:13</t>
+          <t>2026-10-13 23:50</t>
         </is>
       </c>
     </row>
@@ -12717,7 +12689,7 @@
         </is>
       </c>
       <c r="C11" s="10" t="n">
-        <v>0.162</v>
+        <v>0.165</v>
       </c>
       <c r="D11" s="10" t="n">
         <v>0.49</v>
@@ -12726,13 +12698,13 @@
         <v>0.145</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>0.0298</v>
+        <v>0.0237</v>
       </c>
       <c r="G11" s="11" t="n">
-        <v>0.0597</v>
+        <v>0.0473</v>
       </c>
       <c r="H11" s="11" t="n">
-        <v>0.1193</v>
+        <v>0.0946</v>
       </c>
       <c r="I11" s="9" t="inlineStr">
         <is>
@@ -12740,13 +12712,13 @@
         </is>
       </c>
       <c r="J11" s="9" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="L11" s="9" t="n">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="M11" s="9" t="n">
         <v>3.69</v>
@@ -12768,7 +12740,7 @@
       </c>
       <c r="Q11" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:13</t>
+          <t>2026-10-13 23:50</t>
         </is>
       </c>
     </row>
@@ -12784,7 +12756,7 @@
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>8.105</v>
+        <v>7.48</v>
       </c>
       <c r="D12" s="6" t="n">
         <v>15.1</v>
@@ -12793,13 +12765,13 @@
         <v>7.45</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>0.163</v>
+        <v>0.1946</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>0.326</v>
+        <v>0.3892</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>0.652</v>
+        <v>0.7785</v>
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
@@ -12807,13 +12779,13 @@
         </is>
       </c>
       <c r="J12" s="5" t="n">
-        <v>405.25</v>
+        <v>374</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>2.27</v>
+        <v>2.02</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>11.97</v>
+        <v>11.04</v>
       </c>
       <c r="M12" s="5" t="n">
         <v>0.17</v>
@@ -12835,7 +12807,7 @@
       </c>
       <c r="Q12" s="5" t="inlineStr">
         <is>
-          <t>2026-10-13 02:13</t>
+          <t>2026-10-13 23:50</t>
         </is>
       </c>
     </row>
@@ -12851,7 +12823,7 @@
         </is>
       </c>
       <c r="C13" s="10" t="n">
-        <v>22.11</v>
+        <v>21.63</v>
       </c>
       <c r="D13" s="10" t="n">
         <v>25</v>
@@ -12860,13 +12832,13 @@
         <v>14.41</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>0.0055</v>
+        <v>0.0112</v>
       </c>
       <c r="G13" s="11" t="n">
-        <v>0.011</v>
+        <v>0.0223</v>
       </c>
       <c r="H13" s="11" t="n">
-        <v>0.022</v>
+        <v>0.0447</v>
       </c>
       <c r="I13" s="9" t="inlineStr">
         <is>
@@ -12874,13 +12846,13 @@
         </is>
       </c>
       <c r="J13" s="9" t="n">
-        <v>19.57</v>
+        <v>19.84</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>3.33</v>
+        <v>3.18</v>
       </c>
       <c r="L13" s="9" t="n">
-        <v>6.28</v>
+        <v>6.15</v>
       </c>
       <c r="M13" s="9" t="n">
         <v>1.65</v>
@@ -12902,7 +12874,7 @@
       </c>
       <c r="Q13" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:13</t>
+          <t>2026-10-13 23:50</t>
         </is>
       </c>
     </row>
@@ -12969,7 +12941,7 @@
       </c>
       <c r="Q14" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:13</t>
+          <t>2026-10-13 23:50</t>
         </is>
       </c>
     </row>
@@ -12985,7 +12957,7 @@
         </is>
       </c>
       <c r="C15" s="10" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="D15" s="10" t="n">
         <v>1.12</v>
@@ -12994,13 +12966,13 @@
         <v>0.755</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>0.0818</v>
+        <v>0.0798</v>
       </c>
       <c r="G15" s="11" t="n">
-        <v>0.1636</v>
+        <v>0.1595</v>
       </c>
       <c r="H15" s="11" t="n">
-        <v>0.3272</v>
+        <v>0.319</v>
       </c>
       <c r="I15" s="9" t="inlineStr">
         <is>
@@ -13008,13 +12980,13 @@
         </is>
       </c>
       <c r="J15" s="9" t="n">
-        <v>-442.62</v>
+        <v>-445.36</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>-16.2</v>
+        <v>-16.3</v>
       </c>
       <c r="L15" s="9" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="M15" s="9" t="inlineStr">
         <is>
@@ -13038,7 +13010,7 @@
       </c>
       <c r="Q15" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:14</t>
+          <t>2026-10-13 23:50</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13026,7 @@
         </is>
       </c>
       <c r="C16" s="10" t="n">
-        <v>0.044</v>
+        <v>0.045</v>
       </c>
       <c r="D16" s="10" t="n">
         <v>0.155</v>
@@ -13063,13 +13035,13 @@
         <v>0.033</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>1.1705</v>
+        <v>1.1389</v>
       </c>
       <c r="G16" s="11" t="n">
-        <v>2.3409</v>
+        <v>2.2778</v>
       </c>
       <c r="H16" s="11" t="n">
-        <v>4.6818</v>
+        <v>4.5556</v>
       </c>
       <c r="I16" s="9" t="inlineStr">
         <is>
@@ -13077,10 +13049,10 @@
         </is>
       </c>
       <c r="J16" s="9" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="L16" s="9" t="n">
         <v>0.13</v>
@@ -13105,7 +13077,7 @@
       </c>
       <c r="Q16" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:14</t>
+          <t>2026-10-13 23:50</t>
         </is>
       </c>
     </row>
@@ -13121,22 +13093,22 @@
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>0.98</v>
+        <v>0.995</v>
       </c>
       <c r="D17" s="6" t="n">
         <v>2.63</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>0.975</v>
+        <v>0.96</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>0.3155</v>
+        <v>0.307</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>0.631</v>
+        <v>0.6139</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>1.2619</v>
+        <v>1.2278</v>
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
@@ -13144,10 +13116,10 @@
         </is>
       </c>
       <c r="J17" s="5" t="n">
-        <v>-25.12</v>
+        <v>-21.96</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>3.51</v>
+        <v>3.57</v>
       </c>
       <c r="L17" s="5" t="inlineStr">
         <is>
@@ -13174,7 +13146,7 @@
       </c>
       <c r="Q17" s="5" t="inlineStr">
         <is>
-          <t>2026-10-13 02:14</t>
+          <t>2026-10-13 23:50</t>
         </is>
       </c>
     </row>
@@ -13249,7 +13221,7 @@
       </c>
       <c r="Q18" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:14</t>
+          <t>2026-10-13 23:50</t>
         </is>
       </c>
     </row>
@@ -13265,7 +13237,7 @@
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>0.985</v>
+        <v>0.99</v>
       </c>
       <c r="D19" s="6" t="n">
         <v>1.08</v>
@@ -13274,13 +13246,13 @@
         <v>0.365</v>
       </c>
       <c r="F19" s="7" t="n">
-        <v>0.0673</v>
+        <v>0.06569999999999999</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>0.1345</v>
+        <v>0.1313</v>
       </c>
       <c r="H19" s="7" t="n">
-        <v>0.269</v>
+        <v>0.2626</v>
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
@@ -13288,13 +13260,13 @@
         </is>
       </c>
       <c r="J19" s="5" t="n">
-        <v>-30.31</v>
+        <v>-30.46</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>255.22</v>
+        <v>256.51</v>
       </c>
       <c r="M19" s="5" t="n">
         <v>0.4</v>
@@ -13316,7 +13288,7 @@
       </c>
       <c r="Q19" s="5" t="inlineStr">
         <is>
-          <t>2026-10-13 02:14</t>
+          <t>2026-10-13 23:50</t>
         </is>
       </c>
     </row>
@@ -13332,22 +13304,22 @@
         </is>
       </c>
       <c r="C20" s="10" t="n">
-        <v>0.882</v>
+        <v>0.867</v>
       </c>
       <c r="D20" s="10" t="n">
         <v>2.97</v>
       </c>
       <c r="E20" s="10" t="n">
-        <v>0.877</v>
+        <v>0.862</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>0.287</v>
+        <v>0.2963</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>0.574</v>
+        <v>0.5926</v>
       </c>
       <c r="H20" s="11" t="n">
-        <v>1.148</v>
+        <v>1.1852</v>
       </c>
       <c r="I20" s="9" t="inlineStr">
         <is>
@@ -13355,13 +13327,13 @@
         </is>
       </c>
       <c r="J20" s="9" t="n">
-        <v>88.2</v>
+        <v>86.7</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="L20" s="9" t="n">
-        <v>115.7</v>
+        <v>113.75</v>
       </c>
       <c r="M20" s="9" t="n">
         <v>0.49</v>
@@ -13383,7 +13355,7 @@
       </c>
       <c r="Q20" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:14</t>
+          <t>2026-10-13 23:51</t>
         </is>
       </c>
     </row>
@@ -13399,7 +13371,7 @@
         </is>
       </c>
       <c r="C21" s="10" t="n">
-        <v>1.265</v>
+        <v>1.217</v>
       </c>
       <c r="D21" s="10" t="n">
         <v>2.15</v>
@@ -13408,13 +13380,13 @@
         <v>0.995</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>0.0595</v>
+        <v>0.0717</v>
       </c>
       <c r="G21" s="11" t="n">
-        <v>0.119</v>
+        <v>0.1434</v>
       </c>
       <c r="H21" s="11" t="n">
-        <v>0.2379</v>
+        <v>0.2867</v>
       </c>
       <c r="I21" s="9" t="inlineStr">
         <is>
@@ -13422,13 +13394,13 @@
         </is>
       </c>
       <c r="J21" s="9" t="n">
-        <v>126.5</v>
+        <v>121.7</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="L21" s="9" t="n">
-        <v>3.48</v>
+        <v>3.34</v>
       </c>
       <c r="M21" s="9" t="n">
         <v>0.07000000000000001</v>
@@ -13450,76 +13422,76 @@
       </c>
       <c r="Q21" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:14</t>
+          <t>2026-10-13 23:51</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t>PEN</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B22" s="9" t="inlineStr">
         <is>
           <t>Peninsula Energy Limited</t>
         </is>
       </c>
-      <c r="C22" s="6" t="n">
-        <v>0.187</v>
-      </c>
-      <c r="D22" s="6" t="n">
+      <c r="C22" s="10" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D22" s="10" t="n">
         <v>1.075</v>
       </c>
-      <c r="E22" s="6" t="n">
-        <v>0.185</v>
-      </c>
-      <c r="F22" s="7" t="n">
-        <v>0.7927999999999999</v>
-      </c>
-      <c r="G22" s="7" t="n">
-        <v>1.5856</v>
-      </c>
-      <c r="H22" s="7" t="n">
-        <v>3.1711</v>
-      </c>
-      <c r="I22" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J22" s="5" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="K22" s="5" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="L22" s="5" t="n">
-        <v>163.43</v>
-      </c>
-      <c r="M22" s="5" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="N22" s="8" t="inlineStr">
+      <c r="E22" s="10" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="F22" s="11" t="n">
+        <v>0.8333</v>
+      </c>
+      <c r="G22" s="11" t="n">
+        <v>1.6667</v>
+      </c>
+      <c r="H22" s="11" t="n">
+        <v>3.3333</v>
+      </c>
+      <c r="I22" s="9" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="J22" s="9" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="K22" s="9" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="L22" s="9" t="n">
+        <v>157.31</v>
+      </c>
+      <c r="M22" s="9" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="N22" s="12" t="inlineStr">
         <is>
           <t>2024: $11.9M | 2023: $40.4M | 2022: $18.3M</t>
         </is>
       </c>
-      <c r="O22" s="8" t="inlineStr">
+      <c r="O22" s="12" t="inlineStr">
         <is>
           <t>2025: $-12.5M | 2024: $-12.4M | 2023: $-3.5M | 2022: $-4.6M</t>
         </is>
       </c>
-      <c r="P22" s="8" t="inlineStr">
+      <c r="P22" s="12" t="inlineStr">
         <is>
           <t>Peninsula Energy Limited, together with its subsidiaries, operates as a uranium mining company in the United States. Its flagship project is the Lance Project, which consists of the Ross Production Area, Kendrick Mining Area, and Barber Exploration Area located in Wyoming. The company was formerly known as Peninsula Minerals Limited and changed its name to Peninsula Energy Limited in November 2...</t>
         </is>
       </c>
-      <c r="Q22" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-13 02:14</t>
+      <c r="Q22" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-13 23:51</t>
         </is>
       </c>
     </row>
@@ -13535,13 +13507,13 @@
         </is>
       </c>
       <c r="C23" s="10" t="n">
-        <v>0.022</v>
+        <v>0.021</v>
       </c>
       <c r="D23" s="10" t="n">
         <v>0.135</v>
       </c>
       <c r="E23" s="10" t="n">
-        <v>0.022</v>
+        <v>0.02</v>
       </c>
       <c r="F23" s="11" t="n">
         <v/>
@@ -13558,10 +13530,10 @@
         </is>
       </c>
       <c r="J23" s="9" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>0.36</v>
+        <v>0.34</v>
       </c>
       <c r="L23" s="9" t="inlineStr">
         <is>
@@ -13588,7 +13560,7 @@
       </c>
       <c r="Q23" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:14</t>
+          <t>2026-10-13 23:51</t>
         </is>
       </c>
     </row>
@@ -13663,7 +13635,7 @@
       </c>
       <c r="Q24" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:14</t>
+          <t>2026-10-13 23:51</t>
         </is>
       </c>
     </row>
@@ -13679,22 +13651,22 @@
         </is>
       </c>
       <c r="C25" s="10" t="n">
-        <v>1.23</v>
+        <v>1.195</v>
       </c>
       <c r="D25" s="10" t="n">
         <v>7.52</v>
       </c>
       <c r="E25" s="10" t="n">
-        <v>1.23</v>
+        <v>1.192</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>1.2236</v>
+        <v>1.2667</v>
       </c>
       <c r="G25" s="11" t="n">
-        <v>2.4472</v>
+        <v>2.5335</v>
       </c>
       <c r="H25" s="11" t="n">
-        <v>4.8943</v>
+        <v>5.0669</v>
       </c>
       <c r="I25" s="9" t="inlineStr">
         <is>
@@ -13702,13 +13674,13 @@
         </is>
       </c>
       <c r="J25" s="9" t="n">
-        <v>-9.619999999999999</v>
+        <v>-9.31</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="L25" s="9" t="n">
-        <v>107.2</v>
+        <v>104.15</v>
       </c>
       <c r="M25" s="9" t="n">
         <v>5.57</v>
@@ -13730,7 +13702,7 @@
       </c>
       <c r="Q25" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:14</t>
+          <t>2026-10-13 23:51</t>
         </is>
       </c>
     </row>
@@ -13805,7 +13777,7 @@
       </c>
       <c r="Q26" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:14</t>
+          <t>2026-10-13 23:51</t>
         </is>
       </c>
     </row>
@@ -13874,7 +13846,7 @@
       </c>
       <c r="Q27" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:14</t>
+          <t>2026-10-13 23:51</t>
         </is>
       </c>
     </row>
@@ -13949,7 +13921,7 @@
       </c>
       <c r="Q28" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:14</t>
+          <t>2026-10-13 23:51</t>
         </is>
       </c>
     </row>
@@ -14024,7 +13996,7 @@
       </c>
       <c r="Q29" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:14</t>
+          <t>2026-10-13 23:51</t>
         </is>
       </c>
     </row>
@@ -14040,7 +14012,7 @@
         </is>
       </c>
       <c r="C30" s="10" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="D30" s="10" t="n">
         <v>1.015</v>
@@ -14063,13 +14035,13 @@
         </is>
       </c>
       <c r="J30" s="9" t="n">
-        <v>-0.93</v>
+        <v>-0.95</v>
       </c>
       <c r="K30" s="9" t="n">
         <v>0.38</v>
       </c>
       <c r="L30" s="9" t="n">
-        <v>15.28</v>
+        <v>15.46</v>
       </c>
       <c r="M30" s="9" t="n">
         <v>0.58</v>
@@ -14091,7 +14063,7 @@
       </c>
       <c r="Q30" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:14</t>
+          <t>2026-10-13 23:51</t>
         </is>
       </c>
     </row>
@@ -14107,7 +14079,7 @@
         </is>
       </c>
       <c r="C31" s="6" t="n">
-        <v>19.11</v>
+        <v>17.72</v>
       </c>
       <c r="D31" s="6" t="n">
         <v>23.2</v>
@@ -14116,13 +14088,13 @@
         <v>6.4</v>
       </c>
       <c r="F31" s="7" t="n">
-        <v>0.1173</v>
+        <v>0.1443</v>
       </c>
       <c r="G31" s="7" t="n">
-        <v>0.2345</v>
+        <v>0.2886</v>
       </c>
       <c r="H31" s="7" t="n">
-        <v>0.4691</v>
+        <v>0.5770999999999999</v>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
@@ -14130,13 +14102,13 @@
         </is>
       </c>
       <c r="J31" s="5" t="n">
-        <v>20.4</v>
+        <v>18.92</v>
       </c>
       <c r="K31" s="5" t="n">
-        <v>4.09</v>
+        <v>3.8</v>
       </c>
       <c r="L31" s="5" t="n">
-        <v>14.86</v>
+        <v>13.78</v>
       </c>
       <c r="M31" s="5" t="n">
         <v>0.11</v>
@@ -14158,7 +14130,7 @@
       </c>
       <c r="Q31" s="5" t="inlineStr">
         <is>
-          <t>2026-10-13 02:14</t>
+          <t>2026-10-13 23:51</t>
         </is>
       </c>
     </row>
@@ -14174,22 +14146,22 @@
         </is>
       </c>
       <c r="C32" s="10" t="n">
-        <v>2.61</v>
+        <v>2.65</v>
       </c>
       <c r="D32" s="10" t="n">
         <v>8.890000000000001</v>
       </c>
       <c r="E32" s="10" t="n">
-        <v>2.61</v>
+        <v>2.635</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>0.6245000000000001</v>
+        <v>0.6113</v>
       </c>
       <c r="G32" s="11" t="n">
-        <v>1.249</v>
+        <v>1.2226</v>
       </c>
       <c r="H32" s="11" t="n">
-        <v>2.4981</v>
+        <v>2.4453</v>
       </c>
       <c r="I32" s="9" t="inlineStr">
         <is>
@@ -14197,13 +14169,13 @@
         </is>
       </c>
       <c r="J32" s="9" t="n">
-        <v>-17.4</v>
+        <v>-17.67</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>4.07</v>
+        <v>4.13</v>
       </c>
       <c r="L32" s="9" t="n">
-        <v>41.47</v>
+        <v>42.11</v>
       </c>
       <c r="M32" s="9" t="n">
         <v>0.24</v>
@@ -14225,7 +14197,7 @@
       </c>
       <c r="Q32" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:14</t>
+          <t>2026-10-13 23:51</t>
         </is>
       </c>
     </row>
@@ -14300,7 +14272,7 @@
       </c>
       <c r="Q33" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:14</t>
+          <t>2026-10-13 23:51</t>
         </is>
       </c>
     </row>
@@ -14316,7 +14288,7 @@
         </is>
       </c>
       <c r="C34" s="6" t="n">
-        <v>3.655</v>
+        <v>3.66</v>
       </c>
       <c r="D34" s="6" t="n">
         <v>5.16</v>
@@ -14325,13 +14297,13 @@
         <v>2.7</v>
       </c>
       <c r="F34" s="7" t="n">
-        <v>0.1021</v>
+        <v>0.1023</v>
       </c>
       <c r="G34" s="7" t="n">
-        <v>0.2041</v>
+        <v>0.2045</v>
       </c>
       <c r="H34" s="7" t="n">
-        <v>0.4082</v>
+        <v>0.409</v>
       </c>
       <c r="I34" s="5" t="inlineStr">
         <is>
@@ -14339,13 +14311,13 @@
         </is>
       </c>
       <c r="J34" s="5" t="n">
-        <v>52.21</v>
+        <v>52.29</v>
       </c>
       <c r="K34" s="5" t="n">
         <v>1.76</v>
       </c>
       <c r="L34" s="5" t="n">
-        <v>6.67</v>
+        <v>6.68</v>
       </c>
       <c r="M34" s="5" t="n">
         <v>2.02</v>
@@ -14367,7 +14339,7 @@
       </c>
       <c r="Q34" s="5" t="inlineStr">
         <is>
-          <t>2026-10-13 02:14</t>
+          <t>2026-10-13 23:51</t>
         </is>
       </c>
     </row>
@@ -14442,7 +14414,7 @@
       </c>
       <c r="Q35" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:14</t>
+          <t>2026-10-13 23:51</t>
         </is>
       </c>
     </row>
@@ -14458,7 +14430,7 @@
         </is>
       </c>
       <c r="C36" s="10" t="n">
-        <v>0.16</v>
+        <v>0.155</v>
       </c>
       <c r="D36" s="10" t="n">
         <v>0.325</v>
@@ -14467,13 +14439,13 @@
         <v>0.105</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>0.3906</v>
+        <v>0.4113</v>
       </c>
       <c r="G36" s="11" t="n">
-        <v>0.7812</v>
+        <v>0.8226</v>
       </c>
       <c r="H36" s="11" t="n">
-        <v>1.5625</v>
+        <v>1.6452</v>
       </c>
       <c r="I36" s="9" t="inlineStr">
         <is>
@@ -14481,13 +14453,13 @@
         </is>
       </c>
       <c r="J36" s="9" t="n">
-        <v>-9.41</v>
+        <v>-9.119999999999999</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>3.27</v>
+        <v>3.16</v>
       </c>
       <c r="L36" s="9" t="n">
-        <v>2306.83</v>
+        <v>2234.74</v>
       </c>
       <c r="M36" s="9" t="n">
         <v>0.44</v>
@@ -14509,7 +14481,7 @@
       </c>
       <c r="Q36" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:14</t>
+          <t>2026-10-13 23:51</t>
         </is>
       </c>
     </row>
@@ -14525,22 +14497,22 @@
         </is>
       </c>
       <c r="C37" s="10" t="n">
-        <v>0.157</v>
+        <v>0.155</v>
       </c>
       <c r="D37" s="10" t="n">
         <v>0.62</v>
       </c>
       <c r="E37" s="10" t="n">
-        <v>0.155</v>
+        <v>0.147</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>0.176</v>
+        <v>0.1815</v>
       </c>
       <c r="G37" s="11" t="n">
-        <v>0.3519</v>
+        <v>0.3629</v>
       </c>
       <c r="H37" s="11" t="n">
-        <v>0.7038</v>
+        <v>0.7258</v>
       </c>
       <c r="I37" s="9" t="inlineStr">
         <is>
@@ -14548,10 +14520,10 @@
         </is>
       </c>
       <c r="J37" s="9" t="n">
-        <v>-35.6</v>
+        <v>-35.15</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
       <c r="L37" s="9" t="inlineStr">
         <is>
@@ -14578,7 +14550,7 @@
       </c>
       <c r="Q37" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:14</t>
+          <t>2026-10-13 23:51</t>
         </is>
       </c>
     </row>
@@ -14645,7 +14617,7 @@
       </c>
       <c r="Q38" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:14</t>
+          <t>2026-10-13 23:51</t>
         </is>
       </c>
     </row>
@@ -14720,7 +14692,7 @@
       </c>
       <c r="Q39" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:14</t>
+          <t>2026-10-13 23:51</t>
         </is>
       </c>
     </row>
@@ -14736,22 +14708,22 @@
         </is>
       </c>
       <c r="C40" s="10" t="n">
-        <v>0.147</v>
+        <v>0.15</v>
       </c>
       <c r="D40" s="10" t="n">
         <v>0.38</v>
       </c>
       <c r="E40" s="10" t="n">
-        <v>0.13</v>
+        <v>0.135</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>0.5153</v>
+        <v>0.5</v>
       </c>
       <c r="G40" s="11" t="n">
-        <v>1.0306</v>
+        <v>1</v>
       </c>
       <c r="H40" s="11" t="n">
-        <v>2.0612</v>
+        <v>2</v>
       </c>
       <c r="I40" s="9" t="inlineStr">
         <is>
@@ -14764,10 +14736,10 @@
         </is>
       </c>
       <c r="K40" s="9" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="L40" s="9" t="n">
-        <v>1079.81</v>
+        <v>664.28</v>
       </c>
       <c r="M40" s="9" t="n">
         <v>0.14</v>
@@ -14789,7 +14761,7 @@
       </c>
       <c r="Q40" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:14</t>
+          <t>2026-10-13 23:51</t>
         </is>
       </c>
     </row>
@@ -14805,7 +14777,7 @@
         </is>
       </c>
       <c r="C41" s="10" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="D41" s="10" t="n">
         <v>0.345</v>
@@ -14833,10 +14805,10 @@
         </is>
       </c>
       <c r="K41" s="9" t="n">
-        <v>5</v>
+        <v>3.09</v>
       </c>
       <c r="L41" s="9" t="n">
-        <v>5446.22</v>
+        <v>5105.83</v>
       </c>
       <c r="M41" s="9" t="inlineStr">
         <is>
@@ -14860,7 +14832,7 @@
       </c>
       <c r="Q41" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:14</t>
+          <t>2026-10-13 23:51</t>
         </is>
       </c>
     </row>
@@ -14876,7 +14848,7 @@
         </is>
       </c>
       <c r="C42" s="10" t="n">
-        <v>0.004</v>
+        <v>0.005</v>
       </c>
       <c r="D42" s="10" t="n">
         <v>0.019</v>
@@ -14904,7 +14876,7 @@
         </is>
       </c>
       <c r="K42" s="9" t="n">
-        <v>0.57</v>
+        <v>0.71</v>
       </c>
       <c r="L42" s="9" t="inlineStr">
         <is>
@@ -14933,7 +14905,7 @@
       </c>
       <c r="Q42" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:14</t>
+          <t>2026-10-13 23:51</t>
         </is>
       </c>
     </row>
@@ -15004,7 +14976,7 @@
       </c>
       <c r="Q43" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:14</t>
+          <t>2026-10-13 23:51</t>
         </is>
       </c>
     </row>
@@ -15079,7 +15051,7 @@
       </c>
       <c r="Q44" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:14</t>
+          <t>2026-10-13 23:51</t>
         </is>
       </c>
     </row>
@@ -15123,7 +15095,7 @@
         </is>
       </c>
       <c r="K45" s="9" t="n">
-        <v>0.7</v>
+        <v>0.74</v>
       </c>
       <c r="L45" s="9" t="n">
         <v>1067.65</v>
@@ -15148,7 +15120,7 @@
       </c>
       <c r="Q45" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 02:14</t>
+          <t>2026-10-13 23:51</t>
         </is>
       </c>
     </row>
